--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>2026-09-07 04:49</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 10:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,9 @@
       <c r="F2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +535,9 @@
       <c r="F3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,6 +564,9 @@
       <c r="F4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,6 +593,9 @@
       <c r="F5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,6 +622,9 @@
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +651,9 @@
       <c r="F7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,6 +680,9 @@
       <c r="F8" s="2" t="n">
         <v>19.99</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>19.99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +709,9 @@
       <c r="F9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -708,6 +738,9 @@
       <c r="F10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -734,6 +767,9 @@
       <c r="F11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -760,6 +796,9 @@
       <c r="F12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,6 +825,9 @@
       <c r="F13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -812,6 +854,9 @@
       <c r="F14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -838,6 +883,9 @@
       <c r="F15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -864,6 +912,9 @@
       <c r="F16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,6 +941,9 @@
       <c r="F17" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -916,6 +970,9 @@
       <c r="F18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -942,6 +999,9 @@
       <c r="F19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -968,6 +1028,9 @@
       <c r="F20" s="2" t="n">
         <v>20.45</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -994,6 +1057,9 @@
       <c r="F21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1020,6 +1086,9 @@
       <c r="F22" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1046,6 +1115,9 @@
       <c r="F23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1072,6 +1144,9 @@
       <c r="F24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1098,6 +1173,9 @@
       <c r="F25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1124,6 +1202,9 @@
       <c r="F26" s="2" t="n">
         <v>20.5</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1150,6 +1231,9 @@
       <c r="F27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1176,6 +1260,9 @@
       <c r="F28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1202,6 +1289,9 @@
       <c r="F29" s="2" t="n">
         <v>20.55</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>20.55</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1228,6 +1318,9 @@
       <c r="F30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1254,6 +1347,9 @@
       <c r="F31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1280,6 +1376,9 @@
       <c r="F32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1405,9 @@
       <c r="F33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1332,6 +1434,9 @@
       <c r="F34" s="2" t="n">
         <v>20.66</v>
       </c>
+      <c r="G34" s="2" t="n">
+        <v>20.66</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1358,6 +1463,9 @@
       <c r="F35" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G35" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1384,6 +1492,9 @@
       <c r="F36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1410,6 +1521,9 @@
       <c r="F37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1436,6 +1550,9 @@
       <c r="F38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1462,6 +1579,9 @@
       <c r="F39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G39" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1488,6 +1608,9 @@
       <c r="F40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1514,6 +1637,9 @@
       <c r="F41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1540,6 +1666,9 @@
       <c r="F42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1566,6 +1695,9 @@
       <c r="F43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1592,6 +1724,9 @@
       <c r="F44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1618,6 +1753,9 @@
       <c r="F45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1644,6 +1782,9 @@
       <c r="F46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="G46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1670,6 +1811,9 @@
       <c r="F47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1696,6 +1840,9 @@
       <c r="F48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1722,6 +1869,9 @@
       <c r="F49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1748,6 +1898,9 @@
       <c r="F50" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="G50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1774,6 +1927,9 @@
       <c r="F51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1800,6 +1956,9 @@
       <c r="F52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1826,6 +1985,9 @@
       <c r="F53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1852,6 +2014,9 @@
       <c r="F54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1878,6 +2043,9 @@
       <c r="F55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1904,6 +2072,9 @@
       <c r="F56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1930,6 +2101,9 @@
       <c r="F57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1956,6 +2130,9 @@
       <c r="F58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1982,6 +2159,9 @@
       <c r="F59" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G59" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2008,6 +2188,9 @@
       <c r="F60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2034,6 +2217,9 @@
       <c r="F61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2060,6 +2246,9 @@
       <c r="F62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2086,6 +2275,9 @@
       <c r="F63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2112,6 +2304,9 @@
       <c r="F64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2138,6 +2333,9 @@
       <c r="F65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2164,6 +2362,9 @@
       <c r="F66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2190,6 +2391,9 @@
       <c r="F67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2216,6 +2420,9 @@
       <c r="F68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2242,6 +2449,9 @@
       <c r="F69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2268,6 +2478,9 @@
       <c r="F70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2294,6 +2507,9 @@
       <c r="F71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2320,6 +2536,9 @@
       <c r="F72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2346,6 +2565,9 @@
       <c r="F73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2372,6 +2594,9 @@
       <c r="F74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2398,6 +2623,9 @@
       <c r="F75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2424,6 +2652,9 @@
       <c r="F76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2450,6 +2681,9 @@
       <c r="F77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2476,6 +2710,9 @@
       <c r="F78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2502,6 +2739,9 @@
       <c r="F79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2528,6 +2768,9 @@
       <c r="F80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2554,6 +2797,9 @@
       <c r="F81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2580,6 +2826,9 @@
       <c r="F82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2606,6 +2855,9 @@
       <c r="F83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2632,6 +2884,9 @@
       <c r="F84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2658,6 +2913,9 @@
       <c r="F85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2684,6 +2942,9 @@
       <c r="F86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2710,6 +2971,9 @@
       <c r="F87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2736,6 +3000,9 @@
       <c r="F88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2762,6 +3029,9 @@
       <c r="F89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2788,6 +3058,9 @@
       <c r="F90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2814,6 +3087,9 @@
       <c r="F91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2840,6 +3116,9 @@
       <c r="F92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2866,6 +3145,9 @@
       <c r="F93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2892,6 +3174,9 @@
       <c r="F94" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G94" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2918,6 +3203,9 @@
       <c r="F95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2944,6 +3232,9 @@
       <c r="F96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2970,6 +3261,9 @@
       <c r="F97" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G97" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2996,6 +3290,9 @@
       <c r="F98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3022,6 +3319,9 @@
       <c r="F99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3048,6 +3348,9 @@
       <c r="F100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3074,6 +3377,9 @@
       <c r="F101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3100,6 +3406,9 @@
       <c r="F102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3126,6 +3435,9 @@
       <c r="F103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3152,6 +3464,9 @@
       <c r="F104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3178,6 +3493,9 @@
       <c r="F105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3204,6 +3522,9 @@
       <c r="F106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3230,6 +3551,9 @@
       <c r="F107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="G107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3256,6 +3580,9 @@
       <c r="F108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3282,6 +3609,9 @@
       <c r="F109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3308,6 +3638,9 @@
       <c r="F110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3334,6 +3667,9 @@
       <c r="F111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3360,6 +3696,9 @@
       <c r="F112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3386,6 +3725,9 @@
       <c r="F113" s="2" t="n">
         <v>22</v>
       </c>
+      <c r="G113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3412,6 +3754,9 @@
       <c r="F114" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G114" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3438,6 +3783,9 @@
       <c r="F115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3464,6 +3812,9 @@
       <c r="F116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3490,6 +3841,9 @@
       <c r="F117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3516,6 +3870,9 @@
       <c r="F118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3542,6 +3899,9 @@
       <c r="F119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3568,6 +3928,9 @@
       <c r="F120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3594,6 +3957,9 @@
       <c r="F121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3620,6 +3986,9 @@
       <c r="F122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3646,6 +4015,9 @@
       <c r="F123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3672,6 +4044,9 @@
       <c r="F124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3698,6 +4073,9 @@
       <c r="F125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3724,6 +4102,9 @@
       <c r="F126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3750,6 +4131,9 @@
       <c r="F127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3776,6 +4160,9 @@
       <c r="F128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3802,6 +4189,9 @@
       <c r="F129" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G129" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3828,6 +4218,9 @@
       <c r="F130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3854,6 +4247,9 @@
       <c r="F131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3880,6 +4276,9 @@
       <c r="F132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="G132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3906,6 +4305,9 @@
       <c r="F133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3932,6 +4334,9 @@
       <c r="F134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3958,6 +4363,9 @@
       <c r="F135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3984,6 +4392,9 @@
       <c r="F136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4010,6 +4421,9 @@
       <c r="F137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4036,6 +4450,9 @@
       <c r="F138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4062,6 +4479,9 @@
       <c r="F139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4088,6 +4508,9 @@
       <c r="F140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4114,6 +4537,9 @@
       <c r="F141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4140,6 +4566,9 @@
       <c r="F142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4166,6 +4595,9 @@
       <c r="F143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4192,6 +4624,9 @@
       <c r="F144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4218,6 +4653,9 @@
       <c r="F145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="G145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4244,6 +4682,9 @@
       <c r="F146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4270,6 +4711,9 @@
       <c r="F147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4296,6 +4740,9 @@
       <c r="F148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4322,6 +4769,9 @@
       <c r="F149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="G149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4348,6 +4798,9 @@
       <c r="F150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4374,6 +4827,9 @@
       <c r="F151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="G151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4400,6 +4856,9 @@
       <c r="F152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4426,6 +4885,9 @@
       <c r="F153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4452,6 +4914,9 @@
       <c r="F154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="G154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4478,6 +4943,9 @@
       <c r="F155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4504,6 +4972,9 @@
       <c r="F156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4530,6 +5001,9 @@
       <c r="F157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4556,6 +5030,9 @@
       <c r="F158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4582,6 +5059,9 @@
       <c r="F159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="G159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4608,6 +5088,9 @@
       <c r="F160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4634,6 +5117,9 @@
       <c r="F161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4660,6 +5146,9 @@
       <c r="F162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="G162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4686,6 +5175,9 @@
       <c r="F163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="G163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4712,9 +5204,12 @@
       <c r="F164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="G164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F164"/>
+  <autoFilter ref="A1:G164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>2026-09-07 10:09</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +515,9 @@
       <c r="G2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="H2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +547,9 @@
       <c r="G3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +579,9 @@
       <c r="G4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="H4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +611,9 @@
       <c r="G5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,6 +643,9 @@
       <c r="G6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,6 +675,9 @@
       <c r="G7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="H7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +707,9 @@
       <c r="G8" s="2" t="n">
         <v>19.99</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <v>19.99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +739,9 @@
       <c r="G9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -741,6 +771,9 @@
       <c r="G10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,6 +803,9 @@
       <c r="G11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +835,9 @@
       <c r="G12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -828,6 +867,9 @@
       <c r="G13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="H13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +899,9 @@
       <c r="G14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -886,6 +931,9 @@
       <c r="G15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -915,6 +963,9 @@
       <c r="G16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -944,6 +995,9 @@
       <c r="G17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="H17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -973,6 +1027,9 @@
       <c r="G18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1002,6 +1059,9 @@
       <c r="G19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="H19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1031,6 +1091,9 @@
       <c r="G20" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H20" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1060,6 +1123,9 @@
       <c r="G21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1089,6 +1155,9 @@
       <c r="G22" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="H22" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1118,6 +1187,9 @@
       <c r="G23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1147,6 +1219,9 @@
       <c r="G24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1176,6 +1251,9 @@
       <c r="G25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1205,6 +1283,9 @@
       <c r="G26" s="2" t="n">
         <v>20.5</v>
       </c>
+      <c r="H26" s="2" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1234,6 +1315,9 @@
       <c r="G27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1263,6 +1347,9 @@
       <c r="G28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="H28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1292,6 +1379,9 @@
       <c r="G29" s="2" t="n">
         <v>20.55</v>
       </c>
+      <c r="H29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,6 +1411,9 @@
       <c r="G30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1350,6 +1443,9 @@
       <c r="G31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1379,6 +1475,9 @@
       <c r="G32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1507,9 @@
       <c r="G33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1437,6 +1539,9 @@
       <c r="G34" s="2" t="n">
         <v>20.66</v>
       </c>
+      <c r="H34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1466,6 +1571,9 @@
       <c r="G35" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1495,6 +1603,9 @@
       <c r="G36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1524,6 +1635,9 @@
       <c r="G37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1553,6 +1667,9 @@
       <c r="G38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1582,6 +1699,9 @@
       <c r="G39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H39" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,6 +1731,9 @@
       <c r="G40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1640,6 +1763,9 @@
       <c r="G41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1669,6 +1795,9 @@
       <c r="G42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1698,6 +1827,9 @@
       <c r="G43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1727,6 +1859,9 @@
       <c r="G44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1756,6 +1891,9 @@
       <c r="G45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1785,6 +1923,9 @@
       <c r="G46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="H46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1814,6 +1955,9 @@
       <c r="G47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1843,6 +1987,9 @@
       <c r="G48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1872,6 +2019,9 @@
       <c r="G49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1901,6 +2051,9 @@
       <c r="G50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1930,6 +2083,9 @@
       <c r="G51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="H51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1959,6 +2115,9 @@
       <c r="G52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="H52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1988,6 +2147,9 @@
       <c r="G53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2017,6 +2179,9 @@
       <c r="G54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2046,6 +2211,9 @@
       <c r="G55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2075,6 +2243,9 @@
       <c r="G56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2104,6 +2275,9 @@
       <c r="G57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2133,6 +2307,9 @@
       <c r="G58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2162,6 +2339,9 @@
       <c r="G59" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2191,6 +2371,9 @@
       <c r="G60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2220,6 +2403,9 @@
       <c r="G61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2249,6 +2435,9 @@
       <c r="G62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2278,6 +2467,9 @@
       <c r="G63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2307,6 +2499,9 @@
       <c r="G64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2336,6 +2531,9 @@
       <c r="G65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2365,6 +2563,9 @@
       <c r="G66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2394,6 +2595,9 @@
       <c r="G67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2423,6 +2627,9 @@
       <c r="G68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2452,6 +2659,9 @@
       <c r="G69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2481,6 +2691,9 @@
       <c r="G70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2510,6 +2723,9 @@
       <c r="G71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2539,6 +2755,9 @@
       <c r="G72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2568,6 +2787,9 @@
       <c r="G73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2597,6 +2819,9 @@
       <c r="G74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2626,6 +2851,9 @@
       <c r="G75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2655,6 +2883,9 @@
       <c r="G76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2684,6 +2915,9 @@
       <c r="G77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2713,6 +2947,9 @@
       <c r="G78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2742,6 +2979,9 @@
       <c r="G79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2771,6 +3011,9 @@
       <c r="G80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2800,6 +3043,9 @@
       <c r="G81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2829,6 +3075,9 @@
       <c r="G82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2858,6 +3107,9 @@
       <c r="G83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2887,6 +3139,9 @@
       <c r="G84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2916,6 +3171,9 @@
       <c r="G85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2945,6 +3203,9 @@
       <c r="G86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2974,6 +3235,9 @@
       <c r="G87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3003,6 +3267,9 @@
       <c r="G88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3032,6 +3299,9 @@
       <c r="G89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3061,6 +3331,9 @@
       <c r="G90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3090,6 +3363,9 @@
       <c r="G91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3119,6 +3395,9 @@
       <c r="G92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3148,6 +3427,9 @@
       <c r="G93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3177,6 +3459,9 @@
       <c r="G94" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3206,6 +3491,9 @@
       <c r="G95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3235,6 +3523,9 @@
       <c r="G96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3264,6 +3555,9 @@
       <c r="G97" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H97" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3293,6 +3587,9 @@
       <c r="G98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3322,6 +3619,9 @@
       <c r="G99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3351,6 +3651,9 @@
       <c r="G100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3380,6 +3683,9 @@
       <c r="G101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3409,6 +3715,9 @@
       <c r="G102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3438,6 +3747,9 @@
       <c r="G103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3467,6 +3779,9 @@
       <c r="G104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3496,6 +3811,9 @@
       <c r="G105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3525,6 +3843,9 @@
       <c r="G106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3554,6 +3875,9 @@
       <c r="G107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="H107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3583,6 +3907,9 @@
       <c r="G108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3612,6 +3939,9 @@
       <c r="G109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3641,6 +3971,9 @@
       <c r="G110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3670,6 +4003,9 @@
       <c r="G111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3699,6 +4035,9 @@
       <c r="G112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3728,6 +4067,9 @@
       <c r="G113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3757,6 +4099,9 @@
       <c r="G114" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H114" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3786,6 +4131,9 @@
       <c r="G115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3815,6 +4163,9 @@
       <c r="G116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3844,6 +4195,9 @@
       <c r="G117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3873,6 +4227,9 @@
       <c r="G118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3902,6 +4259,9 @@
       <c r="G119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3931,6 +4291,9 @@
       <c r="G120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3960,6 +4323,9 @@
       <c r="G121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3989,6 +4355,9 @@
       <c r="G122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4018,6 +4387,9 @@
       <c r="G123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4047,6 +4419,9 @@
       <c r="G124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4076,6 +4451,9 @@
       <c r="G125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4105,6 +4483,9 @@
       <c r="G126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4134,6 +4515,9 @@
       <c r="G127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4163,6 +4547,9 @@
       <c r="G128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4192,6 +4579,9 @@
       <c r="G129" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H129" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4221,6 +4611,9 @@
       <c r="G130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4250,6 +4643,9 @@
       <c r="G131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4279,6 +4675,9 @@
       <c r="G132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="H132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4308,6 +4707,9 @@
       <c r="G133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4337,6 +4739,9 @@
       <c r="G134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4366,6 +4771,9 @@
       <c r="G135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4395,6 +4803,9 @@
       <c r="G136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4424,6 +4835,9 @@
       <c r="G137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4453,6 +4867,9 @@
       <c r="G138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4482,6 +4899,9 @@
       <c r="G139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4511,6 +4931,9 @@
       <c r="G140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4540,6 +4963,9 @@
       <c r="G141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4569,6 +4995,9 @@
       <c r="G142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4598,6 +5027,9 @@
       <c r="G143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4627,6 +5059,9 @@
       <c r="G144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4656,6 +5091,9 @@
       <c r="G145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="H145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4685,6 +5123,9 @@
       <c r="G146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4714,6 +5155,9 @@
       <c r="G147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4743,6 +5187,9 @@
       <c r="G148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4772,6 +5219,9 @@
       <c r="G149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="H149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4801,6 +5251,9 @@
       <c r="G150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4830,6 +5283,9 @@
       <c r="G151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="H151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4859,6 +5315,9 @@
       <c r="G152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4888,6 +5347,9 @@
       <c r="G153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4917,6 +5379,9 @@
       <c r="G154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="H154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4946,6 +5411,9 @@
       <c r="G155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4975,6 +5443,9 @@
       <c r="G156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5004,6 +5475,9 @@
       <c r="G157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5033,6 +5507,9 @@
       <c r="G158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5062,6 +5539,9 @@
       <c r="G159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="H159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5091,6 +5571,9 @@
       <c r="G160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5120,6 +5603,9 @@
       <c r="G161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5149,6 +5635,9 @@
       <c r="G162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="H162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5178,6 +5667,9 @@
       <c r="G163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="H163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5207,9 +5699,12 @@
       <c r="G164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="H164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G164"/>
+  <autoFilter ref="A1:H164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +487,11 @@
           <t>2026-09-07 13:11</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 16:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +524,9 @@
       <c r="H2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,6 +559,9 @@
       <c r="H3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,6 +594,9 @@
       <c r="H4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,6 +629,9 @@
       <c r="H5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,6 +664,9 @@
       <c r="H6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +699,9 @@
       <c r="H7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -710,6 +734,9 @@
       <c r="H8" s="2" t="n">
         <v>19.99</v>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,6 +769,9 @@
       <c r="H9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -774,6 +804,9 @@
       <c r="H10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,6 +839,9 @@
       <c r="H11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -838,6 +874,9 @@
       <c r="H12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -870,6 +909,9 @@
       <c r="H13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -902,6 +944,9 @@
       <c r="H14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,6 +979,9 @@
       <c r="H15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -966,6 +1014,9 @@
       <c r="H16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -998,6 +1049,9 @@
       <c r="H17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1030,6 +1084,9 @@
       <c r="H18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1062,6 +1119,9 @@
       <c r="H19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1094,6 +1154,9 @@
       <c r="H20" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1126,6 +1189,9 @@
       <c r="H21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1158,6 +1224,9 @@
       <c r="H22" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I22" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1190,6 +1259,9 @@
       <c r="H23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1222,6 +1294,9 @@
       <c r="H24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,6 +1329,9 @@
       <c r="H25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1286,6 +1364,9 @@
       <c r="H26" s="2" t="n">
         <v>20.5</v>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1318,6 +1399,9 @@
       <c r="H27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1350,6 +1434,9 @@
       <c r="H28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="I28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1382,6 +1469,9 @@
       <c r="H29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1414,6 +1504,9 @@
       <c r="H30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1446,6 +1539,9 @@
       <c r="H31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1478,6 +1574,9 @@
       <c r="H32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,6 +1609,9 @@
       <c r="H33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1542,6 +1644,9 @@
       <c r="H34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1574,6 +1679,9 @@
       <c r="H35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1606,6 +1714,9 @@
       <c r="H36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1638,6 +1749,9 @@
       <c r="H37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1670,6 +1784,9 @@
       <c r="H38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1702,6 +1819,9 @@
       <c r="H39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I39" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1734,6 +1854,9 @@
       <c r="H40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1766,6 +1889,9 @@
       <c r="H41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1798,6 +1924,9 @@
       <c r="H42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1830,6 +1959,9 @@
       <c r="H43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1862,6 +1994,9 @@
       <c r="H44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1894,6 +2029,9 @@
       <c r="H45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1926,6 +2064,9 @@
       <c r="H46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="I46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1958,6 +2099,9 @@
       <c r="H47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1990,6 +2134,9 @@
       <c r="H48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2022,6 +2169,9 @@
       <c r="H49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2054,6 +2204,9 @@
       <c r="H50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2086,6 +2239,9 @@
       <c r="H51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="I51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2118,6 +2274,9 @@
       <c r="H52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="I52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2150,6 +2309,9 @@
       <c r="H53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2182,6 +2344,9 @@
       <c r="H54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2214,6 +2379,9 @@
       <c r="H55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2246,6 +2414,9 @@
       <c r="H56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2278,6 +2449,9 @@
       <c r="H57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,6 +2484,9 @@
       <c r="H58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2342,6 +2519,9 @@
       <c r="H59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="I59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2374,6 +2554,9 @@
       <c r="H60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2406,6 +2589,9 @@
       <c r="H61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2438,6 +2624,9 @@
       <c r="H62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,6 +2659,9 @@
       <c r="H63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2502,6 +2694,9 @@
       <c r="H64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,6 +2729,9 @@
       <c r="H65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2566,6 +2764,9 @@
       <c r="H66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2598,6 +2799,9 @@
       <c r="H67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2630,6 +2834,9 @@
       <c r="H68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2662,6 +2869,9 @@
       <c r="H69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2694,6 +2904,9 @@
       <c r="H70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2726,6 +2939,9 @@
       <c r="H71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2758,6 +2974,9 @@
       <c r="H72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2790,6 +3009,9 @@
       <c r="H73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2822,6 +3044,9 @@
       <c r="H74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2854,6 +3079,9 @@
       <c r="H75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2886,6 +3114,9 @@
       <c r="H76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2918,6 +3149,9 @@
       <c r="H77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2950,6 +3184,9 @@
       <c r="H78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2982,6 +3219,9 @@
       <c r="H79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3014,6 +3254,9 @@
       <c r="H80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3046,6 +3289,9 @@
       <c r="H81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3078,6 +3324,9 @@
       <c r="H82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3110,6 +3359,9 @@
       <c r="H83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3142,6 +3394,9 @@
       <c r="H84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3174,6 +3429,9 @@
       <c r="H85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3206,6 +3464,9 @@
       <c r="H86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3238,6 +3499,9 @@
       <c r="H87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3270,6 +3534,9 @@
       <c r="H88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3302,6 +3569,9 @@
       <c r="H89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3334,6 +3604,9 @@
       <c r="H90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3366,6 +3639,9 @@
       <c r="H91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3398,6 +3674,9 @@
       <c r="H92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3430,6 +3709,9 @@
       <c r="H93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3462,6 +3744,9 @@
       <c r="H94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3494,6 +3779,9 @@
       <c r="H95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3526,6 +3814,9 @@
       <c r="H96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3558,6 +3849,9 @@
       <c r="H97" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3590,6 +3884,9 @@
       <c r="H98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3622,6 +3919,9 @@
       <c r="H99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3654,6 +3954,9 @@
       <c r="H100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3686,6 +3989,9 @@
       <c r="H101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3718,6 +4024,9 @@
       <c r="H102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3750,6 +4059,9 @@
       <c r="H103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3782,6 +4094,9 @@
       <c r="H104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3814,6 +4129,9 @@
       <c r="H105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3846,6 +4164,9 @@
       <c r="H106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3878,6 +4199,9 @@
       <c r="H107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="I107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3910,6 +4234,9 @@
       <c r="H108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3942,6 +4269,9 @@
       <c r="H109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3974,6 +4304,9 @@
       <c r="H110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4006,6 +4339,9 @@
       <c r="H111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4038,6 +4374,9 @@
       <c r="H112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4070,6 +4409,9 @@
       <c r="H113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4102,6 +4444,9 @@
       <c r="H114" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I114" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4134,6 +4479,9 @@
       <c r="H115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4166,6 +4514,9 @@
       <c r="H116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4198,6 +4549,9 @@
       <c r="H117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4230,6 +4584,9 @@
       <c r="H118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4262,6 +4619,9 @@
       <c r="H119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4294,6 +4654,9 @@
       <c r="H120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4326,6 +4689,9 @@
       <c r="H121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4358,6 +4724,9 @@
       <c r="H122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4390,6 +4759,9 @@
       <c r="H123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4422,6 +4794,9 @@
       <c r="H124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4454,6 +4829,9 @@
       <c r="H125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4486,6 +4864,9 @@
       <c r="H126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4518,6 +4899,9 @@
       <c r="H127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4550,6 +4934,9 @@
       <c r="H128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4582,6 +4969,9 @@
       <c r="H129" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I129" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4614,6 +5004,9 @@
       <c r="H130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4646,6 +5039,9 @@
       <c r="H131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4678,6 +5074,9 @@
       <c r="H132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="I132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4710,6 +5109,9 @@
       <c r="H133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4742,6 +5144,9 @@
       <c r="H134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4774,6 +5179,9 @@
       <c r="H135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4806,6 +5214,9 @@
       <c r="H136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4838,6 +5249,9 @@
       <c r="H137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4870,6 +5284,9 @@
       <c r="H138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4902,6 +5319,9 @@
       <c r="H139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4934,6 +5354,9 @@
       <c r="H140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4966,6 +5389,9 @@
       <c r="H141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4998,6 +5424,9 @@
       <c r="H142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5030,6 +5459,9 @@
       <c r="H143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5062,6 +5494,9 @@
       <c r="H144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5094,6 +5529,9 @@
       <c r="H145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="I145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5126,6 +5564,9 @@
       <c r="H146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5158,6 +5599,9 @@
       <c r="H147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5190,6 +5634,9 @@
       <c r="H148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5222,6 +5669,9 @@
       <c r="H149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="I149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5254,6 +5704,9 @@
       <c r="H150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5286,6 +5739,9 @@
       <c r="H151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="I151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5318,6 +5774,9 @@
       <c r="H152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5350,6 +5809,9 @@
       <c r="H153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5382,6 +5844,9 @@
       <c r="H154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="I154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5414,6 +5879,9 @@
       <c r="H155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5446,6 +5914,9 @@
       <c r="H156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5478,6 +5949,9 @@
       <c r="H157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5510,6 +5984,9 @@
       <c r="H158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5542,6 +6019,9 @@
       <c r="H159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="I159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5574,6 +6054,9 @@
       <c r="H160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5606,6 +6089,9 @@
       <c r="H161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5638,6 +6124,9 @@
       <c r="H162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="I162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5670,6 +6159,9 @@
       <c r="H163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="I163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5702,9 +6194,12 @@
       <c r="H164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="I164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H164"/>
+  <autoFilter ref="A1:I164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,6 +493,11 @@
           <t>2026-09-07 16:09</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 19:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +533,9 @@
       <c r="I2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="J2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +571,9 @@
       <c r="I3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="J3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +609,9 @@
       <c r="I4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,6 +647,9 @@
       <c r="I5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +685,9 @@
       <c r="I6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +723,9 @@
       <c r="I7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="J7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +761,9 @@
       <c r="I8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="J8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +799,9 @@
       <c r="I9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="J9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -807,6 +837,9 @@
       <c r="I10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="J10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,6 +875,9 @@
       <c r="I11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="J11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -877,6 +913,9 @@
       <c r="I12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -912,6 +951,9 @@
       <c r="I13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="J13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -947,6 +989,9 @@
       <c r="I14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -982,6 +1027,9 @@
       <c r="I15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1017,6 +1065,9 @@
       <c r="I16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,6 +1103,9 @@
       <c r="I17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="J17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1087,6 +1141,9 @@
       <c r="I18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1122,6 +1179,9 @@
       <c r="I19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="J19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1157,6 +1217,9 @@
       <c r="I20" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J20" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1192,6 +1255,9 @@
       <c r="I21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="J21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1227,6 +1293,9 @@
       <c r="I22" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J22" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1262,6 +1331,9 @@
       <c r="I23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1297,6 +1369,9 @@
       <c r="I24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1332,6 +1407,9 @@
       <c r="I25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1367,6 +1445,9 @@
       <c r="I26" s="2" t="n">
         <v>20.5</v>
       </c>
+      <c r="J26" s="2" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1402,6 +1483,9 @@
       <c r="I27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1437,6 +1521,9 @@
       <c r="I28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="J28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1472,6 +1559,9 @@
       <c r="I29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="J29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1597,9 @@
       <c r="I30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1542,6 +1635,9 @@
       <c r="I31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1577,6 +1673,9 @@
       <c r="I32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1612,6 +1711,9 @@
       <c r="I33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1647,6 +1749,9 @@
       <c r="I34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="J34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1682,6 +1787,9 @@
       <c r="I35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1717,6 +1825,9 @@
       <c r="I36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1752,6 +1863,9 @@
       <c r="I37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1787,6 +1901,9 @@
       <c r="I38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1822,6 +1939,9 @@
       <c r="I39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J39" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1857,6 +1977,9 @@
       <c r="I40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1892,6 +2015,9 @@
       <c r="I41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,6 +2053,9 @@
       <c r="I42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1962,6 +2091,9 @@
       <c r="I43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1997,6 +2129,9 @@
       <c r="I44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2032,6 +2167,9 @@
       <c r="I45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2067,6 +2205,9 @@
       <c r="I46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="J46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2102,6 +2243,9 @@
       <c r="I47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2137,6 +2281,9 @@
       <c r="I48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2172,6 +2319,9 @@
       <c r="I49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2207,6 +2357,9 @@
       <c r="I50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2242,6 +2395,9 @@
       <c r="I51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="J51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2277,6 +2433,9 @@
       <c r="I52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="J52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2312,6 +2471,9 @@
       <c r="I53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2347,6 +2509,9 @@
       <c r="I54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2382,6 +2547,9 @@
       <c r="I55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2417,6 +2585,9 @@
       <c r="I56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2452,6 +2623,9 @@
       <c r="I57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2487,6 +2661,9 @@
       <c r="I58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2522,6 +2699,9 @@
       <c r="I59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="J59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2557,6 +2737,9 @@
       <c r="I60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2592,6 +2775,9 @@
       <c r="I61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2627,6 +2813,9 @@
       <c r="I62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +2851,9 @@
       <c r="I63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2697,6 +2889,9 @@
       <c r="I64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2732,6 +2927,9 @@
       <c r="I65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2767,6 +2965,9 @@
       <c r="I66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2802,6 +3003,9 @@
       <c r="I67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2837,6 +3041,9 @@
       <c r="I68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2872,6 +3079,9 @@
       <c r="I69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2907,6 +3117,9 @@
       <c r="I70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2942,6 +3155,9 @@
       <c r="I71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2977,6 +3193,9 @@
       <c r="I72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3012,6 +3231,9 @@
       <c r="I73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3047,6 +3269,9 @@
       <c r="I74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3082,6 +3307,9 @@
       <c r="I75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3117,6 +3345,9 @@
       <c r="I76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3152,6 +3383,9 @@
       <c r="I77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3187,6 +3421,9 @@
       <c r="I78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3222,6 +3459,9 @@
       <c r="I79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3257,6 +3497,9 @@
       <c r="I80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3292,6 +3535,9 @@
       <c r="I81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3327,6 +3573,9 @@
       <c r="I82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3362,6 +3611,9 @@
       <c r="I83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3397,6 +3649,9 @@
       <c r="I84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3432,6 +3687,9 @@
       <c r="I85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3467,6 +3725,9 @@
       <c r="I86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3502,6 +3763,9 @@
       <c r="I87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3537,6 +3801,9 @@
       <c r="I88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3572,6 +3839,9 @@
       <c r="I89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3607,6 +3877,9 @@
       <c r="I90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3642,6 +3915,9 @@
       <c r="I91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3677,6 +3953,9 @@
       <c r="I92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3712,6 +3991,9 @@
       <c r="I93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3747,6 +4029,9 @@
       <c r="I94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3782,6 +4067,9 @@
       <c r="I95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3817,6 +4105,9 @@
       <c r="I96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3852,6 +4143,9 @@
       <c r="I97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3887,6 +4181,9 @@
       <c r="I98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3922,6 +4219,9 @@
       <c r="I99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3957,6 +4257,9 @@
       <c r="I100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3992,6 +4295,9 @@
       <c r="I101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4027,6 +4333,9 @@
       <c r="I102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4062,6 +4371,9 @@
       <c r="I103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4097,6 +4409,9 @@
       <c r="I104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4132,6 +4447,9 @@
       <c r="I105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4167,6 +4485,9 @@
       <c r="I106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4202,6 +4523,9 @@
       <c r="I107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="J107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4237,6 +4561,9 @@
       <c r="I108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4272,6 +4599,9 @@
       <c r="I109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4307,6 +4637,9 @@
       <c r="I110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4342,6 +4675,9 @@
       <c r="I111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4377,6 +4713,9 @@
       <c r="I112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4412,6 +4751,9 @@
       <c r="I113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4447,6 +4789,9 @@
       <c r="I114" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4482,6 +4827,9 @@
       <c r="I115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4517,6 +4865,9 @@
       <c r="I116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4552,6 +4903,9 @@
       <c r="I117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4587,6 +4941,9 @@
       <c r="I118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4622,6 +4979,9 @@
       <c r="I119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4657,6 +5017,9 @@
       <c r="I120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4692,6 +5055,9 @@
       <c r="I121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4727,6 +5093,9 @@
       <c r="I122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4762,6 +5131,9 @@
       <c r="I123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4797,6 +5169,9 @@
       <c r="I124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4832,6 +5207,9 @@
       <c r="I125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4867,6 +5245,9 @@
       <c r="I126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4902,6 +5283,9 @@
       <c r="I127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4937,6 +5321,9 @@
       <c r="I128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4972,6 +5359,9 @@
       <c r="I129" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J129" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5007,6 +5397,9 @@
       <c r="I130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5042,6 +5435,9 @@
       <c r="I131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5077,6 +5473,9 @@
       <c r="I132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="J132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5112,6 +5511,9 @@
       <c r="I133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5147,6 +5549,9 @@
       <c r="I134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5182,6 +5587,9 @@
       <c r="I135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5217,6 +5625,9 @@
       <c r="I136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5252,6 +5663,9 @@
       <c r="I137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5287,6 +5701,9 @@
       <c r="I138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5322,6 +5739,9 @@
       <c r="I139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5357,6 +5777,9 @@
       <c r="I140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5392,6 +5815,9 @@
       <c r="I141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5427,6 +5853,9 @@
       <c r="I142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5462,6 +5891,9 @@
       <c r="I143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5497,6 +5929,9 @@
       <c r="I144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5532,6 +5967,9 @@
       <c r="I145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="J145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5567,6 +6005,9 @@
       <c r="I146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5602,6 +6043,9 @@
       <c r="I147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5637,6 +6081,9 @@
       <c r="I148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5672,6 +6119,9 @@
       <c r="I149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="J149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5707,6 +6157,9 @@
       <c r="I150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5742,6 +6195,9 @@
       <c r="I151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="J151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5777,6 +6233,9 @@
       <c r="I152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5812,6 +6271,9 @@
       <c r="I153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5847,6 +6309,9 @@
       <c r="I154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="J154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5882,6 +6347,9 @@
       <c r="I155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5917,6 +6385,9 @@
       <c r="I156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5952,6 +6423,9 @@
       <c r="I157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5987,6 +6461,9 @@
       <c r="I158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6022,6 +6499,9 @@
       <c r="I159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6057,6 +6537,9 @@
       <c r="I160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6092,6 +6575,9 @@
       <c r="I161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6127,6 +6613,9 @@
       <c r="I162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="J162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6162,6 +6651,9 @@
       <c r="I163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="J163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6197,9 +6689,12 @@
       <c r="I164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="J164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I164"/>
+  <autoFilter ref="A1:J164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +499,11 @@
           <t>2026-09-07 19:15</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,6 +542,9 @@
       <c r="J2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="K2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,6 +583,9 @@
       <c r="J3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="K3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,6 +624,9 @@
       <c r="J4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="K4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +665,9 @@
       <c r="J5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,6 +706,9 @@
       <c r="J6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,6 +747,9 @@
       <c r="J7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="K7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,6 +788,9 @@
       <c r="J8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="K8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -802,6 +829,9 @@
       <c r="J9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="K9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -840,6 +870,9 @@
       <c r="J10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="K10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,6 +911,9 @@
       <c r="J11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="K11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -916,6 +952,9 @@
       <c r="J12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -954,6 +993,9 @@
       <c r="J13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="K13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -992,6 +1034,9 @@
       <c r="J14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1030,6 +1075,9 @@
       <c r="J15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1068,6 +1116,9 @@
       <c r="J16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1106,6 +1157,9 @@
       <c r="J17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="K17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1144,6 +1198,9 @@
       <c r="J18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1182,6 +1239,9 @@
       <c r="J19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="K19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1220,6 +1280,9 @@
       <c r="J20" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K20" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1258,6 +1321,9 @@
       <c r="J21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="K21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1296,6 +1362,9 @@
       <c r="J22" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="K22" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1334,6 +1403,9 @@
       <c r="J23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1372,6 +1444,9 @@
       <c r="J24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1410,6 +1485,9 @@
       <c r="J25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1448,6 +1526,9 @@
       <c r="J26" s="2" t="n">
         <v>20.5</v>
       </c>
+      <c r="K26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1486,6 +1567,9 @@
       <c r="J27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1524,6 +1608,9 @@
       <c r="J28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="K28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1562,6 +1649,9 @@
       <c r="J29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="K29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1600,6 +1690,9 @@
       <c r="J30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1638,6 +1731,9 @@
       <c r="J31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1676,6 +1772,9 @@
       <c r="J32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1714,6 +1813,9 @@
       <c r="J33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1752,6 +1854,9 @@
       <c r="J34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="K34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1790,6 +1895,9 @@
       <c r="J35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1828,6 +1936,9 @@
       <c r="J36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1866,6 +1977,9 @@
       <c r="J37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1904,6 +2018,9 @@
       <c r="J38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1942,6 +2059,9 @@
       <c r="J39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K39" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1980,6 +2100,9 @@
       <c r="J40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2018,6 +2141,9 @@
       <c r="J41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2056,6 +2182,9 @@
       <c r="J42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2094,6 +2223,9 @@
       <c r="J43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2132,6 +2264,9 @@
       <c r="J44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2170,6 +2305,9 @@
       <c r="J45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2208,6 +2346,9 @@
       <c r="J46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="K46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2246,6 +2387,9 @@
       <c r="J47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2284,6 +2428,9 @@
       <c r="J48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2322,6 +2469,9 @@
       <c r="J49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2360,6 +2510,9 @@
       <c r="J50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2398,6 +2551,9 @@
       <c r="J51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="K51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2436,6 +2592,9 @@
       <c r="J52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="K52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2474,6 +2633,9 @@
       <c r="J53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2512,6 +2674,9 @@
       <c r="J54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="K54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2550,6 +2715,9 @@
       <c r="J55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2588,6 +2756,9 @@
       <c r="J56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2626,6 +2797,9 @@
       <c r="J57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2664,6 +2838,9 @@
       <c r="J58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2702,6 +2879,9 @@
       <c r="J59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="K59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2740,6 +2920,9 @@
       <c r="J60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2778,6 +2961,9 @@
       <c r="J61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2816,6 +3002,9 @@
       <c r="J62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2854,6 +3043,9 @@
       <c r="J63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2892,6 +3084,9 @@
       <c r="J64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2930,6 +3125,9 @@
       <c r="J65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2968,6 +3166,9 @@
       <c r="J66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3006,6 +3207,9 @@
       <c r="J67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3044,6 +3248,9 @@
       <c r="J68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3082,6 +3289,9 @@
       <c r="J69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3120,6 +3330,9 @@
       <c r="J70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3158,6 +3371,9 @@
       <c r="J71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3196,6 +3412,9 @@
       <c r="J72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3234,6 +3453,9 @@
       <c r="J73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3272,6 +3494,9 @@
       <c r="J74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3310,6 +3535,9 @@
       <c r="J75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3348,6 +3576,9 @@
       <c r="J76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3386,6 +3617,9 @@
       <c r="J77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3424,6 +3658,9 @@
       <c r="J78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3462,6 +3699,9 @@
       <c r="J79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3500,6 +3740,9 @@
       <c r="J80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3538,6 +3781,9 @@
       <c r="J81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3576,6 +3822,9 @@
       <c r="J82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3614,6 +3863,9 @@
       <c r="J83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3652,6 +3904,9 @@
       <c r="J84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3690,6 +3945,9 @@
       <c r="J85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3728,6 +3986,9 @@
       <c r="J86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3766,6 +4027,9 @@
       <c r="J87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3804,6 +4068,9 @@
       <c r="J88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3842,6 +4109,9 @@
       <c r="J89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3880,6 +4150,9 @@
       <c r="J90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3918,6 +4191,9 @@
       <c r="J91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3956,6 +4232,9 @@
       <c r="J92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3994,6 +4273,9 @@
       <c r="J93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="K93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4032,6 +4314,9 @@
       <c r="J94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4070,6 +4355,9 @@
       <c r="J95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4108,6 +4396,9 @@
       <c r="J96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4146,6 +4437,9 @@
       <c r="J97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4184,6 +4478,9 @@
       <c r="J98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4222,6 +4519,9 @@
       <c r="J99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4260,6 +4560,9 @@
       <c r="J100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4298,6 +4601,9 @@
       <c r="J101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4336,6 +4642,9 @@
       <c r="J102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4374,6 +4683,9 @@
       <c r="J103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4412,6 +4724,9 @@
       <c r="J104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4450,6 +4765,9 @@
       <c r="J105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4488,6 +4806,9 @@
       <c r="J106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4526,6 +4847,9 @@
       <c r="J107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="K107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4564,6 +4888,9 @@
       <c r="J108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4602,6 +4929,9 @@
       <c r="J109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4640,6 +4970,9 @@
       <c r="J110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4678,6 +5011,9 @@
       <c r="J111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4716,6 +5052,9 @@
       <c r="J112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4754,6 +5093,9 @@
       <c r="J113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4792,6 +5134,9 @@
       <c r="J114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4830,6 +5175,9 @@
       <c r="J115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4868,6 +5216,9 @@
       <c r="J116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4906,6 +5257,9 @@
       <c r="J117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4944,6 +5298,9 @@
       <c r="J118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4982,6 +5339,9 @@
       <c r="J119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5020,6 +5380,9 @@
       <c r="J120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5058,6 +5421,9 @@
       <c r="J121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5096,6 +5462,9 @@
       <c r="J122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5134,6 +5503,9 @@
       <c r="J123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5172,6 +5544,9 @@
       <c r="J124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5210,6 +5585,9 @@
       <c r="J125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5248,6 +5626,9 @@
       <c r="J126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5286,6 +5667,9 @@
       <c r="J127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5324,6 +5708,9 @@
       <c r="J128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5362,6 +5749,9 @@
       <c r="J129" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K129" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5400,6 +5790,9 @@
       <c r="J130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5438,6 +5831,9 @@
       <c r="J131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5476,6 +5872,9 @@
       <c r="J132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="K132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5514,6 +5913,9 @@
       <c r="J133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="K133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5552,6 +5954,9 @@
       <c r="J134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="K134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5590,6 +5995,9 @@
       <c r="J135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5628,6 +6036,9 @@
       <c r="J136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5666,6 +6077,9 @@
       <c r="J137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5704,6 +6118,9 @@
       <c r="J138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="K138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5742,6 +6159,9 @@
       <c r="J139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5780,6 +6200,9 @@
       <c r="J140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5818,6 +6241,9 @@
       <c r="J141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5856,6 +6282,9 @@
       <c r="J142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5894,6 +6323,9 @@
       <c r="J143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5932,6 +6364,9 @@
       <c r="J144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5970,6 +6405,9 @@
       <c r="J145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="K145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6008,6 +6446,9 @@
       <c r="J146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6046,6 +6487,9 @@
       <c r="J147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6084,6 +6528,9 @@
       <c r="J148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="K148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6122,6 +6569,9 @@
       <c r="J149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="K149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6160,6 +6610,9 @@
       <c r="J150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="K150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6198,6 +6651,9 @@
       <c r="J151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="K151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6236,6 +6692,9 @@
       <c r="J152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6274,6 +6733,9 @@
       <c r="J153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6312,6 +6774,9 @@
       <c r="J154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="K154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6350,6 +6815,9 @@
       <c r="J155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="K155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6388,6 +6856,9 @@
       <c r="J156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6426,6 +6897,9 @@
       <c r="J157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6464,6 +6938,9 @@
       <c r="J158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6502,6 +6979,9 @@
       <c r="J159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="K159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6540,6 +7020,9 @@
       <c r="J160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6578,6 +7061,9 @@
       <c r="J161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6616,6 +7102,9 @@
       <c r="J162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="K162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6654,6 +7143,9 @@
       <c r="J163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="K163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6692,9 +7184,12 @@
       <c r="J164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="K164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J164"/>
+  <autoFilter ref="A1:K164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,42 +459,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07 01:13</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-07 04:10</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-07 04:49</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-07 10:09</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-07 13:11</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-07 16:09</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-07 19:15</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-07 22:09</t>
+          <t>2026-09-08 01:12</t>
         </is>
       </c>
     </row>
@@ -524,27 +482,6 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>13.45</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,27 +502,6 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -606,27 +522,6 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>17.95</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,27 +542,6 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,27 +562,6 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -729,27 +582,6 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>19.49</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -768,27 +600,6 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="K8" s="2" t="n">
         <v>20.19</v>
       </c>
     </row>
@@ -811,27 +622,6 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -852,27 +642,6 @@
       <c r="D10" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>20.1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -893,27 +662,6 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>20.19</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,27 +682,6 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,27 +702,6 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>20.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1016,27 +722,6 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1057,27 +742,6 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,27 +762,6 @@
       <c r="D16" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1137,27 +780,6 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="K17" s="2" t="n">
         <v>20.75</v>
       </c>
     </row>
@@ -1180,27 +802,6 @@
       <c r="D18" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1221,27 +822,6 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>20.77</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1260,27 +840,6 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K20" s="2" t="n">
         <v>20.39</v>
       </c>
     </row>
@@ -1303,27 +862,6 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>20.48</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1342,27 +880,6 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="K22" s="2" t="n">
         <v>21.89</v>
       </c>
     </row>
@@ -1385,27 +902,6 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1426,27 +922,6 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1467,27 +942,6 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1506,27 +960,6 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="K26" s="2" t="n">
         <v>20.8</v>
       </c>
     </row>
@@ -1549,27 +982,6 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1590,27 +1002,6 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>20.54</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1629,27 +1020,6 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="K29" s="2" t="n">
         <v>20.75</v>
       </c>
     </row>
@@ -1672,27 +1042,6 @@
       <c r="D30" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1713,27 +1062,6 @@
       <c r="D31" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1754,27 +1082,6 @@
       <c r="D32" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1795,27 +1102,6 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1834,27 +1120,6 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="K34" s="2" t="n">
         <v>20.77</v>
       </c>
     </row>
@@ -1875,27 +1140,6 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K35" s="2" t="n">
         <v>20.39</v>
       </c>
     </row>
@@ -1918,27 +1162,6 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1959,27 +1182,6 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2000,27 +1202,6 @@
       <c r="D38" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2041,27 +1222,6 @@
       <c r="D39" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2082,27 +1242,6 @@
       <c r="D40" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2123,27 +1262,6 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2164,27 +1282,6 @@
       <c r="D42" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2205,27 +1302,6 @@
       <c r="D43" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2246,27 +1322,6 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2287,27 +1342,6 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2328,27 +1362,6 @@
       <c r="D46" s="2" t="n">
         <v>21.05</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>21.05</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2369,27 +1382,6 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2410,27 +1402,6 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2451,27 +1422,6 @@
       <c r="D49" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2490,27 +1440,6 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K50" s="2" t="n">
         <v>21.8</v>
       </c>
     </row>
@@ -2533,27 +1462,6 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>20.85</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2574,27 +1482,6 @@
       <c r="D52" s="2" t="n">
         <v>20.85</v>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>20.85</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2615,27 +1502,6 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2656,27 +1522,6 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>21.79</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2697,27 +1542,6 @@
       <c r="D55" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2738,27 +1562,6 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2779,27 +1582,6 @@
       <c r="D57" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2820,27 +1602,6 @@
       <c r="D58" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2859,27 +1620,6 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K59" s="2" t="n">
         <v>22.2</v>
       </c>
     </row>
@@ -2902,27 +1642,6 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2943,27 +1662,6 @@
       <c r="D61" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2984,27 +1682,6 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3025,27 +1702,6 @@
       <c r="D63" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3066,27 +1722,6 @@
       <c r="D64" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3107,27 +1742,6 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K65" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3148,27 +1762,6 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3189,27 +1782,6 @@
       <c r="D67" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3230,27 +1802,6 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3271,27 +1822,6 @@
       <c r="D69" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3312,27 +1842,6 @@
       <c r="D70" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3353,27 +1862,6 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K71" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3394,27 +1882,6 @@
       <c r="D72" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3435,27 +1902,6 @@
       <c r="D73" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3476,27 +1922,6 @@
       <c r="D74" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3517,27 +1942,6 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3558,27 +1962,6 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3599,27 +1982,6 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3640,27 +2002,6 @@
       <c r="D78" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3681,27 +2022,6 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3722,27 +2042,6 @@
       <c r="D80" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3763,27 +2062,6 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3804,27 +2082,6 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3845,27 +2102,6 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3886,27 +2122,6 @@
       <c r="D84" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3927,27 +2142,6 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3968,27 +2162,6 @@
       <c r="D86" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4009,27 +2182,6 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4050,27 +2202,6 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4091,27 +2222,6 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4132,27 +2242,6 @@
       <c r="D90" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4173,27 +2262,6 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4214,27 +2282,6 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4255,27 +2302,6 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
-      <c r="E93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>21.89</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4294,27 +2320,6 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K94" s="2" t="n">
         <v>21.39</v>
       </c>
     </row>
@@ -4337,27 +2342,6 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4378,27 +2362,6 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4417,27 +2380,6 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K97" s="2" t="n">
         <v>21.5</v>
       </c>
     </row>
@@ -4460,27 +2402,6 @@
       <c r="D98" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4501,27 +2422,6 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4542,27 +2442,6 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4583,27 +2462,6 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4624,27 +2482,6 @@
       <c r="D102" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4665,27 +2502,6 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4706,27 +2522,6 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4747,27 +2542,6 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4788,27 +2562,6 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4829,27 +2582,6 @@
       <c r="D107" s="2" t="n">
         <v>21.29</v>
       </c>
-      <c r="E107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>21.29</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4870,27 +2602,6 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4911,27 +2622,6 @@
       <c r="D109" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4952,27 +2642,6 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4993,27 +2662,6 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5034,27 +2682,6 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5073,27 +2700,6 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K113" s="2" t="n">
         <v>22.3</v>
       </c>
     </row>
@@ -5114,27 +2720,6 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K114" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -5157,27 +2742,6 @@
       <c r="D115" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5198,27 +2762,6 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5239,27 +2782,6 @@
       <c r="D117" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5280,27 +2802,6 @@
       <c r="D118" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5321,27 +2822,6 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5362,27 +2842,6 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5403,27 +2862,6 @@
       <c r="D121" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5444,27 +2882,6 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5485,27 +2902,6 @@
       <c r="D123" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5526,27 +2922,6 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5567,27 +2942,6 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5608,27 +2962,6 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5649,27 +2982,6 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5690,27 +3002,6 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5731,27 +3022,6 @@
       <c r="D129" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5772,27 +3042,6 @@
       <c r="D130" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5813,27 +3062,6 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5854,27 +3082,6 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="E132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>21.6</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5895,27 +3102,6 @@
       <c r="D133" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="E133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>21.7</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5936,27 +3122,6 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="E134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>21.7</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5977,27 +3142,6 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6018,27 +3162,6 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6059,27 +3182,6 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6100,27 +3202,6 @@
       <c r="D138" s="2" t="n">
         <v>21.89</v>
       </c>
-      <c r="E138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="K138" s="2" t="n">
-        <v>21.89</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6141,27 +3222,6 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K139" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6182,27 +3242,6 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6223,27 +3262,6 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6264,27 +3282,6 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6305,27 +3302,6 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6346,27 +3322,6 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6387,27 +3342,6 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
-      <c r="E145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>22.29</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6428,27 +3362,6 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6469,27 +3382,6 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K147" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6510,27 +3402,6 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
-      <c r="E148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="K148" s="2" t="n">
-        <v>22.35</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6551,27 +3422,6 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
-      <c r="E149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="K149" s="2" t="n">
-        <v>22.49</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6592,27 +3442,6 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K150" s="2" t="n">
-        <v>22.5</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6633,27 +3462,6 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
-      <c r="E151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="K151" s="2" t="n">
-        <v>22.59</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6674,27 +3482,6 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6715,27 +3502,6 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6756,27 +3522,6 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>22.7</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6797,27 +3542,6 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>22.79</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6838,27 +3562,6 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6879,27 +3582,6 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K157" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6920,27 +3602,6 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K158" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6961,27 +3622,6 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
-      <c r="E159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="K159" s="2" t="n">
-        <v>23.99</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7002,27 +3642,6 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K160" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7043,27 +3662,6 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K161" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7084,27 +3682,6 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
-      <c r="E162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="K162" s="2" t="n">
-        <v>23.49</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7125,27 +3702,6 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K163" s="2" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7166,30 +3722,9 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="K164" s="2" t="n">
-        <v>24.25</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K164"/>
+  <autoFilter ref="A1:D164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,13 +432,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:E164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,6 +463,11 @@
           <t>2026-09-08 01:12</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,6 +488,9 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,6 +511,9 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -522,6 +534,9 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +557,9 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,6 +580,9 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -582,6 +603,9 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,6 +626,9 @@
       <c r="D8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="E8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +649,9 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,6 +672,9 @@
       <c r="D10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -662,6 +695,9 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,6 +718,9 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -702,6 +741,9 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,6 +764,9 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,6 +787,9 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -762,6 +810,9 @@
       <c r="D16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,6 +833,9 @@
       <c r="D17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="E17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -802,6 +856,9 @@
       <c r="D18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -822,6 +879,9 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,6 +902,9 @@
       <c r="D20" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,6 +925,9 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -882,6 +948,9 @@
       <c r="D22" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -902,6 +971,9 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -922,6 +994,9 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -942,6 +1017,9 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -962,6 +1040,9 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="E26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -982,6 +1063,9 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1002,6 +1086,9 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1022,6 +1109,9 @@
       <c r="D29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="E29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1042,6 +1132,9 @@
       <c r="D30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1062,6 +1155,9 @@
       <c r="D31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1082,6 +1178,9 @@
       <c r="D32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1102,6 +1201,9 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1122,6 +1224,9 @@
       <c r="D34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="E34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1142,6 +1247,9 @@
       <c r="D35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1162,6 +1270,9 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1182,6 +1293,9 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1202,6 +1316,9 @@
       <c r="D38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1222,6 +1339,9 @@
       <c r="D39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E39" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1242,6 +1362,9 @@
       <c r="D40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1262,6 +1385,9 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1282,6 +1408,9 @@
       <c r="D42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1302,6 +1431,9 @@
       <c r="D43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1322,6 +1454,9 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1342,6 +1477,9 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1362,6 +1500,9 @@
       <c r="D46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="E46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1382,6 +1523,9 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1402,6 +1546,9 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1422,6 +1569,9 @@
       <c r="D49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1442,6 +1592,9 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1462,6 +1615,9 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="E51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1482,6 +1638,9 @@
       <c r="D52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="E52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1502,6 +1661,9 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1522,6 +1684,9 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1542,6 +1707,9 @@
       <c r="D55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1562,6 +1730,9 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1582,6 +1753,9 @@
       <c r="D57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1602,6 +1776,9 @@
       <c r="D58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1622,6 +1799,9 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="E59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1642,6 +1822,9 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1662,6 +1845,9 @@
       <c r="D61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1682,6 +1868,9 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1702,6 +1891,9 @@
       <c r="D63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1722,6 +1914,9 @@
       <c r="D64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1742,6 +1937,9 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1762,6 +1960,9 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1782,6 +1983,9 @@
       <c r="D67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1802,6 +2006,9 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1822,6 +2029,9 @@
       <c r="D69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1842,6 +2052,9 @@
       <c r="D70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1862,6 +2075,9 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1882,6 +2098,9 @@
       <c r="D72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1902,6 +2121,9 @@
       <c r="D73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1922,6 +2144,9 @@
       <c r="D74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1942,6 +2167,9 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1962,6 +2190,9 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1982,6 +2213,9 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2002,6 +2236,9 @@
       <c r="D78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2022,6 +2259,9 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2042,6 +2282,9 @@
       <c r="D80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2062,6 +2305,9 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2082,6 +2328,9 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2102,6 +2351,9 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2122,6 +2374,9 @@
       <c r="D84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2142,6 +2397,9 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2162,6 +2420,9 @@
       <c r="D86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2182,6 +2443,9 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2202,6 +2466,9 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2222,6 +2489,9 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2242,6 +2512,9 @@
       <c r="D90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2262,6 +2535,9 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2282,6 +2558,9 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2302,6 +2581,9 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="E93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2322,6 +2604,9 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2342,6 +2627,9 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2362,6 +2650,9 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2382,6 +2673,9 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2402,6 +2696,9 @@
       <c r="D98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2422,6 +2719,9 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2442,6 +2742,9 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2462,6 +2765,9 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2482,6 +2788,9 @@
       <c r="D102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2502,6 +2811,9 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2522,6 +2834,9 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2542,6 +2857,9 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2562,6 +2880,9 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2582,6 +2903,9 @@
       <c r="D107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="E107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2602,6 +2926,9 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2622,6 +2949,9 @@
       <c r="D109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2642,6 +2972,9 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2662,6 +2995,9 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2682,6 +3018,9 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2702,6 +3041,9 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2722,6 +3064,9 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2742,6 +3087,9 @@
       <c r="D115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2762,6 +3110,9 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2782,6 +3133,9 @@
       <c r="D117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2802,6 +3156,9 @@
       <c r="D118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2822,6 +3179,9 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2842,6 +3202,9 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2862,6 +3225,9 @@
       <c r="D121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2882,6 +3248,9 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2902,6 +3271,9 @@
       <c r="D123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2922,6 +3294,9 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2942,6 +3317,9 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2962,6 +3340,9 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2982,6 +3363,9 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3002,6 +3386,9 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3022,6 +3409,9 @@
       <c r="D129" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E129" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3042,6 +3432,9 @@
       <c r="D130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3062,6 +3455,9 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3082,6 +3478,9 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="E132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3102,6 +3501,9 @@
       <c r="D133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="E133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3122,6 +3524,9 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="E134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3142,6 +3547,9 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3162,6 +3570,9 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3182,6 +3593,9 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3202,6 +3616,9 @@
       <c r="D138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="E138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3222,6 +3639,9 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3242,6 +3662,9 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3262,6 +3685,9 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3282,6 +3708,9 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3302,6 +3731,9 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3322,6 +3754,9 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3342,6 +3777,9 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="E145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3362,6 +3800,9 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3382,6 +3823,9 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3402,6 +3846,9 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3422,6 +3869,9 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="E149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3442,6 +3892,9 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="E150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3462,6 +3915,9 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="E151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3482,6 +3938,9 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3502,6 +3961,9 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3522,6 +3984,9 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="E154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3542,6 +4007,9 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3562,6 +4030,9 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3582,6 +4053,9 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3602,6 +4076,9 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3622,6 +4099,9 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="E159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3642,6 +4122,9 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3662,6 +4145,9 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3682,6 +4168,9 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="E162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3702,6 +4191,9 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="E163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3722,9 +4214,12 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="E164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D164"/>
+  <autoFilter ref="A1:E164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,11 @@
           <t>2026-09-08 04:10</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 07:13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +497,9 @@
       <c r="E2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,6 +523,9 @@
       <c r="E3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="F3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +549,9 @@
       <c r="E4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,6 +575,9 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +601,9 @@
       <c r="E6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -606,6 +627,9 @@
       <c r="E7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="F7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -629,6 +653,9 @@
       <c r="E8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -652,6 +679,9 @@
       <c r="E9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="F9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -675,6 +705,9 @@
       <c r="E10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="F10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +731,9 @@
       <c r="E11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="F11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -721,6 +757,9 @@
       <c r="E12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,6 +783,9 @@
       <c r="E13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="F13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -767,6 +809,9 @@
       <c r="E14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -790,6 +835,9 @@
       <c r="E15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -813,6 +861,9 @@
       <c r="E16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -836,6 +887,9 @@
       <c r="E17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="F17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -859,6 +913,9 @@
       <c r="E18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -882,6 +939,9 @@
       <c r="E19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="F19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -905,6 +965,9 @@
       <c r="E20" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F20" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -928,6 +991,9 @@
       <c r="E21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="F21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -951,6 +1017,9 @@
       <c r="E22" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="F22" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -974,6 +1043,9 @@
       <c r="E23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -997,6 +1069,9 @@
       <c r="E24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1020,6 +1095,9 @@
       <c r="E25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1043,6 +1121,9 @@
       <c r="E26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="F26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1066,6 +1147,9 @@
       <c r="E27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1089,6 +1173,9 @@
       <c r="E28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="F28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1112,6 +1199,9 @@
       <c r="E29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="F29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1135,6 +1225,9 @@
       <c r="E30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1158,6 +1251,9 @@
       <c r="E31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1181,6 +1277,9 @@
       <c r="E32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1204,6 +1303,9 @@
       <c r="E33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1227,6 +1329,9 @@
       <c r="E34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="F34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1250,6 +1355,9 @@
       <c r="E35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1273,6 +1381,9 @@
       <c r="E36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1296,6 +1407,9 @@
       <c r="E37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1319,6 +1433,9 @@
       <c r="E38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1342,6 +1459,9 @@
       <c r="E39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F39" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1365,6 +1485,9 @@
       <c r="E40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1388,6 +1511,9 @@
       <c r="E41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1411,6 +1537,9 @@
       <c r="E42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1434,6 +1563,9 @@
       <c r="E43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1457,6 +1589,9 @@
       <c r="E44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1480,6 +1615,9 @@
       <c r="E45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1503,6 +1641,9 @@
       <c r="E46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="F46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1526,6 +1667,9 @@
       <c r="E47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1549,6 +1693,9 @@
       <c r="E48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1572,6 +1719,9 @@
       <c r="E49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1595,6 +1745,9 @@
       <c r="E50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1618,6 +1771,9 @@
       <c r="E51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="F51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1641,6 +1797,9 @@
       <c r="E52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="F52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1664,6 +1823,9 @@
       <c r="E53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1687,6 +1849,9 @@
       <c r="E54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1710,6 +1875,9 @@
       <c r="E55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1733,6 +1901,9 @@
       <c r="E56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1756,6 +1927,9 @@
       <c r="E57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1779,6 +1953,9 @@
       <c r="E58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1802,6 +1979,9 @@
       <c r="E59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="F59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1825,6 +2005,9 @@
       <c r="E60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1848,6 +2031,9 @@
       <c r="E61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1871,6 +2057,9 @@
       <c r="E62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1894,6 +2083,9 @@
       <c r="E63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1917,6 +2109,9 @@
       <c r="E64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1940,6 +2135,9 @@
       <c r="E65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1963,6 +2161,9 @@
       <c r="E66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1986,6 +2187,9 @@
       <c r="E67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2009,6 +2213,9 @@
       <c r="E68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2032,6 +2239,9 @@
       <c r="E69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2055,6 +2265,9 @@
       <c r="E70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2078,6 +2291,9 @@
       <c r="E71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2101,6 +2317,9 @@
       <c r="E72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2124,6 +2343,9 @@
       <c r="E73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2147,6 +2369,9 @@
       <c r="E74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2170,6 +2395,9 @@
       <c r="E75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2193,6 +2421,9 @@
       <c r="E76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2216,6 +2447,9 @@
       <c r="E77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2239,6 +2473,9 @@
       <c r="E78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2262,6 +2499,9 @@
       <c r="E79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2285,6 +2525,9 @@
       <c r="E80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2308,6 +2551,9 @@
       <c r="E81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2331,6 +2577,9 @@
       <c r="E82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2354,6 +2603,9 @@
       <c r="E83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2377,6 +2629,9 @@
       <c r="E84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2400,6 +2655,9 @@
       <c r="E85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2423,6 +2681,9 @@
       <c r="E86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2446,6 +2707,9 @@
       <c r="E87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2469,6 +2733,9 @@
       <c r="E88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2492,6 +2759,9 @@
       <c r="E89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2515,6 +2785,9 @@
       <c r="E90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2538,6 +2811,9 @@
       <c r="E91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2561,6 +2837,9 @@
       <c r="E92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2584,6 +2863,9 @@
       <c r="E93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="F93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2607,6 +2889,9 @@
       <c r="E94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2630,6 +2915,9 @@
       <c r="E95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2653,6 +2941,9 @@
       <c r="E96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2676,6 +2967,9 @@
       <c r="E97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2699,6 +2993,9 @@
       <c r="E98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2722,6 +3019,9 @@
       <c r="E99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2745,6 +3045,9 @@
       <c r="E100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2768,6 +3071,9 @@
       <c r="E101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2791,6 +3097,9 @@
       <c r="E102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2814,6 +3123,9 @@
       <c r="E103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2837,6 +3149,9 @@
       <c r="E104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2860,6 +3175,9 @@
       <c r="E105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2883,6 +3201,9 @@
       <c r="E106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2906,6 +3227,9 @@
       <c r="E107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="F107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2929,6 +3253,9 @@
       <c r="E108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2952,6 +3279,9 @@
       <c r="E109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2975,6 +3305,9 @@
       <c r="E110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2998,6 +3331,9 @@
       <c r="E111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3021,6 +3357,9 @@
       <c r="E112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3044,6 +3383,9 @@
       <c r="E113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3067,6 +3409,9 @@
       <c r="E114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3090,6 +3435,9 @@
       <c r="E115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3113,6 +3461,9 @@
       <c r="E116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3136,6 +3487,9 @@
       <c r="E117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3159,6 +3513,9 @@
       <c r="E118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3182,6 +3539,9 @@
       <c r="E119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3205,6 +3565,9 @@
       <c r="E120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3228,6 +3591,9 @@
       <c r="E121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3251,6 +3617,9 @@
       <c r="E122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3274,6 +3643,9 @@
       <c r="E123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3297,6 +3669,9 @@
       <c r="E124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3320,6 +3695,9 @@
       <c r="E125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3343,6 +3721,9 @@
       <c r="E126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3366,6 +3747,9 @@
       <c r="E127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3389,6 +3773,9 @@
       <c r="E128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3412,6 +3799,9 @@
       <c r="E129" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3435,6 +3825,9 @@
       <c r="E130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3458,6 +3851,9 @@
       <c r="E131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3481,6 +3877,9 @@
       <c r="E132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="F132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3504,6 +3903,9 @@
       <c r="E133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="F133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3527,6 +3929,9 @@
       <c r="E134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="F134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3550,6 +3955,9 @@
       <c r="E135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3573,6 +3981,9 @@
       <c r="E136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3596,6 +4007,9 @@
       <c r="E137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3619,6 +4033,9 @@
       <c r="E138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="F138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3642,6 +4059,9 @@
       <c r="E139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3665,6 +4085,9 @@
       <c r="E140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3688,6 +4111,9 @@
       <c r="E141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3711,6 +4137,9 @@
       <c r="E142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3734,6 +4163,9 @@
       <c r="E143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3757,6 +4189,9 @@
       <c r="E144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3780,6 +4215,9 @@
       <c r="E145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="F145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3803,6 +4241,9 @@
       <c r="E146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3826,6 +4267,9 @@
       <c r="E147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3849,6 +4293,9 @@
       <c r="E148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3872,6 +4319,9 @@
       <c r="E149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="F149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3895,6 +4345,9 @@
       <c r="E150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="F150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3918,6 +4371,9 @@
       <c r="E151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="F151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3941,6 +4397,9 @@
       <c r="E152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3964,6 +4423,9 @@
       <c r="E153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3987,6 +4449,9 @@
       <c r="E154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="F154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4010,6 +4475,9 @@
       <c r="E155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4033,6 +4501,9 @@
       <c r="E156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4056,6 +4527,9 @@
       <c r="E157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4079,6 +4553,9 @@
       <c r="E158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4102,6 +4579,9 @@
       <c r="E159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="F159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4125,6 +4605,9 @@
       <c r="E160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4148,6 +4631,9 @@
       <c r="E161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4171,6 +4657,9 @@
       <c r="E162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="F162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4194,6 +4683,9 @@
       <c r="E163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="F163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4217,9 +4709,12 @@
       <c r="E164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="F164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E164"/>
+  <autoFilter ref="A1:F164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>2026-09-08 07:13</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,9 @@
       <c r="F2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +535,9 @@
       <c r="F3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,6 +564,9 @@
       <c r="F4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,6 +593,9 @@
       <c r="F5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,6 +622,9 @@
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +651,9 @@
       <c r="F7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,6 +680,9 @@
       <c r="F8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +709,9 @@
       <c r="F9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -708,6 +738,9 @@
       <c r="F10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -734,6 +767,9 @@
       <c r="F11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -760,6 +796,9 @@
       <c r="F12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,6 +825,9 @@
       <c r="F13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -812,6 +854,9 @@
       <c r="F14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -838,6 +883,9 @@
       <c r="F15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -864,6 +912,9 @@
       <c r="F16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,6 +941,9 @@
       <c r="F17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -916,6 +970,9 @@
       <c r="F18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -942,6 +999,9 @@
       <c r="F19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -968,6 +1028,9 @@
       <c r="F20" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -994,6 +1057,9 @@
       <c r="F21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1020,6 +1086,9 @@
       <c r="F22" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1046,6 +1115,9 @@
       <c r="F23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1072,6 +1144,9 @@
       <c r="F24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1098,6 +1173,9 @@
       <c r="F25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1124,6 +1202,9 @@
       <c r="F26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1150,6 +1231,9 @@
       <c r="F27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1176,6 +1260,9 @@
       <c r="F28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1202,6 +1289,9 @@
       <c r="F29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1228,6 +1318,9 @@
       <c r="F30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1254,6 +1347,9 @@
       <c r="F31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1280,6 +1376,9 @@
       <c r="F32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1405,9 @@
       <c r="F33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1332,6 +1434,9 @@
       <c r="F34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="G34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1358,6 +1463,9 @@
       <c r="F35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G35" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1384,6 +1492,9 @@
       <c r="F36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1410,6 +1521,9 @@
       <c r="F37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1436,6 +1550,9 @@
       <c r="F38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1462,6 +1579,9 @@
       <c r="F39" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1488,6 +1608,9 @@
       <c r="F40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1514,6 +1637,9 @@
       <c r="F41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1540,6 +1666,9 @@
       <c r="F42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1566,6 +1695,9 @@
       <c r="F43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1592,6 +1724,9 @@
       <c r="F44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1618,6 +1753,9 @@
       <c r="F45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1644,6 +1782,9 @@
       <c r="F46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="G46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1670,6 +1811,9 @@
       <c r="F47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1696,6 +1840,9 @@
       <c r="F48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1722,6 +1869,9 @@
       <c r="F49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1748,6 +1898,9 @@
       <c r="F50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1774,6 +1927,9 @@
       <c r="F51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1800,6 +1956,9 @@
       <c r="F52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1826,6 +1985,9 @@
       <c r="F53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1852,6 +2014,9 @@
       <c r="F54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1878,6 +2043,9 @@
       <c r="F55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G55" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1904,6 +2072,9 @@
       <c r="F56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1930,6 +2101,9 @@
       <c r="F57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1956,6 +2130,9 @@
       <c r="F58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1982,6 +2159,9 @@
       <c r="F59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="G59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2008,6 +2188,9 @@
       <c r="F60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2034,6 +2217,9 @@
       <c r="F61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2060,6 +2246,9 @@
       <c r="F62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2086,6 +2275,9 @@
       <c r="F63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2112,6 +2304,9 @@
       <c r="F64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2138,6 +2333,9 @@
       <c r="F65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2164,6 +2362,9 @@
       <c r="F66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2190,6 +2391,9 @@
       <c r="F67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2216,6 +2420,9 @@
       <c r="F68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2242,6 +2449,9 @@
       <c r="F69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2268,6 +2478,9 @@
       <c r="F70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2294,6 +2507,9 @@
       <c r="F71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2320,6 +2536,9 @@
       <c r="F72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2346,6 +2565,9 @@
       <c r="F73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2372,6 +2594,9 @@
       <c r="F74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2398,6 +2623,9 @@
       <c r="F75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2424,6 +2652,9 @@
       <c r="F76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2450,6 +2681,9 @@
       <c r="F77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2476,6 +2710,9 @@
       <c r="F78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2502,6 +2739,9 @@
       <c r="F79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2528,6 +2768,9 @@
       <c r="F80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2554,6 +2797,9 @@
       <c r="F81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2580,6 +2826,9 @@
       <c r="F82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2606,6 +2855,9 @@
       <c r="F83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2632,6 +2884,9 @@
       <c r="F84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2658,6 +2913,9 @@
       <c r="F85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2684,6 +2942,9 @@
       <c r="F86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2710,6 +2971,9 @@
       <c r="F87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2736,6 +3000,9 @@
       <c r="F88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2762,6 +3029,9 @@
       <c r="F89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2788,6 +3058,9 @@
       <c r="F90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2814,6 +3087,9 @@
       <c r="F91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2840,6 +3116,9 @@
       <c r="F92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2866,6 +3145,9 @@
       <c r="F93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2892,6 +3174,9 @@
       <c r="F94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2918,6 +3203,9 @@
       <c r="F95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2944,6 +3232,9 @@
       <c r="F96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2970,6 +3261,9 @@
       <c r="F97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2996,6 +3290,9 @@
       <c r="F98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3022,6 +3319,9 @@
       <c r="F99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3048,6 +3348,9 @@
       <c r="F100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3074,6 +3377,9 @@
       <c r="F101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3100,6 +3406,9 @@
       <c r="F102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3126,6 +3435,9 @@
       <c r="F103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3152,6 +3464,9 @@
       <c r="F104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3178,6 +3493,9 @@
       <c r="F105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3204,6 +3522,9 @@
       <c r="F106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3230,6 +3551,9 @@
       <c r="F107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="G107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3256,6 +3580,9 @@
       <c r="F108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3282,6 +3609,9 @@
       <c r="F109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3308,6 +3638,9 @@
       <c r="F110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3334,6 +3667,9 @@
       <c r="F111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3360,6 +3696,9 @@
       <c r="F112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3386,6 +3725,9 @@
       <c r="F113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3412,6 +3754,9 @@
       <c r="F114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3438,6 +3783,9 @@
       <c r="F115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3464,6 +3812,9 @@
       <c r="F116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3490,6 +3841,9 @@
       <c r="F117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3516,6 +3870,9 @@
       <c r="F118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3542,6 +3899,9 @@
       <c r="F119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3568,6 +3928,9 @@
       <c r="F120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3594,6 +3957,9 @@
       <c r="F121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3620,6 +3986,9 @@
       <c r="F122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3646,6 +4015,9 @@
       <c r="F123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3672,6 +4044,9 @@
       <c r="F124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3698,6 +4073,9 @@
       <c r="F125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3724,6 +4102,9 @@
       <c r="F126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3750,6 +4131,9 @@
       <c r="F127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3776,6 +4160,9 @@
       <c r="F128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3802,6 +4189,9 @@
       <c r="F129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3828,6 +4218,9 @@
       <c r="F130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3854,6 +4247,9 @@
       <c r="F131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3880,6 +4276,9 @@
       <c r="F132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="G132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3906,6 +4305,9 @@
       <c r="F133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3932,6 +4334,9 @@
       <c r="F134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3958,6 +4363,9 @@
       <c r="F135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3984,6 +4392,9 @@
       <c r="F136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4010,6 +4421,9 @@
       <c r="F137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4036,6 +4450,9 @@
       <c r="F138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G138" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4062,6 +4479,9 @@
       <c r="F139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4088,6 +4508,9 @@
       <c r="F140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4114,6 +4537,9 @@
       <c r="F141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4140,6 +4566,9 @@
       <c r="F142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4166,6 +4595,9 @@
       <c r="F143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4192,6 +4624,9 @@
       <c r="F144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4218,6 +4653,9 @@
       <c r="F145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="G145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4244,6 +4682,9 @@
       <c r="F146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4270,6 +4711,9 @@
       <c r="F147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4296,6 +4740,9 @@
       <c r="F148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4322,6 +4769,9 @@
       <c r="F149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="G149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4348,6 +4798,9 @@
       <c r="F150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4374,6 +4827,9 @@
       <c r="F151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="G151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4400,6 +4856,9 @@
       <c r="F152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4426,6 +4885,9 @@
       <c r="F153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4452,6 +4914,9 @@
       <c r="F154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="G154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4478,6 +4943,9 @@
       <c r="F155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4504,6 +4972,9 @@
       <c r="F156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4530,6 +5001,9 @@
       <c r="F157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4556,6 +5030,9 @@
       <c r="F158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4582,6 +5059,9 @@
       <c r="F159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="G159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4608,6 +5088,9 @@
       <c r="F160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4634,6 +5117,9 @@
       <c r="F161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4660,6 +5146,9 @@
       <c r="F162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="G162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4686,6 +5175,9 @@
       <c r="F163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="G163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4712,9 +5204,12 @@
       <c r="F164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="G164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F164"/>
+  <autoFilter ref="A1:G164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>2026-09-08 10:10</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +515,9 @@
       <c r="G2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="H2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +547,9 @@
       <c r="G3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +579,9 @@
       <c r="G4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="H4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +611,9 @@
       <c r="G5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,6 +643,9 @@
       <c r="G6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,6 +675,9 @@
       <c r="G7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="H7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +707,9 @@
       <c r="G8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +739,9 @@
       <c r="G9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -741,6 +771,9 @@
       <c r="G10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,6 +803,9 @@
       <c r="G11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +835,9 @@
       <c r="G12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -828,6 +867,9 @@
       <c r="G13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="H13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +899,9 @@
       <c r="G14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -886,6 +931,9 @@
       <c r="G15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -915,6 +963,9 @@
       <c r="G16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -944,6 +995,9 @@
       <c r="G17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="H17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -973,6 +1027,9 @@
       <c r="G18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1002,6 +1059,9 @@
       <c r="G19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="H19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1031,6 +1091,9 @@
       <c r="G20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="H20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1060,6 +1123,9 @@
       <c r="G21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1089,6 +1155,9 @@
       <c r="G22" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1118,6 +1187,9 @@
       <c r="G23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1147,6 +1219,9 @@
       <c r="G24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1176,6 +1251,9 @@
       <c r="G25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1205,6 +1283,9 @@
       <c r="G26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="H26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1234,6 +1315,9 @@
       <c r="G27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1263,6 +1347,9 @@
       <c r="G28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="H28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1292,6 +1379,9 @@
       <c r="G29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="H29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,6 +1411,9 @@
       <c r="G30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1350,6 +1443,9 @@
       <c r="G31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1379,6 +1475,9 @@
       <c r="G32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1507,9 @@
       <c r="G33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1437,6 +1539,9 @@
       <c r="G34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="H34" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1466,6 +1571,9 @@
       <c r="G35" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H35" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1495,6 +1603,9 @@
       <c r="G36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1524,6 +1635,9 @@
       <c r="G37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1553,6 +1667,9 @@
       <c r="G38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1582,6 +1699,9 @@
       <c r="G39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="H39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,6 +1731,9 @@
       <c r="G40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1640,6 +1763,9 @@
       <c r="G41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1669,6 +1795,9 @@
       <c r="G42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1698,6 +1827,9 @@
       <c r="G43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1727,6 +1859,9 @@
       <c r="G44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1756,6 +1891,9 @@
       <c r="G45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1785,6 +1923,9 @@
       <c r="G46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="H46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1814,6 +1955,9 @@
       <c r="G47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1843,6 +1987,9 @@
       <c r="G48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1872,6 +2019,9 @@
       <c r="G49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1901,6 +2051,9 @@
       <c r="G50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1930,6 +2083,9 @@
       <c r="G51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="H51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1959,6 +2115,9 @@
       <c r="G52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="H52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1988,6 +2147,9 @@
       <c r="G53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2017,6 +2179,9 @@
       <c r="G54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2046,6 +2211,9 @@
       <c r="G55" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2075,6 +2243,9 @@
       <c r="G56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2104,6 +2275,9 @@
       <c r="G57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2133,6 +2307,9 @@
       <c r="G58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2162,6 +2339,9 @@
       <c r="G59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="H59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2191,6 +2371,9 @@
       <c r="G60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2220,6 +2403,9 @@
       <c r="G61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2249,6 +2435,9 @@
       <c r="G62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2278,6 +2467,9 @@
       <c r="G63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2307,6 +2499,9 @@
       <c r="G64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2336,6 +2531,9 @@
       <c r="G65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2365,6 +2563,9 @@
       <c r="G66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2394,6 +2595,9 @@
       <c r="G67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2423,6 +2627,9 @@
       <c r="G68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2452,6 +2659,9 @@
       <c r="G69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2481,6 +2691,9 @@
       <c r="G70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2510,6 +2723,9 @@
       <c r="G71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2539,6 +2755,9 @@
       <c r="G72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2568,6 +2787,9 @@
       <c r="G73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2597,6 +2819,9 @@
       <c r="G74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2626,6 +2851,9 @@
       <c r="G75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2655,6 +2883,9 @@
       <c r="G76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2684,6 +2915,9 @@
       <c r="G77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2713,6 +2947,9 @@
       <c r="G78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2742,6 +2979,9 @@
       <c r="G79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2771,6 +3011,9 @@
       <c r="G80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2800,6 +3043,9 @@
       <c r="G81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2829,6 +3075,9 @@
       <c r="G82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2858,6 +3107,9 @@
       <c r="G83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2887,6 +3139,9 @@
       <c r="G84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2916,6 +3171,9 @@
       <c r="G85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2945,6 +3203,9 @@
       <c r="G86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2974,6 +3235,9 @@
       <c r="G87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3003,6 +3267,9 @@
       <c r="G88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3032,6 +3299,9 @@
       <c r="G89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3061,6 +3331,9 @@
       <c r="G90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3090,6 +3363,9 @@
       <c r="G91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3119,6 +3395,9 @@
       <c r="G92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3148,6 +3427,9 @@
       <c r="G93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3177,6 +3459,9 @@
       <c r="G94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3206,6 +3491,9 @@
       <c r="G95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3235,6 +3523,9 @@
       <c r="G96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3264,6 +3555,9 @@
       <c r="G97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3293,6 +3587,9 @@
       <c r="G98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H98" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3322,6 +3619,9 @@
       <c r="G99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3351,6 +3651,9 @@
       <c r="G100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3380,6 +3683,9 @@
       <c r="G101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3409,6 +3715,9 @@
       <c r="G102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3438,6 +3747,9 @@
       <c r="G103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3467,6 +3779,9 @@
       <c r="G104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3496,6 +3811,9 @@
       <c r="G105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3525,6 +3843,9 @@
       <c r="G106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3554,6 +3875,9 @@
       <c r="G107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="H107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3583,6 +3907,9 @@
       <c r="G108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3612,6 +3939,9 @@
       <c r="G109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3641,6 +3971,9 @@
       <c r="G110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3670,6 +4003,9 @@
       <c r="G111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3699,6 +4035,9 @@
       <c r="G112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3728,6 +4067,9 @@
       <c r="G113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3757,6 +4099,9 @@
       <c r="G114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3786,6 +4131,9 @@
       <c r="G115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3815,6 +4163,9 @@
       <c r="G116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3844,6 +4195,9 @@
       <c r="G117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3873,6 +4227,9 @@
       <c r="G118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3902,6 +4259,9 @@
       <c r="G119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3931,6 +4291,9 @@
       <c r="G120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3960,6 +4323,9 @@
       <c r="G121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3989,6 +4355,9 @@
       <c r="G122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4018,6 +4387,9 @@
       <c r="G123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4047,6 +4419,9 @@
       <c r="G124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4076,6 +4451,9 @@
       <c r="G125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4105,6 +4483,9 @@
       <c r="G126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4134,6 +4515,9 @@
       <c r="G127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4163,6 +4547,9 @@
       <c r="G128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4192,6 +4579,9 @@
       <c r="G129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4221,6 +4611,9 @@
       <c r="G130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4250,6 +4643,9 @@
       <c r="G131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4279,6 +4675,9 @@
       <c r="G132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="H132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4308,6 +4707,9 @@
       <c r="G133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4337,6 +4739,9 @@
       <c r="G134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4366,6 +4771,9 @@
       <c r="G135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4395,6 +4803,9 @@
       <c r="G136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4424,6 +4835,9 @@
       <c r="G137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4453,6 +4867,9 @@
       <c r="G138" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4482,6 +4899,9 @@
       <c r="G139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4511,6 +4931,9 @@
       <c r="G140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4540,6 +4963,9 @@
       <c r="G141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4569,6 +4995,9 @@
       <c r="G142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4598,6 +5027,9 @@
       <c r="G143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4627,6 +5059,9 @@
       <c r="G144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4656,6 +5091,9 @@
       <c r="G145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="H145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4685,6 +5123,9 @@
       <c r="G146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4714,6 +5155,9 @@
       <c r="G147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4743,6 +5187,9 @@
       <c r="G148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4772,6 +5219,9 @@
       <c r="G149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="H149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4801,6 +5251,9 @@
       <c r="G150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4830,6 +5283,9 @@
       <c r="G151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="H151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4859,6 +5315,9 @@
       <c r="G152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4888,6 +5347,9 @@
       <c r="G153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4917,6 +5379,9 @@
       <c r="G154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="H154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4946,6 +5411,9 @@
       <c r="G155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4975,6 +5443,9 @@
       <c r="G156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5004,6 +5475,9 @@
       <c r="G157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5033,6 +5507,9 @@
       <c r="G158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5062,6 +5539,9 @@
       <c r="G159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="H159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5091,6 +5571,9 @@
       <c r="G160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5120,6 +5603,9 @@
       <c r="G161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5149,6 +5635,9 @@
       <c r="G162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="H162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5178,6 +5667,9 @@
       <c r="G163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="H163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5207,9 +5699,36 @@
       <c r="G164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="H164" s="2" t="n">
+        <v>24.25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TUMAN</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>MARIA MELIDA DELGADO OBLITAS</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SECTOR VILLA EL VALLE S/N</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="n"/>
+      <c r="H165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G164"/>
+  <autoFilter ref="A1:H165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +487,11 @@
           <t>2026-09-08 13:11</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 16:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +524,9 @@
       <c r="H2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,6 +559,9 @@
       <c r="H3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,6 +594,9 @@
       <c r="H4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,6 +629,9 @@
       <c r="H5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,6 +664,9 @@
       <c r="H6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +699,9 @@
       <c r="H7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -710,6 +734,9 @@
       <c r="H8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,6 +769,9 @@
       <c r="H9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -774,6 +804,9 @@
       <c r="H10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>20.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,6 +839,9 @@
       <c r="H11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -838,6 +874,9 @@
       <c r="H12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -870,6 +909,9 @@
       <c r="H13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -902,6 +944,9 @@
       <c r="H14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,6 +979,9 @@
       <c r="H15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -966,6 +1014,9 @@
       <c r="H16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -998,6 +1049,9 @@
       <c r="H17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1030,6 +1084,9 @@
       <c r="H18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1062,6 +1119,9 @@
       <c r="H19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1094,6 +1154,9 @@
       <c r="H20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1126,6 +1189,9 @@
       <c r="H21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1158,6 +1224,9 @@
       <c r="H22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1190,6 +1259,9 @@
       <c r="H23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1222,6 +1294,9 @@
       <c r="H24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,6 +1329,9 @@
       <c r="H25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1286,6 +1364,9 @@
       <c r="H26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1318,6 +1399,9 @@
       <c r="H27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1350,6 +1434,9 @@
       <c r="H28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="I28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1382,6 +1469,9 @@
       <c r="H29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1414,6 +1504,9 @@
       <c r="H30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1446,6 +1539,9 @@
       <c r="H31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1478,6 +1574,9 @@
       <c r="H32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,6 +1609,9 @@
       <c r="H33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1542,6 +1644,9 @@
       <c r="H34" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1574,6 +1679,9 @@
       <c r="H35" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1606,6 +1714,9 @@
       <c r="H36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1638,6 +1749,9 @@
       <c r="H37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1670,6 +1784,9 @@
       <c r="H38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1702,6 +1819,9 @@
       <c r="H39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="I39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1734,6 +1854,9 @@
       <c r="H40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1766,6 +1889,9 @@
       <c r="H41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1798,6 +1924,9 @@
       <c r="H42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1830,6 +1959,9 @@
       <c r="H43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1862,6 +1994,9 @@
       <c r="H44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1894,6 +2029,9 @@
       <c r="H45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1926,6 +2064,9 @@
       <c r="H46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="I46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1958,6 +2099,9 @@
       <c r="H47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1990,6 +2134,9 @@
       <c r="H48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2022,6 +2169,9 @@
       <c r="H49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2054,6 +2204,9 @@
       <c r="H50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2086,6 +2239,9 @@
       <c r="H51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="I51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2118,6 +2274,9 @@
       <c r="H52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="I52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2150,6 +2309,9 @@
       <c r="H53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2182,6 +2344,9 @@
       <c r="H54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2214,6 +2379,9 @@
       <c r="H55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2246,6 +2414,9 @@
       <c r="H56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2278,6 +2449,9 @@
       <c r="H57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,6 +2484,9 @@
       <c r="H58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2342,6 +2519,9 @@
       <c r="H59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="I59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2374,6 +2554,9 @@
       <c r="H60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2406,6 +2589,9 @@
       <c r="H61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2438,6 +2624,9 @@
       <c r="H62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,6 +2659,9 @@
       <c r="H63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2502,6 +2694,9 @@
       <c r="H64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,6 +2729,9 @@
       <c r="H65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2566,6 +2764,9 @@
       <c r="H66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2598,6 +2799,9 @@
       <c r="H67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2630,6 +2834,9 @@
       <c r="H68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2662,6 +2869,9 @@
       <c r="H69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2694,6 +2904,9 @@
       <c r="H70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2726,6 +2939,9 @@
       <c r="H71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2758,6 +2974,9 @@
       <c r="H72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2790,6 +3009,9 @@
       <c r="H73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2822,6 +3044,9 @@
       <c r="H74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2854,6 +3079,9 @@
       <c r="H75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2886,6 +3114,9 @@
       <c r="H76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2918,6 +3149,9 @@
       <c r="H77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2950,6 +3184,9 @@
       <c r="H78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2982,6 +3219,9 @@
       <c r="H79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3014,6 +3254,9 @@
       <c r="H80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3046,6 +3289,9 @@
       <c r="H81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3078,6 +3324,9 @@
       <c r="H82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3110,6 +3359,9 @@
       <c r="H83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3142,6 +3394,9 @@
       <c r="H84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3174,6 +3429,9 @@
       <c r="H85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3206,6 +3464,9 @@
       <c r="H86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3238,6 +3499,9 @@
       <c r="H87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3270,6 +3534,9 @@
       <c r="H88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3302,6 +3569,9 @@
       <c r="H89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3334,6 +3604,9 @@
       <c r="H90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3366,6 +3639,9 @@
       <c r="H91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3398,6 +3674,9 @@
       <c r="H92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3430,6 +3709,9 @@
       <c r="H93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3462,6 +3744,9 @@
       <c r="H94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3494,6 +3779,9 @@
       <c r="H95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3526,6 +3814,9 @@
       <c r="H96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3558,6 +3849,9 @@
       <c r="H97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3590,6 +3884,9 @@
       <c r="H98" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I98" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3622,6 +3919,9 @@
       <c r="H99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3654,6 +3954,9 @@
       <c r="H100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3686,6 +3989,9 @@
       <c r="H101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3718,6 +4024,9 @@
       <c r="H102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3750,6 +4059,9 @@
       <c r="H103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3782,6 +4094,9 @@
       <c r="H104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3814,6 +4129,9 @@
       <c r="H105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3846,6 +4164,9 @@
       <c r="H106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3878,6 +4199,9 @@
       <c r="H107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="I107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3910,6 +4234,9 @@
       <c r="H108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3942,6 +4269,9 @@
       <c r="H109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3974,6 +4304,9 @@
       <c r="H110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4006,6 +4339,9 @@
       <c r="H111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4038,6 +4374,9 @@
       <c r="H112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4070,6 +4409,9 @@
       <c r="H113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4102,6 +4444,9 @@
       <c r="H114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4134,6 +4479,9 @@
       <c r="H115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4166,6 +4514,9 @@
       <c r="H116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4198,6 +4549,9 @@
       <c r="H117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4230,6 +4584,9 @@
       <c r="H118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4262,6 +4619,9 @@
       <c r="H119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4294,6 +4654,9 @@
       <c r="H120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4326,6 +4689,9 @@
       <c r="H121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4358,6 +4724,9 @@
       <c r="H122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4390,6 +4759,9 @@
       <c r="H123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4422,6 +4794,9 @@
       <c r="H124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4454,6 +4829,9 @@
       <c r="H125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4486,6 +4864,9 @@
       <c r="H126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4518,6 +4899,9 @@
       <c r="H127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4550,6 +4934,9 @@
       <c r="H128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4582,6 +4969,9 @@
       <c r="H129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4614,6 +5004,9 @@
       <c r="H130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4646,6 +5039,9 @@
       <c r="H131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4678,6 +5074,9 @@
       <c r="H132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="I132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4710,6 +5109,9 @@
       <c r="H133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4742,6 +5144,9 @@
       <c r="H134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4774,6 +5179,9 @@
       <c r="H135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4806,6 +5214,9 @@
       <c r="H136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4838,6 +5249,9 @@
       <c r="H137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4870,6 +5284,9 @@
       <c r="H138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4902,6 +5319,9 @@
       <c r="H139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4934,6 +5354,9 @@
       <c r="H140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4966,6 +5389,9 @@
       <c r="H141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4998,6 +5424,9 @@
       <c r="H142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5030,6 +5459,9 @@
       <c r="H143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5062,6 +5494,9 @@
       <c r="H144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5094,6 +5529,9 @@
       <c r="H145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="I145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5126,6 +5564,9 @@
       <c r="H146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5158,6 +5599,9 @@
       <c r="H147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5190,6 +5634,9 @@
       <c r="H148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5222,6 +5669,9 @@
       <c r="H149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="I149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5254,6 +5704,9 @@
       <c r="H150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5286,6 +5739,9 @@
       <c r="H151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="I151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5318,6 +5774,9 @@
       <c r="H152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5350,6 +5809,9 @@
       <c r="H153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5382,6 +5844,9 @@
       <c r="H154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="I154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5414,6 +5879,9 @@
       <c r="H155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5446,6 +5914,9 @@
       <c r="H156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5478,6 +5949,9 @@
       <c r="H157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5510,6 +5984,9 @@
       <c r="H158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5542,6 +6019,9 @@
       <c r="H159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="I159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5574,6 +6054,9 @@
       <c r="H160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5606,6 +6089,9 @@
       <c r="H161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5638,6 +6124,9 @@
       <c r="H162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="I162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5670,6 +6159,9 @@
       <c r="H163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="I163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5700,6 +6192,9 @@
         <v>24.25</v>
       </c>
       <c r="H164" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I164" s="2" t="n">
         <v>24.25</v>
       </c>
     </row>
@@ -5726,9 +6221,12 @@
       <c r="H165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H165"/>
+  <autoFilter ref="A1:I165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,6 +493,11 @@
           <t>2026-09-08 16:08</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 19:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +533,9 @@
       <c r="I2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="J2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +571,9 @@
       <c r="I3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="J3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +609,9 @@
       <c r="I4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,6 +647,9 @@
       <c r="I5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +685,9 @@
       <c r="I6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +723,9 @@
       <c r="I7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="J7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +761,9 @@
       <c r="I8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="J8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +799,9 @@
       <c r="I9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="J9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -807,6 +837,9 @@
       <c r="I10" s="2" t="n">
         <v>20.1</v>
       </c>
+      <c r="J10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,6 +875,9 @@
       <c r="I11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="J11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -877,6 +913,9 @@
       <c r="I12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -912,6 +951,9 @@
       <c r="I13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="J13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -947,6 +989,9 @@
       <c r="I14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -982,6 +1027,9 @@
       <c r="I15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1017,6 +1065,9 @@
       <c r="I16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,6 +1103,9 @@
       <c r="I17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="J17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1087,6 +1141,9 @@
       <c r="I18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1122,6 +1179,9 @@
       <c r="I19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="J19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1157,6 +1217,9 @@
       <c r="I20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="J20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1192,6 +1255,9 @@
       <c r="I21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="J21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1227,6 +1293,9 @@
       <c r="I22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1262,6 +1331,9 @@
       <c r="I23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1297,6 +1369,9 @@
       <c r="I24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1332,6 +1407,9 @@
       <c r="I25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1367,6 +1445,9 @@
       <c r="I26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="J26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1402,6 +1483,9 @@
       <c r="I27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1437,6 +1521,9 @@
       <c r="I28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="J28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1472,6 +1559,9 @@
       <c r="I29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="J29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1597,9 @@
       <c r="I30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1542,6 +1635,9 @@
       <c r="I31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1577,6 +1673,9 @@
       <c r="I32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1612,6 +1711,9 @@
       <c r="I33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1647,6 +1749,9 @@
       <c r="I34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1682,6 +1787,9 @@
       <c r="I35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1717,6 +1825,9 @@
       <c r="I36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1752,6 +1863,9 @@
       <c r="I37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1787,6 +1901,9 @@
       <c r="I38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1822,6 +1939,9 @@
       <c r="I39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="J39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1857,6 +1977,9 @@
       <c r="I40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1892,6 +2015,9 @@
       <c r="I41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,6 +2053,9 @@
       <c r="I42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1962,6 +2091,9 @@
       <c r="I43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J43" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1997,6 +2129,9 @@
       <c r="I44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2032,6 +2167,9 @@
       <c r="I45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2067,6 +2205,9 @@
       <c r="I46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="J46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2102,6 +2243,9 @@
       <c r="I47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2137,6 +2281,9 @@
       <c r="I48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2172,6 +2319,9 @@
       <c r="I49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2207,6 +2357,9 @@
       <c r="I50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2242,6 +2395,9 @@
       <c r="I51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="J51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2277,6 +2433,9 @@
       <c r="I52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="J52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2312,6 +2471,9 @@
       <c r="I53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2347,6 +2509,9 @@
       <c r="I54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2382,6 +2547,9 @@
       <c r="I55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2417,6 +2585,9 @@
       <c r="I56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2452,6 +2623,9 @@
       <c r="I57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2487,6 +2661,9 @@
       <c r="I58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2522,6 +2699,9 @@
       <c r="I59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="J59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2557,6 +2737,9 @@
       <c r="I60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2592,6 +2775,9 @@
       <c r="I61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2627,6 +2813,9 @@
       <c r="I62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +2851,9 @@
       <c r="I63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2697,6 +2889,9 @@
       <c r="I64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2732,6 +2927,9 @@
       <c r="I65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2767,6 +2965,9 @@
       <c r="I66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2802,6 +3003,9 @@
       <c r="I67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2837,6 +3041,9 @@
       <c r="I68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2872,6 +3079,9 @@
       <c r="I69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J69" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2907,6 +3117,9 @@
       <c r="I70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2942,6 +3155,9 @@
       <c r="I71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2977,6 +3193,9 @@
       <c r="I72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3012,6 +3231,9 @@
       <c r="I73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J73" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3047,6 +3269,9 @@
       <c r="I74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3082,6 +3307,9 @@
       <c r="I75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3117,6 +3345,9 @@
       <c r="I76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3152,6 +3383,9 @@
       <c r="I77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3187,6 +3421,9 @@
       <c r="I78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3222,6 +3459,9 @@
       <c r="I79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3257,6 +3497,9 @@
       <c r="I80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3292,6 +3535,9 @@
       <c r="I81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3327,6 +3573,9 @@
       <c r="I82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3362,6 +3611,9 @@
       <c r="I83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3397,6 +3649,9 @@
       <c r="I84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3432,6 +3687,9 @@
       <c r="I85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3467,6 +3725,9 @@
       <c r="I86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J86" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3502,6 +3763,9 @@
       <c r="I87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3537,6 +3801,9 @@
       <c r="I88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3572,6 +3839,9 @@
       <c r="I89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3607,6 +3877,9 @@
       <c r="I90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3642,6 +3915,9 @@
       <c r="I91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3677,6 +3953,9 @@
       <c r="I92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3712,6 +3991,9 @@
       <c r="I93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3747,6 +4029,9 @@
       <c r="I94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3782,6 +4067,9 @@
       <c r="I95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3817,6 +4105,9 @@
       <c r="I96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3852,6 +4143,9 @@
       <c r="I97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3887,6 +4181,9 @@
       <c r="I98" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="J98" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3922,6 +4219,9 @@
       <c r="I99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3957,6 +4257,9 @@
       <c r="I100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3992,6 +4295,9 @@
       <c r="I101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4027,6 +4333,9 @@
       <c r="I102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4062,6 +4371,9 @@
       <c r="I103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4097,6 +4409,9 @@
       <c r="I104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4132,6 +4447,9 @@
       <c r="I105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4167,6 +4485,9 @@
       <c r="I106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4202,6 +4523,9 @@
       <c r="I107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="J107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4237,6 +4561,9 @@
       <c r="I108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4272,6 +4599,9 @@
       <c r="I109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4307,6 +4637,9 @@
       <c r="I110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4342,6 +4675,9 @@
       <c r="I111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4377,6 +4713,9 @@
       <c r="I112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4412,6 +4751,9 @@
       <c r="I113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4447,6 +4789,9 @@
       <c r="I114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4482,6 +4827,9 @@
       <c r="I115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4517,6 +4865,9 @@
       <c r="I116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4552,6 +4903,9 @@
       <c r="I117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J117" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4587,6 +4941,9 @@
       <c r="I118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4622,6 +4979,9 @@
       <c r="I119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4657,6 +5017,9 @@
       <c r="I120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4692,6 +5055,9 @@
       <c r="I121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4727,6 +5093,9 @@
       <c r="I122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4762,6 +5131,9 @@
       <c r="I123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4797,6 +5169,9 @@
       <c r="I124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4832,6 +5207,9 @@
       <c r="I125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4867,6 +5245,9 @@
       <c r="I126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4902,6 +5283,9 @@
       <c r="I127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4937,6 +5321,9 @@
       <c r="I128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4972,6 +5359,9 @@
       <c r="I129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5007,6 +5397,9 @@
       <c r="I130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5042,6 +5435,9 @@
       <c r="I131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5077,6 +5473,9 @@
       <c r="I132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="J132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5112,6 +5511,9 @@
       <c r="I133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5147,6 +5549,9 @@
       <c r="I134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5182,6 +5587,9 @@
       <c r="I135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5217,6 +5625,9 @@
       <c r="I136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5252,6 +5663,9 @@
       <c r="I137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5287,6 +5701,9 @@
       <c r="I138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5322,6 +5739,9 @@
       <c r="I139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5357,6 +5777,9 @@
       <c r="I140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5392,6 +5815,9 @@
       <c r="I141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5427,6 +5853,9 @@
       <c r="I142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5462,6 +5891,9 @@
       <c r="I143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5497,6 +5929,9 @@
       <c r="I144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5532,6 +5967,9 @@
       <c r="I145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="J145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5567,6 +6005,9 @@
       <c r="I146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5602,6 +6043,9 @@
       <c r="I147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5637,6 +6081,9 @@
       <c r="I148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5672,6 +6119,9 @@
       <c r="I149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="J149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5707,6 +6157,9 @@
       <c r="I150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5742,6 +6195,9 @@
       <c r="I151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="J151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5777,6 +6233,9 @@
       <c r="I152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5812,6 +6271,9 @@
       <c r="I153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5847,6 +6309,9 @@
       <c r="I154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="J154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5882,6 +6347,9 @@
       <c r="I155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5917,6 +6385,9 @@
       <c r="I156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5952,6 +6423,9 @@
       <c r="I157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5987,6 +6461,9 @@
       <c r="I158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6022,6 +6499,9 @@
       <c r="I159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6057,6 +6537,9 @@
       <c r="I160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6092,6 +6575,9 @@
       <c r="I161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6127,6 +6613,9 @@
       <c r="I162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="J162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6162,6 +6651,9 @@
       <c r="I163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="J163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6195,6 +6687,9 @@
         <v>24.25</v>
       </c>
       <c r="I164" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="J164" s="2" t="n">
         <v>24.25</v>
       </c>
     </row>
@@ -6224,9 +6719,12 @@
       <c r="I165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I165"/>
+  <autoFilter ref="A1:J165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +499,11 @@
           <t>2026-09-08 19:15</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 22:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,6 +542,9 @@
       <c r="J2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="K2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,6 +583,9 @@
       <c r="J3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="K3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,6 +624,9 @@
       <c r="J4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="K4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +665,9 @@
       <c r="J5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,6 +706,9 @@
       <c r="J6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,6 +747,9 @@
       <c r="J7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="K7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,6 +788,9 @@
       <c r="J8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="K8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -802,6 +829,9 @@
       <c r="J9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="K9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -840,6 +870,9 @@
       <c r="J10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,6 +911,9 @@
       <c r="J11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="K11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -916,6 +952,9 @@
       <c r="J12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -954,6 +993,9 @@
       <c r="J13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="K13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -992,6 +1034,9 @@
       <c r="J14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1030,6 +1075,9 @@
       <c r="J15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1068,6 +1116,9 @@
       <c r="J16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1106,6 +1157,9 @@
       <c r="J17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="K17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1144,6 +1198,9 @@
       <c r="J18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1182,6 +1239,9 @@
       <c r="J19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="K19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1220,6 +1280,9 @@
       <c r="J20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="K20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1258,6 +1321,9 @@
       <c r="J21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="K21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1296,6 +1362,9 @@
       <c r="J22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1334,6 +1403,9 @@
       <c r="J23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1372,6 +1444,9 @@
       <c r="J24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1410,6 +1485,9 @@
       <c r="J25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1448,6 +1526,9 @@
       <c r="J26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="K26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1486,6 +1567,9 @@
       <c r="J27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1524,6 +1608,9 @@
       <c r="J28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="K28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1562,6 +1649,9 @@
       <c r="J29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="K29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1600,6 +1690,9 @@
       <c r="J30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1638,6 +1731,9 @@
       <c r="J31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1676,6 +1772,9 @@
       <c r="J32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1714,6 +1813,9 @@
       <c r="J33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1752,6 +1854,9 @@
       <c r="J34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1790,6 +1895,9 @@
       <c r="J35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1828,6 +1936,9 @@
       <c r="J36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1866,6 +1977,9 @@
       <c r="J37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1904,6 +2018,9 @@
       <c r="J38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1942,6 +2059,9 @@
       <c r="J39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="K39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1980,6 +2100,9 @@
       <c r="J40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2018,6 +2141,9 @@
       <c r="J41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2056,6 +2182,9 @@
       <c r="J42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2094,6 +2223,9 @@
       <c r="J43" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2132,6 +2264,9 @@
       <c r="J44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2170,6 +2305,9 @@
       <c r="J45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2208,6 +2346,9 @@
       <c r="J46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="K46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2246,6 +2387,9 @@
       <c r="J47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2284,6 +2428,9 @@
       <c r="J48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2322,6 +2469,9 @@
       <c r="J49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2360,6 +2510,9 @@
       <c r="J50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2398,6 +2551,9 @@
       <c r="J51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="K51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2436,6 +2592,9 @@
       <c r="J52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="K52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2474,6 +2633,9 @@
       <c r="J53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2512,6 +2674,9 @@
       <c r="J54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="K54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2550,6 +2715,9 @@
       <c r="J55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2588,6 +2756,9 @@
       <c r="J56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2626,6 +2797,9 @@
       <c r="J57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2664,6 +2838,9 @@
       <c r="J58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2702,6 +2879,9 @@
       <c r="J59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="K59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2740,6 +2920,9 @@
       <c r="J60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2778,6 +2961,9 @@
       <c r="J61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2816,6 +3002,9 @@
       <c r="J62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2854,6 +3043,9 @@
       <c r="J63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2892,6 +3084,9 @@
       <c r="J64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2930,6 +3125,9 @@
       <c r="J65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2968,6 +3166,9 @@
       <c r="J66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3006,6 +3207,9 @@
       <c r="J67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3044,6 +3248,9 @@
       <c r="J68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3082,6 +3289,9 @@
       <c r="J69" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K69" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3120,6 +3330,9 @@
       <c r="J70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3158,6 +3371,9 @@
       <c r="J71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3196,6 +3412,9 @@
       <c r="J72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3234,6 +3453,9 @@
       <c r="J73" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K73" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3272,6 +3494,9 @@
       <c r="J74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3310,6 +3535,9 @@
       <c r="J75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3348,6 +3576,9 @@
       <c r="J76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3386,6 +3617,9 @@
       <c r="J77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3424,6 +3658,9 @@
       <c r="J78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3462,6 +3699,9 @@
       <c r="J79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3500,6 +3740,9 @@
       <c r="J80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3538,6 +3781,9 @@
       <c r="J81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3576,6 +3822,9 @@
       <c r="J82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3614,6 +3863,9 @@
       <c r="J83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3652,6 +3904,9 @@
       <c r="J84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3690,6 +3945,9 @@
       <c r="J85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3728,6 +3986,9 @@
       <c r="J86" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K86" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3766,6 +4027,9 @@
       <c r="J87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3804,6 +4068,9 @@
       <c r="J88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3842,6 +4109,9 @@
       <c r="J89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3880,6 +4150,9 @@
       <c r="J90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3918,6 +4191,9 @@
       <c r="J91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3956,6 +4232,9 @@
       <c r="J92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3994,6 +4273,9 @@
       <c r="J93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="K93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4032,6 +4314,9 @@
       <c r="J94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4070,6 +4355,9 @@
       <c r="J95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4108,6 +4396,9 @@
       <c r="J96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4146,6 +4437,9 @@
       <c r="J97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4184,6 +4478,9 @@
       <c r="J98" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="K98" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4222,6 +4519,9 @@
       <c r="J99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4260,6 +4560,9 @@
       <c r="J100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4298,6 +4601,9 @@
       <c r="J101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4336,6 +4642,9 @@
       <c r="J102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4374,6 +4683,9 @@
       <c r="J103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4412,6 +4724,9 @@
       <c r="J104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4450,6 +4765,9 @@
       <c r="J105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4488,6 +4806,9 @@
       <c r="J106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4526,6 +4847,9 @@
       <c r="J107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="K107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4564,6 +4888,9 @@
       <c r="J108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4602,6 +4929,9 @@
       <c r="J109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4640,6 +4970,9 @@
       <c r="J110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4678,6 +5011,9 @@
       <c r="J111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4716,6 +5052,9 @@
       <c r="J112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4754,6 +5093,9 @@
       <c r="J113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4792,6 +5134,9 @@
       <c r="J114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4830,6 +5175,9 @@
       <c r="J115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4868,6 +5216,9 @@
       <c r="J116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4906,6 +5257,9 @@
       <c r="J117" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4944,6 +5298,9 @@
       <c r="J118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4982,6 +5339,9 @@
       <c r="J119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5020,6 +5380,9 @@
       <c r="J120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5058,6 +5421,9 @@
       <c r="J121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5096,6 +5462,9 @@
       <c r="J122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5134,6 +5503,9 @@
       <c r="J123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5172,6 +5544,9 @@
       <c r="J124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5210,6 +5585,9 @@
       <c r="J125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5248,6 +5626,9 @@
       <c r="J126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5286,6 +5667,9 @@
       <c r="J127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5324,6 +5708,9 @@
       <c r="J128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5362,6 +5749,9 @@
       <c r="J129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5400,6 +5790,9 @@
       <c r="J130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5438,6 +5831,9 @@
       <c r="J131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5476,6 +5872,9 @@
       <c r="J132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="K132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5514,6 +5913,9 @@
       <c r="J133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="K133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5552,6 +5954,9 @@
       <c r="J134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="K134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5590,6 +5995,9 @@
       <c r="J135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5628,6 +6036,9 @@
       <c r="J136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5666,6 +6077,9 @@
       <c r="J137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5704,6 +6118,9 @@
       <c r="J138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5742,6 +6159,9 @@
       <c r="J139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5780,6 +6200,9 @@
       <c r="J140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5818,6 +6241,9 @@
       <c r="J141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5856,6 +6282,9 @@
       <c r="J142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5894,6 +6323,9 @@
       <c r="J143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5932,6 +6364,9 @@
       <c r="J144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5970,6 +6405,9 @@
       <c r="J145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="K145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6008,6 +6446,9 @@
       <c r="J146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6046,6 +6487,9 @@
       <c r="J147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6084,6 +6528,9 @@
       <c r="J148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="K148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6122,6 +6569,9 @@
       <c r="J149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="K149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6160,6 +6610,9 @@
       <c r="J150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="K150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6198,6 +6651,9 @@
       <c r="J151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="K151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6236,6 +6692,9 @@
       <c r="J152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6274,6 +6733,9 @@
       <c r="J153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6312,6 +6774,9 @@
       <c r="J154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="K154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6350,6 +6815,9 @@
       <c r="J155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="K155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6388,6 +6856,9 @@
       <c r="J156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6426,6 +6897,9 @@
       <c r="J157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6464,6 +6938,9 @@
       <c r="J158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6502,6 +6979,9 @@
       <c r="J159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="K159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6540,6 +7020,9 @@
       <c r="J160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6578,6 +7061,9 @@
       <c r="J161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6616,6 +7102,9 @@
       <c r="J162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="K162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6654,6 +7143,9 @@
       <c r="J163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="K163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6690,6 +7182,9 @@
         <v>24.25</v>
       </c>
       <c r="J164" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="K164" s="2" t="n">
         <v>24.25</v>
       </c>
     </row>
@@ -6722,9 +7217,12 @@
       <c r="J165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J165"/>
+  <autoFilter ref="A1:K165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,42 +459,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08 01:12</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-08 04:10</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-08 07:13</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-08 10:10</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-08 13:11</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-08 16:08</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-08 19:15</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-08 22:09</t>
+          <t>2026-09-09 01:12</t>
         </is>
       </c>
     </row>
@@ -524,27 +482,6 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>13.45</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,27 +502,6 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -606,27 +522,6 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>17.95</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,27 +542,6 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,27 +562,6 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -729,27 +582,6 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>19.49</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -770,27 +602,6 @@
       <c r="D8" s="2" t="n">
         <v>20.19</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>20.19</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -811,27 +622,6 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -850,27 +640,6 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K10" s="2" t="n">
         <v>20.9</v>
       </c>
     </row>
@@ -893,27 +662,6 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>20.19</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,27 +682,6 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,27 +702,6 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>20.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1016,27 +722,6 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1057,27 +742,6 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,27 +762,6 @@
       <c r="D16" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1139,27 +782,6 @@
       <c r="D17" s="2" t="n">
         <v>20.75</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>20.75</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1180,27 +802,6 @@
       <c r="D18" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1221,27 +822,6 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>20.77</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1260,27 +840,6 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="K20" s="2" t="n">
         <v>20.65</v>
       </c>
     </row>
@@ -1303,27 +862,6 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>20.48</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1342,27 +880,6 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K22" s="2" t="n">
         <v>21.99</v>
       </c>
     </row>
@@ -1385,27 +902,6 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1426,27 +922,6 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1467,27 +942,6 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1508,27 +962,6 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>20.8</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1549,27 +982,6 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1590,27 +1002,6 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>20.54</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1631,27 +1022,6 @@
       <c r="D29" s="2" t="n">
         <v>20.75</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>20.75</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1672,27 +1042,6 @@
       <c r="D30" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1713,27 +1062,6 @@
       <c r="D31" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1754,27 +1082,6 @@
       <c r="D32" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1795,27 +1102,6 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1834,27 +1120,6 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K34" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1877,27 +1142,6 @@
       <c r="D35" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1918,27 +1162,6 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1959,27 +1182,6 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2000,27 +1202,6 @@
       <c r="D38" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2039,27 +1220,6 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="K39" s="2" t="n">
         <v>20.98</v>
       </c>
     </row>
@@ -2082,27 +1242,6 @@
       <c r="D40" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2123,27 +1262,6 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2164,27 +1282,6 @@
       <c r="D42" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2203,27 +1300,6 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K43" s="2" t="n">
         <v>20.95</v>
       </c>
     </row>
@@ -2246,27 +1322,6 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2287,27 +1342,6 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2328,27 +1362,6 @@
       <c r="D46" s="2" t="n">
         <v>21.05</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>21.05</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2369,27 +1382,6 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2410,27 +1402,6 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2451,27 +1422,6 @@
       <c r="D49" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2492,27 +1442,6 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2533,27 +1462,6 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>20.85</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2574,27 +1482,6 @@
       <c r="D52" s="2" t="n">
         <v>20.85</v>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>20.85</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2615,27 +1502,6 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2656,27 +1522,6 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>21.79</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2695,27 +1540,6 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K55" s="2" t="n">
         <v>21.3</v>
       </c>
     </row>
@@ -2738,27 +1562,6 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2779,27 +1582,6 @@
       <c r="D57" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2820,27 +1602,6 @@
       <c r="D58" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2861,27 +1622,6 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>22.2</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2902,27 +1642,6 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2943,27 +1662,6 @@
       <c r="D61" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2984,27 +1682,6 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3025,27 +1702,6 @@
       <c r="D63" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3066,27 +1722,6 @@
       <c r="D64" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3107,27 +1742,6 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K65" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3148,27 +1762,6 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3189,27 +1782,6 @@
       <c r="D67" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3230,27 +1802,6 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3269,27 +1820,6 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K69" s="2" t="n">
         <v>21.85</v>
       </c>
     </row>
@@ -3312,27 +1842,6 @@
       <c r="D70" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3353,27 +1862,6 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K71" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3394,27 +1882,6 @@
       <c r="D72" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3433,27 +1900,6 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K73" s="2" t="n">
         <v>21.85</v>
       </c>
     </row>
@@ -3476,27 +1922,6 @@
       <c r="D74" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3517,27 +1942,6 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3558,27 +1962,6 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3599,27 +1982,6 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3640,27 +2002,6 @@
       <c r="D78" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3681,27 +2022,6 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3722,27 +2042,6 @@
       <c r="D80" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3763,27 +2062,6 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3804,27 +2082,6 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3845,27 +2102,6 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3886,27 +2122,6 @@
       <c r="D84" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3927,27 +2142,6 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3966,27 +2160,6 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K86" s="2" t="n">
         <v>21.85</v>
       </c>
     </row>
@@ -4009,27 +2182,6 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4050,27 +2202,6 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4091,27 +2222,6 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4132,27 +2242,6 @@
       <c r="D90" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4173,27 +2262,6 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4214,27 +2282,6 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4255,27 +2302,6 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
-      <c r="E93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>21.89</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4296,27 +2322,6 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4337,27 +2342,6 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4378,27 +2362,6 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4419,27 +2382,6 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4458,27 +2400,6 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="K98" s="2" t="n">
         <v>21.05</v>
       </c>
     </row>
@@ -4501,27 +2422,6 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4542,27 +2442,6 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4583,27 +2462,6 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4624,27 +2482,6 @@
       <c r="D102" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4665,27 +2502,6 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4706,27 +2522,6 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4747,27 +2542,6 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4788,27 +2562,6 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4829,27 +2582,6 @@
       <c r="D107" s="2" t="n">
         <v>21.29</v>
       </c>
-      <c r="E107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>21.29</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4870,27 +2602,6 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4911,27 +2622,6 @@
       <c r="D109" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4952,27 +2642,6 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4993,27 +2662,6 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5034,27 +2682,6 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5075,27 +2702,6 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5116,27 +2722,6 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5157,27 +2742,6 @@
       <c r="D115" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5198,27 +2762,6 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5237,27 +2780,6 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K117" s="2" t="n">
         <v>21.85</v>
       </c>
     </row>
@@ -5280,27 +2802,6 @@
       <c r="D118" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5321,27 +2822,6 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5362,27 +2842,6 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5403,27 +2862,6 @@
       <c r="D121" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5444,27 +2882,6 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5485,27 +2902,6 @@
       <c r="D123" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5526,27 +2922,6 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5567,27 +2942,6 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5608,27 +2962,6 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5649,27 +2982,6 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5690,27 +3002,6 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5729,27 +3020,6 @@
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K129" s="2" t="n">
         <v>22.6</v>
       </c>
     </row>
@@ -5772,27 +3042,6 @@
       <c r="D130" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5813,27 +3062,6 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5854,27 +3082,6 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="E132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>21.6</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5895,27 +3102,6 @@
       <c r="D133" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="E133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>21.7</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5936,27 +3122,6 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="E134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>21.7</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5977,27 +3142,6 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6018,27 +3162,6 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6059,27 +3182,6 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6098,27 +3200,6 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K138" s="2" t="n">
         <v>20.69</v>
       </c>
     </row>
@@ -6141,27 +3222,6 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K139" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6182,27 +3242,6 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6223,27 +3262,6 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6264,27 +3282,6 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6305,27 +3302,6 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6346,27 +3322,6 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6387,27 +3342,6 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
-      <c r="E145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>22.29</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6428,27 +3362,6 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6469,27 +3382,6 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K147" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6510,27 +3402,6 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
-      <c r="E148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="K148" s="2" t="n">
-        <v>22.35</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6551,27 +3422,6 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
-      <c r="E149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="K149" s="2" t="n">
-        <v>22.49</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6592,27 +3442,6 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K150" s="2" t="n">
-        <v>22.5</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6633,27 +3462,6 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
-      <c r="E151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="K151" s="2" t="n">
-        <v>22.59</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6674,27 +3482,6 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6715,27 +3502,6 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6756,27 +3522,6 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>22.7</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6797,27 +3542,6 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>22.79</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6838,27 +3562,6 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6879,27 +3582,6 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K157" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6920,27 +3602,6 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K158" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6961,27 +3622,6 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
-      <c r="E159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="K159" s="2" t="n">
-        <v>23.99</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7002,27 +3642,6 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K160" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7043,27 +3662,6 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K161" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7084,27 +3682,6 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
-      <c r="E162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="K162" s="2" t="n">
-        <v>23.49</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7125,27 +3702,6 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K163" s="2" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7166,27 +3722,6 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="K164" s="2" t="n">
-        <v>24.25</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7204,25 +3739,12 @@
           <t>SECTOR VILLA EL VALLE S/N</t>
         </is>
       </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="2" t="n"/>
-      <c r="F165" s="2" t="n"/>
-      <c r="G165" s="2" t="n"/>
-      <c r="H165" s="2" t="n">
+      <c r="D165" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="I165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K165" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K165"/>
+  <autoFilter ref="A1:D165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,13 +432,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,6 +463,11 @@
           <t>2026-09-09 01:12</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,6 +488,9 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,6 +511,9 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -522,6 +534,9 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +557,9 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,6 +580,9 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -582,6 +603,9 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,6 +626,9 @@
       <c r="D8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="E8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +649,9 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,6 +672,9 @@
       <c r="D10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -662,6 +695,9 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,6 +718,9 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -702,6 +741,9 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,6 +764,9 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,6 +787,9 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -762,6 +810,9 @@
       <c r="D16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,6 +833,9 @@
       <c r="D17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="E17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -802,6 +856,9 @@
       <c r="D18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -822,6 +879,9 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,6 +902,9 @@
       <c r="D20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,6 +925,9 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -882,6 +948,9 @@
       <c r="D22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -902,6 +971,9 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -922,6 +994,9 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -942,6 +1017,9 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -962,6 +1040,9 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="E26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -982,6 +1063,9 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1002,6 +1086,9 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1022,6 +1109,9 @@
       <c r="D29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="E29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1042,6 +1132,9 @@
       <c r="D30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1062,6 +1155,9 @@
       <c r="D31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1082,6 +1178,9 @@
       <c r="D32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1102,6 +1201,9 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1122,6 +1224,9 @@
       <c r="D34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1142,6 +1247,9 @@
       <c r="D35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1162,6 +1270,9 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1182,6 +1293,9 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1202,6 +1316,9 @@
       <c r="D38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1222,6 +1339,9 @@
       <c r="D39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="E39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1242,6 +1362,9 @@
       <c r="D40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1262,6 +1385,9 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1282,6 +1408,9 @@
       <c r="D42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1302,6 +1431,9 @@
       <c r="D43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1322,6 +1454,9 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1342,6 +1477,9 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1362,6 +1500,9 @@
       <c r="D46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="E46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1382,6 +1523,9 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1402,6 +1546,9 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1422,6 +1569,9 @@
       <c r="D49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1442,6 +1592,9 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1462,6 +1615,9 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="E51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1482,6 +1638,9 @@
       <c r="D52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="E52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1502,6 +1661,9 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1522,6 +1684,9 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1542,6 +1707,9 @@
       <c r="D55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1562,6 +1730,9 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1582,6 +1753,9 @@
       <c r="D57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1602,6 +1776,9 @@
       <c r="D58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1622,6 +1799,9 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="E59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1642,6 +1822,9 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1662,6 +1845,9 @@
       <c r="D61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1682,6 +1868,9 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1702,6 +1891,9 @@
       <c r="D63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1722,6 +1914,9 @@
       <c r="D64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1742,6 +1937,9 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1762,6 +1960,9 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1782,6 +1983,9 @@
       <c r="D67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1802,6 +2006,9 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1822,6 +2029,9 @@
       <c r="D69" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="E69" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1842,6 +2052,9 @@
       <c r="D70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1862,6 +2075,9 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1882,6 +2098,9 @@
       <c r="D72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1902,6 +2121,9 @@
       <c r="D73" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="E73" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1922,6 +2144,9 @@
       <c r="D74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1942,6 +2167,9 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1962,6 +2190,9 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1982,6 +2213,9 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2002,6 +2236,9 @@
       <c r="D78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2022,6 +2259,9 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2042,6 +2282,9 @@
       <c r="D80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E80" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2062,6 +2305,9 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2082,6 +2328,9 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2102,6 +2351,9 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2122,6 +2374,9 @@
       <c r="D84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2142,6 +2397,9 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2162,6 +2420,9 @@
       <c r="D86" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="E86" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2182,6 +2443,9 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2202,6 +2466,9 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2222,6 +2489,9 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2242,6 +2512,9 @@
       <c r="D90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2262,6 +2535,9 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2282,6 +2558,9 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2302,6 +2581,9 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="E93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2322,6 +2604,9 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2342,6 +2627,9 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2362,6 +2650,9 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2382,6 +2673,9 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2402,6 +2696,9 @@
       <c r="D98" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="E98" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2422,6 +2719,9 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2442,6 +2742,9 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2462,6 +2765,9 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2482,6 +2788,9 @@
       <c r="D102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2502,6 +2811,9 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2522,6 +2834,9 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2542,6 +2857,9 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2562,6 +2880,9 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2582,6 +2903,9 @@
       <c r="D107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="E107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2602,6 +2926,9 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2622,6 +2949,9 @@
       <c r="D109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2642,6 +2972,9 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2662,6 +2995,9 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2682,6 +3018,9 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2702,6 +3041,9 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2722,6 +3064,9 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2742,6 +3087,9 @@
       <c r="D115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2762,6 +3110,9 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2782,6 +3133,9 @@
       <c r="D117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="E117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2802,6 +3156,9 @@
       <c r="D118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2822,6 +3179,9 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2842,6 +3202,9 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2862,6 +3225,9 @@
       <c r="D121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E121" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2882,6 +3248,9 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2902,6 +3271,9 @@
       <c r="D123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2922,6 +3294,9 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2942,6 +3317,9 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2962,6 +3340,9 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2982,6 +3363,9 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3002,6 +3386,9 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3022,6 +3409,9 @@
       <c r="D129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3042,6 +3432,9 @@
       <c r="D130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3062,6 +3455,9 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3082,6 +3478,9 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="E132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3102,6 +3501,9 @@
       <c r="D133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="E133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3122,6 +3524,9 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="E134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3142,6 +3547,9 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3162,6 +3570,9 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3182,6 +3593,9 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3202,6 +3616,9 @@
       <c r="D138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3222,6 +3639,9 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3242,6 +3662,9 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3262,6 +3685,9 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3282,6 +3708,9 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3302,6 +3731,9 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3322,6 +3754,9 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3342,6 +3777,9 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="E145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3362,6 +3800,9 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3382,6 +3823,9 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3402,6 +3846,9 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3422,6 +3869,9 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="E149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3442,6 +3892,9 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="E150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3462,6 +3915,9 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="E151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3482,6 +3938,9 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3502,6 +3961,9 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3522,6 +3984,9 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="E154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3542,6 +4007,9 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3562,6 +4030,9 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3582,6 +4053,9 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3602,6 +4076,9 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3622,6 +4099,9 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="E159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3642,6 +4122,9 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3662,6 +4145,9 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3682,6 +4168,9 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="E162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3702,6 +4191,9 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="E163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3722,6 +4214,9 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="E164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3742,9 +4237,12 @@
       <c r="D165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D165"/>
+  <autoFilter ref="A1:E165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,11 @@
           <t>2026-09-09 04:10</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +497,9 @@
       <c r="E2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,6 +523,9 @@
       <c r="E3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="F3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +549,9 @@
       <c r="E4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,6 +575,9 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +601,9 @@
       <c r="E6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -606,6 +627,9 @@
       <c r="E7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="F7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -629,6 +653,9 @@
       <c r="E8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -652,6 +679,9 @@
       <c r="E9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="F9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -675,6 +705,9 @@
       <c r="E10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +731,9 @@
       <c r="E11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="F11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -721,6 +757,9 @@
       <c r="E12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,6 +783,9 @@
       <c r="E13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="F13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -767,6 +809,9 @@
       <c r="E14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -790,6 +835,9 @@
       <c r="E15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -813,6 +861,9 @@
       <c r="E16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -836,6 +887,9 @@
       <c r="E17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="F17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -859,6 +913,9 @@
       <c r="E18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -882,6 +939,9 @@
       <c r="E19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="F19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -905,6 +965,9 @@
       <c r="E20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="F20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -928,6 +991,9 @@
       <c r="E21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="F21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -951,6 +1017,9 @@
       <c r="E22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -974,6 +1043,9 @@
       <c r="E23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -997,6 +1069,9 @@
       <c r="E24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1020,6 +1095,9 @@
       <c r="E25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1043,6 +1121,9 @@
       <c r="E26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="F26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1066,6 +1147,9 @@
       <c r="E27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1089,6 +1173,9 @@
       <c r="E28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="F28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1112,6 +1199,9 @@
       <c r="E29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="F29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1135,6 +1225,9 @@
       <c r="E30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1158,6 +1251,9 @@
       <c r="E31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1181,6 +1277,9 @@
       <c r="E32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1204,6 +1303,9 @@
       <c r="E33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1227,6 +1329,9 @@
       <c r="E34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1250,6 +1355,9 @@
       <c r="E35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1273,6 +1381,9 @@
       <c r="E36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1296,6 +1407,9 @@
       <c r="E37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1319,6 +1433,9 @@
       <c r="E38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1342,6 +1459,9 @@
       <c r="E39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="F39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1365,6 +1485,9 @@
       <c r="E40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1388,6 +1511,9 @@
       <c r="E41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1411,6 +1537,9 @@
       <c r="E42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1434,6 +1563,9 @@
       <c r="E43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1457,6 +1589,9 @@
       <c r="E44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1480,6 +1615,9 @@
       <c r="E45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1503,6 +1641,9 @@
       <c r="E46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="F46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1526,6 +1667,9 @@
       <c r="E47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1549,6 +1693,9 @@
       <c r="E48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1572,6 +1719,9 @@
       <c r="E49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1595,6 +1745,9 @@
       <c r="E50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1618,6 +1771,9 @@
       <c r="E51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="F51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1641,6 +1797,9 @@
       <c r="E52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="F52" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1664,6 +1823,9 @@
       <c r="E53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1687,6 +1849,9 @@
       <c r="E54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1710,6 +1875,9 @@
       <c r="E55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1733,6 +1901,9 @@
       <c r="E56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1756,6 +1927,9 @@
       <c r="E57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1779,6 +1953,9 @@
       <c r="E58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1802,6 +1979,9 @@
       <c r="E59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="F59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1825,6 +2005,9 @@
       <c r="E60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1848,6 +2031,9 @@
       <c r="E61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1871,6 +2057,9 @@
       <c r="E62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1894,6 +2083,9 @@
       <c r="E63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1917,6 +2109,9 @@
       <c r="E64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1940,6 +2135,9 @@
       <c r="E65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1963,6 +2161,9 @@
       <c r="E66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1986,6 +2187,9 @@
       <c r="E67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2009,6 +2213,9 @@
       <c r="E68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2032,6 +2239,9 @@
       <c r="E69" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="F69" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2055,6 +2265,9 @@
       <c r="E70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2078,6 +2291,9 @@
       <c r="E71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2101,6 +2317,9 @@
       <c r="E72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2124,6 +2343,9 @@
       <c r="E73" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="F73" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2147,6 +2369,9 @@
       <c r="E74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F74" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2170,6 +2395,9 @@
       <c r="E75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2193,6 +2421,9 @@
       <c r="E76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2216,6 +2447,9 @@
       <c r="E77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2239,6 +2473,9 @@
       <c r="E78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2262,6 +2499,9 @@
       <c r="E79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2285,6 +2525,9 @@
       <c r="E80" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2308,6 +2551,9 @@
       <c r="E81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2331,6 +2577,9 @@
       <c r="E82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2354,6 +2603,9 @@
       <c r="E83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2377,6 +2629,9 @@
       <c r="E84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F84" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2400,6 +2655,9 @@
       <c r="E85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2423,6 +2681,9 @@
       <c r="E86" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="F86" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2446,6 +2707,9 @@
       <c r="E87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2469,6 +2733,9 @@
       <c r="E88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2492,6 +2759,9 @@
       <c r="E89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2515,6 +2785,9 @@
       <c r="E90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2538,6 +2811,9 @@
       <c r="E91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2561,6 +2837,9 @@
       <c r="E92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2584,6 +2863,9 @@
       <c r="E93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="F93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2607,6 +2889,9 @@
       <c r="E94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2630,6 +2915,9 @@
       <c r="E95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2653,6 +2941,9 @@
       <c r="E96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2676,6 +2967,9 @@
       <c r="E97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2699,6 +2993,9 @@
       <c r="E98" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="F98" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2722,6 +3019,9 @@
       <c r="E99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2745,6 +3045,9 @@
       <c r="E100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2768,6 +3071,9 @@
       <c r="E101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2791,6 +3097,9 @@
       <c r="E102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2814,6 +3123,9 @@
       <c r="E103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2837,6 +3149,9 @@
       <c r="E104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2860,6 +3175,9 @@
       <c r="E105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2883,6 +3201,9 @@
       <c r="E106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2906,6 +3227,9 @@
       <c r="E107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="F107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2929,6 +3253,9 @@
       <c r="E108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2952,6 +3279,9 @@
       <c r="E109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2975,6 +3305,9 @@
       <c r="E110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2998,6 +3331,9 @@
       <c r="E111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3021,6 +3357,9 @@
       <c r="E112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3044,6 +3383,9 @@
       <c r="E113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3067,6 +3409,9 @@
       <c r="E114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3090,6 +3435,9 @@
       <c r="E115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3113,6 +3461,9 @@
       <c r="E116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3136,6 +3487,9 @@
       <c r="E117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="F117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3159,6 +3513,9 @@
       <c r="E118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F118" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3182,6 +3539,9 @@
       <c r="E119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3205,6 +3565,9 @@
       <c r="E120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3228,6 +3591,9 @@
       <c r="E121" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3251,6 +3617,9 @@
       <c r="E122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3274,6 +3643,9 @@
       <c r="E123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3297,6 +3669,9 @@
       <c r="E124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3320,6 +3695,9 @@
       <c r="E125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3343,6 +3721,9 @@
       <c r="E126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3366,6 +3747,9 @@
       <c r="E127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3389,6 +3773,9 @@
       <c r="E128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3412,6 +3799,9 @@
       <c r="E129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3435,6 +3825,9 @@
       <c r="E130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3458,6 +3851,9 @@
       <c r="E131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3481,6 +3877,9 @@
       <c r="E132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="F132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3504,6 +3903,9 @@
       <c r="E133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="F133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3527,6 +3929,9 @@
       <c r="E134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="F134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3550,6 +3955,9 @@
       <c r="E135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3573,6 +3981,9 @@
       <c r="E136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3596,6 +4007,9 @@
       <c r="E137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3619,6 +4033,9 @@
       <c r="E138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3642,6 +4059,9 @@
       <c r="E139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3665,6 +4085,9 @@
       <c r="E140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3688,6 +4111,9 @@
       <c r="E141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3711,6 +4137,9 @@
       <c r="E142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3734,6 +4163,9 @@
       <c r="E143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3757,6 +4189,9 @@
       <c r="E144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3780,6 +4215,9 @@
       <c r="E145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="F145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3803,6 +4241,9 @@
       <c r="E146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3826,6 +4267,9 @@
       <c r="E147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3849,6 +4293,9 @@
       <c r="E148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3872,6 +4319,9 @@
       <c r="E149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="F149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3895,6 +4345,9 @@
       <c r="E150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="F150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3918,6 +4371,9 @@
       <c r="E151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="F151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3941,6 +4397,9 @@
       <c r="E152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3964,6 +4423,9 @@
       <c r="E153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3987,6 +4449,9 @@
       <c r="E154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="F154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4010,6 +4475,9 @@
       <c r="E155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4033,6 +4501,9 @@
       <c r="E156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4056,6 +4527,9 @@
       <c r="E157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4079,6 +4553,9 @@
       <c r="E158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4102,6 +4579,9 @@
       <c r="E159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="F159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4125,6 +4605,9 @@
       <c r="E160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4148,6 +4631,9 @@
       <c r="E161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4171,6 +4657,9 @@
       <c r="E162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="F162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4194,6 +4683,9 @@
       <c r="E163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="F163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4217,6 +4709,9 @@
       <c r="E164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="F164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4240,9 +4735,12 @@
       <c r="E165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E165"/>
+  <autoFilter ref="A1:F165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>2026-09-09 07:11</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,9 @@
       <c r="F2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +535,9 @@
       <c r="F3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,6 +564,9 @@
       <c r="F4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,6 +593,9 @@
       <c r="F5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,6 +622,9 @@
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +651,9 @@
       <c r="F7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,6 +680,9 @@
       <c r="F8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +709,9 @@
       <c r="F9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -708,6 +738,9 @@
       <c r="F10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -734,6 +767,9 @@
       <c r="F11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -760,6 +796,9 @@
       <c r="F12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,6 +825,9 @@
       <c r="F13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -812,6 +854,9 @@
       <c r="F14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -838,6 +883,9 @@
       <c r="F15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -864,6 +912,9 @@
       <c r="F16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,6 +941,9 @@
       <c r="F17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -916,6 +970,9 @@
       <c r="F18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -942,6 +999,9 @@
       <c r="F19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -968,6 +1028,9 @@
       <c r="F20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -994,6 +1057,9 @@
       <c r="F21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1020,6 +1086,9 @@
       <c r="F22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1046,6 +1115,9 @@
       <c r="F23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1072,6 +1144,9 @@
       <c r="F24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1098,6 +1173,9 @@
       <c r="F25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1124,6 +1202,9 @@
       <c r="F26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1150,6 +1231,9 @@
       <c r="F27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1176,6 +1260,9 @@
       <c r="F28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1202,6 +1289,9 @@
       <c r="F29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1228,6 +1318,9 @@
       <c r="F30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1254,6 +1347,9 @@
       <c r="F31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1280,6 +1376,9 @@
       <c r="F32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1405,9 @@
       <c r="F33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1332,6 +1434,9 @@
       <c r="F34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1358,6 +1463,9 @@
       <c r="F35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1384,6 +1492,9 @@
       <c r="F36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1410,6 +1521,9 @@
       <c r="F37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1436,6 +1550,9 @@
       <c r="F38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1462,6 +1579,9 @@
       <c r="F39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="G39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1488,6 +1608,9 @@
       <c r="F40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1514,6 +1637,9 @@
       <c r="F41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1540,6 +1666,9 @@
       <c r="F42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1566,6 +1695,9 @@
       <c r="F43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1592,6 +1724,9 @@
       <c r="F44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1618,6 +1753,9 @@
       <c r="F45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1644,6 +1782,9 @@
       <c r="F46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="G46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1670,6 +1811,9 @@
       <c r="F47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1696,6 +1840,9 @@
       <c r="F48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1722,6 +1869,9 @@
       <c r="F49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1748,6 +1898,9 @@
       <c r="F50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1774,6 +1927,9 @@
       <c r="F51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1800,6 +1956,9 @@
       <c r="F52" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1826,6 +1985,9 @@
       <c r="F53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1852,6 +2014,9 @@
       <c r="F54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1878,6 +2043,9 @@
       <c r="F55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1904,6 +2072,9 @@
       <c r="F56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1930,6 +2101,9 @@
       <c r="F57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1956,6 +2130,9 @@
       <c r="F58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1982,6 +2159,9 @@
       <c r="F59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="G59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2008,6 +2188,9 @@
       <c r="F60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2034,6 +2217,9 @@
       <c r="F61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G61" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2060,6 +2246,9 @@
       <c r="F62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2086,6 +2275,9 @@
       <c r="F63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2112,6 +2304,9 @@
       <c r="F64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2138,6 +2333,9 @@
       <c r="F65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2164,6 +2362,9 @@
       <c r="F66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2190,6 +2391,9 @@
       <c r="F67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G67" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2216,6 +2420,9 @@
       <c r="F68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2242,6 +2449,9 @@
       <c r="F69" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="G69" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2268,6 +2478,9 @@
       <c r="F70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2294,6 +2507,9 @@
       <c r="F71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2320,6 +2536,9 @@
       <c r="F72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2346,6 +2565,9 @@
       <c r="F73" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="G73" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2372,6 +2594,9 @@
       <c r="F74" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G74" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2398,6 +2623,9 @@
       <c r="F75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2424,6 +2652,9 @@
       <c r="F76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2450,6 +2681,9 @@
       <c r="F77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2476,6 +2710,9 @@
       <c r="F78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2502,6 +2739,9 @@
       <c r="F79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2528,6 +2768,9 @@
       <c r="F80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2554,6 +2797,9 @@
       <c r="F81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2580,6 +2826,9 @@
       <c r="F82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2606,6 +2855,9 @@
       <c r="F83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2632,6 +2884,9 @@
       <c r="F84" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G84" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2658,6 +2913,9 @@
       <c r="F85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2684,6 +2942,9 @@
       <c r="F86" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="G86" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2710,6 +2971,9 @@
       <c r="F87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2736,6 +3000,9 @@
       <c r="F88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2762,6 +3029,9 @@
       <c r="F89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2788,6 +3058,9 @@
       <c r="F90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2814,6 +3087,9 @@
       <c r="F91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2840,6 +3116,9 @@
       <c r="F92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2866,6 +3145,9 @@
       <c r="F93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2892,6 +3174,9 @@
       <c r="F94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2918,6 +3203,9 @@
       <c r="F95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2944,6 +3232,9 @@
       <c r="F96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2970,6 +3261,9 @@
       <c r="F97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2996,6 +3290,9 @@
       <c r="F98" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="G98" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3022,6 +3319,9 @@
       <c r="F99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3048,6 +3348,9 @@
       <c r="F100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3074,6 +3377,9 @@
       <c r="F101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3100,6 +3406,9 @@
       <c r="F102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3126,6 +3435,9 @@
       <c r="F103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3152,6 +3464,9 @@
       <c r="F104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3178,6 +3493,9 @@
       <c r="F105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3204,6 +3522,9 @@
       <c r="F106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3230,6 +3551,9 @@
       <c r="F107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="G107" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3256,6 +3580,9 @@
       <c r="F108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3282,6 +3609,9 @@
       <c r="F109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3308,6 +3638,9 @@
       <c r="F110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3334,6 +3667,9 @@
       <c r="F111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3360,6 +3696,9 @@
       <c r="F112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3386,6 +3725,9 @@
       <c r="F113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3412,6 +3754,9 @@
       <c r="F114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3438,6 +3783,9 @@
       <c r="F115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3464,6 +3812,9 @@
       <c r="F116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3490,6 +3841,9 @@
       <c r="F117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="G117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3516,6 +3870,9 @@
       <c r="F118" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3542,6 +3899,9 @@
       <c r="F119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3568,6 +3928,9 @@
       <c r="F120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3594,6 +3957,9 @@
       <c r="F121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3620,6 +3986,9 @@
       <c r="F122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3646,6 +4015,9 @@
       <c r="F123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3672,6 +4044,9 @@
       <c r="F124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3698,6 +4073,9 @@
       <c r="F125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3724,6 +4102,9 @@
       <c r="F126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3750,6 +4131,9 @@
       <c r="F127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3776,6 +4160,9 @@
       <c r="F128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3802,6 +4189,9 @@
       <c r="F129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3828,6 +4218,9 @@
       <c r="F130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3854,6 +4247,9 @@
       <c r="F131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3880,6 +4276,9 @@
       <c r="F132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="G132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3906,6 +4305,9 @@
       <c r="F133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3932,6 +4334,9 @@
       <c r="F134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3958,6 +4363,9 @@
       <c r="F135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3984,6 +4392,9 @@
       <c r="F136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4010,6 +4421,9 @@
       <c r="F137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4036,6 +4450,9 @@
       <c r="F138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4062,6 +4479,9 @@
       <c r="F139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4088,6 +4508,9 @@
       <c r="F140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4114,6 +4537,9 @@
       <c r="F141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4140,6 +4566,9 @@
       <c r="F142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4166,6 +4595,9 @@
       <c r="F143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4192,6 +4624,9 @@
       <c r="F144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4218,6 +4653,9 @@
       <c r="F145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="G145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4244,6 +4682,9 @@
       <c r="F146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4270,6 +4711,9 @@
       <c r="F147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4296,6 +4740,9 @@
       <c r="F148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4322,6 +4769,9 @@
       <c r="F149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="G149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4348,6 +4798,9 @@
       <c r="F150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4374,6 +4827,9 @@
       <c r="F151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="G151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4400,6 +4856,9 @@
       <c r="F152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4426,6 +4885,9 @@
       <c r="F153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4452,6 +4914,9 @@
       <c r="F154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="G154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4478,6 +4943,9 @@
       <c r="F155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4504,6 +4972,9 @@
       <c r="F156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4530,6 +5001,9 @@
       <c r="F157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4556,6 +5030,9 @@
       <c r="F158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4582,6 +5059,9 @@
       <c r="F159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="G159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4608,6 +5088,9 @@
       <c r="F160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4634,6 +5117,9 @@
       <c r="F161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4660,6 +5146,9 @@
       <c r="F162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="G162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4686,6 +5175,9 @@
       <c r="F163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="G163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4712,6 +5204,9 @@
       <c r="F164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="G164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4738,9 +5233,12 @@
       <c r="F165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F165"/>
+  <autoFilter ref="A1:G165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>2026-09-09 10:08</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +515,9 @@
       <c r="G2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="H2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +547,9 @@
       <c r="G3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +579,9 @@
       <c r="G4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="H4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +611,9 @@
       <c r="G5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,6 +643,9 @@
       <c r="G6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,6 +675,9 @@
       <c r="G7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="H7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +707,9 @@
       <c r="G8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +739,9 @@
       <c r="G9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -741,6 +771,9 @@
       <c r="G10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,6 +803,9 @@
       <c r="G11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +835,9 @@
       <c r="G12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -828,6 +867,9 @@
       <c r="G13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="H13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +899,9 @@
       <c r="G14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -886,6 +931,9 @@
       <c r="G15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -915,6 +963,9 @@
       <c r="G16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -944,6 +995,9 @@
       <c r="G17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="H17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -973,6 +1027,9 @@
       <c r="G18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1002,6 +1059,9 @@
       <c r="G19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="H19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1031,6 +1091,9 @@
       <c r="G20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="H20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1060,6 +1123,9 @@
       <c r="G21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1089,6 +1155,9 @@
       <c r="G22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1118,6 +1187,9 @@
       <c r="G23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1147,6 +1219,9 @@
       <c r="G24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1176,6 +1251,9 @@
       <c r="G25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1205,6 +1283,9 @@
       <c r="G26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="H26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1234,6 +1315,9 @@
       <c r="G27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1263,6 +1347,9 @@
       <c r="G28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="H28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1292,6 +1379,9 @@
       <c r="G29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="H29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,6 +1411,9 @@
       <c r="G30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H30" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1350,6 +1443,9 @@
       <c r="G31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H31" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1379,6 +1475,9 @@
       <c r="G32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H32" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1507,9 @@
       <c r="G33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1437,6 +1539,9 @@
       <c r="G34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1466,6 +1571,9 @@
       <c r="G35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1495,6 +1603,9 @@
       <c r="G36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1524,6 +1635,9 @@
       <c r="G37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1553,6 +1667,9 @@
       <c r="G38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H38" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1582,6 +1699,9 @@
       <c r="G39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="H39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,6 +1731,9 @@
       <c r="G40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1640,6 +1763,9 @@
       <c r="G41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1669,6 +1795,9 @@
       <c r="G42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1698,6 +1827,9 @@
       <c r="G43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1727,6 +1859,9 @@
       <c r="G44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1756,6 +1891,9 @@
       <c r="G45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1785,6 +1923,9 @@
       <c r="G46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="H46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1814,6 +1955,9 @@
       <c r="G47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1843,6 +1987,9 @@
       <c r="G48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1872,6 +2019,9 @@
       <c r="G49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1901,6 +2051,9 @@
       <c r="G50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1930,6 +2083,9 @@
       <c r="G51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="H51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1959,6 +2115,9 @@
       <c r="G52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1988,6 +2147,9 @@
       <c r="G53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2017,6 +2179,9 @@
       <c r="G54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2046,6 +2211,9 @@
       <c r="G55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2075,6 +2243,9 @@
       <c r="G56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2104,6 +2275,9 @@
       <c r="G57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2133,6 +2307,9 @@
       <c r="G58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2162,6 +2339,9 @@
       <c r="G59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="H59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2191,6 +2371,9 @@
       <c r="G60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2220,6 +2403,9 @@
       <c r="G61" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2249,6 +2435,9 @@
       <c r="G62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2278,6 +2467,9 @@
       <c r="G63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2307,6 +2499,9 @@
       <c r="G64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2336,6 +2531,9 @@
       <c r="G65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2365,6 +2563,9 @@
       <c r="G66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2394,6 +2595,9 @@
       <c r="G67" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2423,6 +2627,9 @@
       <c r="G68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2452,6 +2659,9 @@
       <c r="G69" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2481,6 +2691,9 @@
       <c r="G70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2510,6 +2723,9 @@
       <c r="G71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2539,6 +2755,9 @@
       <c r="G72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2568,6 +2787,9 @@
       <c r="G73" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2597,6 +2819,9 @@
       <c r="G74" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2626,6 +2851,9 @@
       <c r="G75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2655,6 +2883,9 @@
       <c r="G76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2684,6 +2915,9 @@
       <c r="G77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2713,6 +2947,9 @@
       <c r="G78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2742,6 +2979,9 @@
       <c r="G79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2771,6 +3011,9 @@
       <c r="G80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2800,6 +3043,9 @@
       <c r="G81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2829,6 +3075,9 @@
       <c r="G82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2858,6 +3107,9 @@
       <c r="G83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2887,6 +3139,9 @@
       <c r="G84" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H84" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2916,6 +3171,9 @@
       <c r="G85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2945,6 +3203,9 @@
       <c r="G86" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H86" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2974,6 +3235,9 @@
       <c r="G87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3003,6 +3267,9 @@
       <c r="G88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3032,6 +3299,9 @@
       <c r="G89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3061,6 +3331,9 @@
       <c r="G90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3090,6 +3363,9 @@
       <c r="G91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3119,6 +3395,9 @@
       <c r="G92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3148,6 +3427,9 @@
       <c r="G93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3177,6 +3459,9 @@
       <c r="G94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3206,6 +3491,9 @@
       <c r="G95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3235,6 +3523,9 @@
       <c r="G96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3264,6 +3555,9 @@
       <c r="G97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3293,6 +3587,9 @@
       <c r="G98" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="H98" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3322,6 +3619,9 @@
       <c r="G99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3351,6 +3651,9 @@
       <c r="G100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3380,6 +3683,9 @@
       <c r="G101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3409,6 +3715,9 @@
       <c r="G102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3438,6 +3747,9 @@
       <c r="G103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3467,6 +3779,9 @@
       <c r="G104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3496,6 +3811,9 @@
       <c r="G105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3525,6 +3843,9 @@
       <c r="G106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3554,6 +3875,9 @@
       <c r="G107" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="H107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3583,6 +3907,9 @@
       <c r="G108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3612,6 +3939,9 @@
       <c r="G109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3641,6 +3971,9 @@
       <c r="G110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3670,6 +4003,9 @@
       <c r="G111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3699,6 +4035,9 @@
       <c r="G112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3728,6 +4067,9 @@
       <c r="G113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3757,6 +4099,9 @@
       <c r="G114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3786,6 +4131,9 @@
       <c r="G115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3815,6 +4163,9 @@
       <c r="G116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3844,6 +4195,9 @@
       <c r="G117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3873,6 +4227,9 @@
       <c r="G118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3902,6 +4259,9 @@
       <c r="G119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3931,6 +4291,9 @@
       <c r="G120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3960,6 +4323,9 @@
       <c r="G121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3989,6 +4355,9 @@
       <c r="G122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4018,6 +4387,9 @@
       <c r="G123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4047,6 +4419,9 @@
       <c r="G124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4076,6 +4451,9 @@
       <c r="G125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4105,6 +4483,9 @@
       <c r="G126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4134,6 +4515,9 @@
       <c r="G127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4163,6 +4547,9 @@
       <c r="G128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4192,6 +4579,9 @@
       <c r="G129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4221,6 +4611,9 @@
       <c r="G130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4250,6 +4643,9 @@
       <c r="G131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4279,6 +4675,9 @@
       <c r="G132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="H132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4308,6 +4707,9 @@
       <c r="G133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4337,6 +4739,9 @@
       <c r="G134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4366,6 +4771,9 @@
       <c r="G135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4395,6 +4803,9 @@
       <c r="G136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4424,6 +4835,9 @@
       <c r="G137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4453,6 +4867,9 @@
       <c r="G138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4482,6 +4899,9 @@
       <c r="G139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4511,6 +4931,9 @@
       <c r="G140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4540,6 +4963,9 @@
       <c r="G141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4569,6 +4995,9 @@
       <c r="G142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4598,6 +5027,9 @@
       <c r="G143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4627,6 +5059,9 @@
       <c r="G144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4656,6 +5091,9 @@
       <c r="G145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="H145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4685,6 +5123,9 @@
       <c r="G146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4714,6 +5155,9 @@
       <c r="G147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4743,6 +5187,9 @@
       <c r="G148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4772,6 +5219,9 @@
       <c r="G149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="H149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4801,6 +5251,9 @@
       <c r="G150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4830,6 +5283,9 @@
       <c r="G151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="H151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4859,6 +5315,9 @@
       <c r="G152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4888,6 +5347,9 @@
       <c r="G153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4917,6 +5379,9 @@
       <c r="G154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="H154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4946,6 +5411,9 @@
       <c r="G155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4975,6 +5443,9 @@
       <c r="G156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5004,6 +5475,9 @@
       <c r="G157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5033,6 +5507,9 @@
       <c r="G158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5062,6 +5539,9 @@
       <c r="G159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="H159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5091,6 +5571,9 @@
       <c r="G160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5120,6 +5603,9 @@
       <c r="G161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5149,6 +5635,9 @@
       <c r="G162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="H162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5178,6 +5667,9 @@
       <c r="G163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="H163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5207,6 +5699,9 @@
       <c r="G164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="H164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5236,9 +5731,12 @@
       <c r="G165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G165"/>
+  <autoFilter ref="A1:H165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +487,11 @@
           <t>2026-09-09 13:11</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +524,9 @@
       <c r="H2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,6 +559,9 @@
       <c r="H3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,6 +594,9 @@
       <c r="H4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,6 +629,9 @@
       <c r="H5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,6 +664,9 @@
       <c r="H6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +699,9 @@
       <c r="H7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -710,6 +734,9 @@
       <c r="H8" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,6 +769,9 @@
       <c r="H9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -774,6 +804,9 @@
       <c r="H10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,6 +839,9 @@
       <c r="H11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -838,6 +874,9 @@
       <c r="H12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -870,6 +909,9 @@
       <c r="H13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -902,6 +944,9 @@
       <c r="H14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,6 +979,9 @@
       <c r="H15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -966,6 +1014,9 @@
       <c r="H16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -998,6 +1049,9 @@
       <c r="H17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1030,6 +1084,9 @@
       <c r="H18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1062,6 +1119,9 @@
       <c r="H19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1094,6 +1154,9 @@
       <c r="H20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1126,6 +1189,9 @@
       <c r="H21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1158,6 +1224,9 @@
       <c r="H22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1190,6 +1259,9 @@
       <c r="H23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1222,6 +1294,9 @@
       <c r="H24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,6 +1329,9 @@
       <c r="H25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1286,6 +1364,9 @@
       <c r="H26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1318,6 +1399,9 @@
       <c r="H27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1350,6 +1434,9 @@
       <c r="H28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="I28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1382,6 +1469,9 @@
       <c r="H29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1414,6 +1504,9 @@
       <c r="H30" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1446,6 +1539,9 @@
       <c r="H31" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1478,6 +1574,9 @@
       <c r="H32" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,6 +1609,9 @@
       <c r="H33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1542,6 +1644,9 @@
       <c r="H34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1574,6 +1679,9 @@
       <c r="H35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1606,6 +1714,9 @@
       <c r="H36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1638,6 +1749,9 @@
       <c r="H37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1670,6 +1784,9 @@
       <c r="H38" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1702,6 +1819,9 @@
       <c r="H39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="I39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1734,6 +1854,9 @@
       <c r="H40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1766,6 +1889,9 @@
       <c r="H41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1798,6 +1924,9 @@
       <c r="H42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1830,6 +1959,9 @@
       <c r="H43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1862,6 +1994,9 @@
       <c r="H44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1894,6 +2029,9 @@
       <c r="H45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1926,6 +2064,9 @@
       <c r="H46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="I46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1958,6 +2099,9 @@
       <c r="H47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1990,6 +2134,9 @@
       <c r="H48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2022,6 +2169,9 @@
       <c r="H49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I49" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2054,6 +2204,9 @@
       <c r="H50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2086,6 +2239,9 @@
       <c r="H51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="I51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2118,6 +2274,9 @@
       <c r="H52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2150,6 +2309,9 @@
       <c r="H53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2182,6 +2344,9 @@
       <c r="H54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2214,6 +2379,9 @@
       <c r="H55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2246,6 +2414,9 @@
       <c r="H56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2278,6 +2449,9 @@
       <c r="H57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,6 +2484,9 @@
       <c r="H58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2342,6 +2519,9 @@
       <c r="H59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="I59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2374,6 +2554,9 @@
       <c r="H60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2406,6 +2589,9 @@
       <c r="H61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="I61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2438,6 +2624,9 @@
       <c r="H62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,6 +2659,9 @@
       <c r="H63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2502,6 +2694,9 @@
       <c r="H64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,6 +2729,9 @@
       <c r="H65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2566,6 +2764,9 @@
       <c r="H66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2598,6 +2799,9 @@
       <c r="H67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2630,6 +2834,9 @@
       <c r="H68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2662,6 +2869,9 @@
       <c r="H69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2694,6 +2904,9 @@
       <c r="H70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2726,6 +2939,9 @@
       <c r="H71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2758,6 +2974,9 @@
       <c r="H72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2790,6 +3009,9 @@
       <c r="H73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2822,6 +3044,9 @@
       <c r="H74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2854,6 +3079,9 @@
       <c r="H75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2886,6 +3114,9 @@
       <c r="H76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2918,6 +3149,9 @@
       <c r="H77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2950,6 +3184,9 @@
       <c r="H78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2982,6 +3219,9 @@
       <c r="H79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3014,6 +3254,9 @@
       <c r="H80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3046,6 +3289,9 @@
       <c r="H81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3078,6 +3324,9 @@
       <c r="H82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3110,6 +3359,9 @@
       <c r="H83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3142,6 +3394,9 @@
       <c r="H84" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="I84" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3174,6 +3429,9 @@
       <c r="H85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3206,6 +3464,9 @@
       <c r="H86" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="I86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3238,6 +3499,9 @@
       <c r="H87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3270,6 +3534,9 @@
       <c r="H88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3302,6 +3569,9 @@
       <c r="H89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3334,6 +3604,9 @@
       <c r="H90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3366,6 +3639,9 @@
       <c r="H91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3398,6 +3674,9 @@
       <c r="H92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3430,6 +3709,9 @@
       <c r="H93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3462,6 +3744,9 @@
       <c r="H94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3494,6 +3779,9 @@
       <c r="H95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3526,6 +3814,9 @@
       <c r="H96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3558,6 +3849,9 @@
       <c r="H97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3590,6 +3884,9 @@
       <c r="H98" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="I98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3622,6 +3919,9 @@
       <c r="H99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3654,6 +3954,9 @@
       <c r="H100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3686,6 +3989,9 @@
       <c r="H101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3718,6 +4024,9 @@
       <c r="H102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I102" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3750,6 +4059,9 @@
       <c r="H103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3782,6 +4094,9 @@
       <c r="H104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3814,6 +4129,9 @@
       <c r="H105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3846,6 +4164,9 @@
       <c r="H106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3878,6 +4199,9 @@
       <c r="H107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3910,6 +4234,9 @@
       <c r="H108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3942,6 +4269,9 @@
       <c r="H109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I109" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3974,6 +4304,9 @@
       <c r="H110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4006,6 +4339,9 @@
       <c r="H111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4038,6 +4374,9 @@
       <c r="H112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4070,6 +4409,9 @@
       <c r="H113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4102,6 +4444,9 @@
       <c r="H114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4134,6 +4479,9 @@
       <c r="H115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4166,6 +4514,9 @@
       <c r="H116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4198,6 +4549,9 @@
       <c r="H117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="I117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4230,6 +4584,9 @@
       <c r="H118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4262,6 +4619,9 @@
       <c r="H119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4294,6 +4654,9 @@
       <c r="H120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4326,6 +4689,9 @@
       <c r="H121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4358,6 +4724,9 @@
       <c r="H122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4390,6 +4759,9 @@
       <c r="H123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I123" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4422,6 +4794,9 @@
       <c r="H124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4454,6 +4829,9 @@
       <c r="H125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4486,6 +4864,9 @@
       <c r="H126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4518,6 +4899,9 @@
       <c r="H127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4550,6 +4934,9 @@
       <c r="H128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4582,6 +4969,9 @@
       <c r="H129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4614,6 +5004,9 @@
       <c r="H130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4646,6 +5039,9 @@
       <c r="H131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4678,6 +5074,9 @@
       <c r="H132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="I132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4710,6 +5109,9 @@
       <c r="H133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4742,6 +5144,9 @@
       <c r="H134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4774,6 +5179,9 @@
       <c r="H135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4806,6 +5214,9 @@
       <c r="H136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4838,6 +5249,9 @@
       <c r="H137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4870,6 +5284,9 @@
       <c r="H138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4902,6 +5319,9 @@
       <c r="H139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4934,6 +5354,9 @@
       <c r="H140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4966,6 +5389,9 @@
       <c r="H141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4998,6 +5424,9 @@
       <c r="H142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5030,6 +5459,9 @@
       <c r="H143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5062,6 +5494,9 @@
       <c r="H144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5094,6 +5529,9 @@
       <c r="H145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="I145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5126,6 +5564,9 @@
       <c r="H146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5158,6 +5599,9 @@
       <c r="H147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5190,6 +5634,9 @@
       <c r="H148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5222,6 +5669,9 @@
       <c r="H149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="I149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5254,6 +5704,9 @@
       <c r="H150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5286,6 +5739,9 @@
       <c r="H151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="I151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5318,6 +5774,9 @@
       <c r="H152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5350,6 +5809,9 @@
       <c r="H153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5382,6 +5844,9 @@
       <c r="H154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="I154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5414,6 +5879,9 @@
       <c r="H155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5446,6 +5914,9 @@
       <c r="H156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5478,6 +5949,9 @@
       <c r="H157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5510,6 +5984,9 @@
       <c r="H158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5542,6 +6019,9 @@
       <c r="H159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="I159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5574,6 +6054,9 @@
       <c r="H160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5606,6 +6089,9 @@
       <c r="H161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5638,6 +6124,9 @@
       <c r="H162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="I162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5670,6 +6159,9 @@
       <c r="H163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="I163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5702,6 +6194,9 @@
       <c r="H164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="I164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5734,9 +6229,12 @@
       <c r="H165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H165"/>
+  <autoFilter ref="A1:I165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,6 +493,11 @@
           <t>2026-09-09 16:08</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +533,9 @@
       <c r="I2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="J2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +571,9 @@
       <c r="I3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="J3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +609,9 @@
       <c r="I4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,6 +647,9 @@
       <c r="I5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +685,9 @@
       <c r="I6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +723,9 @@
       <c r="I7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="J7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +761,9 @@
       <c r="I8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="J8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +799,9 @@
       <c r="I9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="J9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -807,6 +837,9 @@
       <c r="I10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,6 +875,9 @@
       <c r="I11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="J11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -877,6 +913,9 @@
       <c r="I12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -912,6 +951,9 @@
       <c r="I13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="J13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -947,6 +989,9 @@
       <c r="I14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -982,6 +1027,9 @@
       <c r="I15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1017,6 +1065,9 @@
       <c r="I16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,6 +1103,9 @@
       <c r="I17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="J17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1087,6 +1141,9 @@
       <c r="I18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1122,6 +1179,9 @@
       <c r="I19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="J19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1157,6 +1217,9 @@
       <c r="I20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="J20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1192,6 +1255,9 @@
       <c r="I21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="J21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1227,6 +1293,9 @@
       <c r="I22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1262,6 +1331,9 @@
       <c r="I23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1297,6 +1369,9 @@
       <c r="I24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1332,6 +1407,9 @@
       <c r="I25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1367,6 +1445,9 @@
       <c r="I26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="J26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1402,6 +1483,9 @@
       <c r="I27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1437,6 +1521,9 @@
       <c r="I28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="J28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1472,6 +1559,9 @@
       <c r="I29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="J29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1597,9 @@
       <c r="I30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1542,6 +1635,9 @@
       <c r="I31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1577,6 +1673,9 @@
       <c r="I32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1612,6 +1711,9 @@
       <c r="I33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1647,6 +1749,9 @@
       <c r="I34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1682,6 +1787,9 @@
       <c r="I35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1717,6 +1825,9 @@
       <c r="I36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1752,6 +1863,9 @@
       <c r="I37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1787,6 +1901,9 @@
       <c r="I38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="J38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1822,6 +1939,9 @@
       <c r="I39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="J39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1857,6 +1977,9 @@
       <c r="I40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1892,6 +2015,9 @@
       <c r="I41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,6 +2053,9 @@
       <c r="I42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1962,6 +2091,9 @@
       <c r="I43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1997,6 +2129,9 @@
       <c r="I44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2032,6 +2167,9 @@
       <c r="I45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2067,6 +2205,9 @@
       <c r="I46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="J46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2102,6 +2243,9 @@
       <c r="I47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2137,6 +2281,9 @@
       <c r="I48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2172,6 +2319,9 @@
       <c r="I49" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2207,6 +2357,9 @@
       <c r="I50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2242,6 +2395,9 @@
       <c r="I51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="J51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2277,6 +2433,9 @@
       <c r="I52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2312,6 +2471,9 @@
       <c r="I53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2347,6 +2509,9 @@
       <c r="I54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2382,6 +2547,9 @@
       <c r="I55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2417,6 +2585,9 @@
       <c r="I56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2452,6 +2623,9 @@
       <c r="I57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2487,6 +2661,9 @@
       <c r="I58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2522,6 +2699,9 @@
       <c r="I59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="J59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2557,6 +2737,9 @@
       <c r="I60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2592,6 +2775,9 @@
       <c r="I61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="J61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2627,6 +2813,9 @@
       <c r="I62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +2851,9 @@
       <c r="I63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2697,6 +2889,9 @@
       <c r="I64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2732,6 +2927,9 @@
       <c r="I65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2767,6 +2965,9 @@
       <c r="I66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2802,6 +3003,9 @@
       <c r="I67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2837,6 +3041,9 @@
       <c r="I68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2872,6 +3079,9 @@
       <c r="I69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2907,6 +3117,9 @@
       <c r="I70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2942,6 +3155,9 @@
       <c r="I71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2977,6 +3193,9 @@
       <c r="I72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="J72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3012,6 +3231,9 @@
       <c r="I73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3047,6 +3269,9 @@
       <c r="I74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3082,6 +3307,9 @@
       <c r="I75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3117,6 +3345,9 @@
       <c r="I76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3152,6 +3383,9 @@
       <c r="I77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3187,6 +3421,9 @@
       <c r="I78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3222,6 +3459,9 @@
       <c r="I79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3257,6 +3497,9 @@
       <c r="I80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3292,6 +3535,9 @@
       <c r="I81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3327,6 +3573,9 @@
       <c r="I82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3362,6 +3611,9 @@
       <c r="I83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3397,6 +3649,9 @@
       <c r="I84" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="J84" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3432,6 +3687,9 @@
       <c r="I85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3467,6 +3725,9 @@
       <c r="I86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3502,6 +3763,9 @@
       <c r="I87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3537,6 +3801,9 @@
       <c r="I88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3572,6 +3839,9 @@
       <c r="I89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3607,6 +3877,9 @@
       <c r="I90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3642,6 +3915,9 @@
       <c r="I91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3677,6 +3953,9 @@
       <c r="I92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3712,6 +3991,9 @@
       <c r="I93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3747,6 +4029,9 @@
       <c r="I94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3782,6 +4067,9 @@
       <c r="I95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3817,6 +4105,9 @@
       <c r="I96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3852,6 +4143,9 @@
       <c r="I97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3887,6 +4181,9 @@
       <c r="I98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3922,6 +4219,9 @@
       <c r="I99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3957,6 +4257,9 @@
       <c r="I100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3992,6 +4295,9 @@
       <c r="I101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4027,6 +4333,9 @@
       <c r="I102" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4062,6 +4371,9 @@
       <c r="I103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4097,6 +4409,9 @@
       <c r="I104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4132,6 +4447,9 @@
       <c r="I105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4167,6 +4485,9 @@
       <c r="I106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4202,6 +4523,9 @@
       <c r="I107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4237,6 +4561,9 @@
       <c r="I108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4272,6 +4599,9 @@
       <c r="I109" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4307,6 +4637,9 @@
       <c r="I110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4342,6 +4675,9 @@
       <c r="I111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4377,6 +4713,9 @@
       <c r="I112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4412,6 +4751,9 @@
       <c r="I113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4447,6 +4789,9 @@
       <c r="I114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4482,6 +4827,9 @@
       <c r="I115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4517,6 +4865,9 @@
       <c r="I116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4552,6 +4903,9 @@
       <c r="I117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="J117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4587,6 +4941,9 @@
       <c r="I118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4622,6 +4979,9 @@
       <c r="I119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4657,6 +5017,9 @@
       <c r="I120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4692,6 +5055,9 @@
       <c r="I121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4727,6 +5093,9 @@
       <c r="I122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4762,6 +5131,9 @@
       <c r="I123" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4797,6 +5169,9 @@
       <c r="I124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4832,6 +5207,9 @@
       <c r="I125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4867,6 +5245,9 @@
       <c r="I126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4902,6 +5283,9 @@
       <c r="I127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4937,6 +5321,9 @@
       <c r="I128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4972,6 +5359,9 @@
       <c r="I129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5007,6 +5397,9 @@
       <c r="I130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5042,6 +5435,9 @@
       <c r="I131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5077,6 +5473,9 @@
       <c r="I132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="J132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5112,6 +5511,9 @@
       <c r="I133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J133" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5147,6 +5549,9 @@
       <c r="I134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5182,6 +5587,9 @@
       <c r="I135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5217,6 +5625,9 @@
       <c r="I136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5252,6 +5663,9 @@
       <c r="I137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5287,6 +5701,9 @@
       <c r="I138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5322,6 +5739,9 @@
       <c r="I139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5357,6 +5777,9 @@
       <c r="I140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5392,6 +5815,9 @@
       <c r="I141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5427,6 +5853,9 @@
       <c r="I142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5462,6 +5891,9 @@
       <c r="I143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5497,6 +5929,9 @@
       <c r="I144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5532,6 +5967,9 @@
       <c r="I145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="J145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5567,6 +6005,9 @@
       <c r="I146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5602,6 +6043,9 @@
       <c r="I147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5637,6 +6081,9 @@
       <c r="I148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5672,6 +6119,9 @@
       <c r="I149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="J149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5707,6 +6157,9 @@
       <c r="I150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5742,6 +6195,9 @@
       <c r="I151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="J151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5777,6 +6233,9 @@
       <c r="I152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5812,6 +6271,9 @@
       <c r="I153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5847,6 +6309,9 @@
       <c r="I154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="J154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5882,6 +6347,9 @@
       <c r="I155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5917,6 +6385,9 @@
       <c r="I156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5952,6 +6423,9 @@
       <c r="I157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5987,6 +6461,9 @@
       <c r="I158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6022,6 +6499,9 @@
       <c r="I159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6057,6 +6537,9 @@
       <c r="I160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6092,6 +6575,9 @@
       <c r="I161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6127,6 +6613,9 @@
       <c r="I162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="J162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6162,6 +6651,9 @@
       <c r="I163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="J163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6197,6 +6689,9 @@
       <c r="I164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="J164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6232,9 +6727,12 @@
       <c r="I165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I165"/>
+  <autoFilter ref="A1:J165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +499,11 @@
           <t>2026-09-09 19:12</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-09 22:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,6 +542,9 @@
       <c r="J2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="K2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,6 +583,9 @@
       <c r="J3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="K3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,6 +624,9 @@
       <c r="J4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="K4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +665,9 @@
       <c r="J5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,6 +706,9 @@
       <c r="J6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,6 +747,9 @@
       <c r="J7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="K7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,6 +788,9 @@
       <c r="J8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="K8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -802,6 +829,9 @@
       <c r="J9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="K9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -840,6 +870,9 @@
       <c r="J10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,6 +911,9 @@
       <c r="J11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="K11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -916,6 +952,9 @@
       <c r="J12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -954,6 +993,9 @@
       <c r="J13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="K13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -992,6 +1034,9 @@
       <c r="J14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1030,6 +1075,9 @@
       <c r="J15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1068,6 +1116,9 @@
       <c r="J16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1106,6 +1157,9 @@
       <c r="J17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="K17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1144,6 +1198,9 @@
       <c r="J18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1182,6 +1239,9 @@
       <c r="J19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="K19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1220,6 +1280,9 @@
       <c r="J20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="K20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1258,6 +1321,9 @@
       <c r="J21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="K21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1296,6 +1362,9 @@
       <c r="J22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1334,6 +1403,9 @@
       <c r="J23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1372,6 +1444,9 @@
       <c r="J24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1410,6 +1485,9 @@
       <c r="J25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1448,6 +1526,9 @@
       <c r="J26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="K26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1486,6 +1567,9 @@
       <c r="J27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1524,6 +1608,9 @@
       <c r="J28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="K28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1562,6 +1649,9 @@
       <c r="J29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="K29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1600,6 +1690,9 @@
       <c r="J30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1638,6 +1731,9 @@
       <c r="J31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1676,6 +1772,9 @@
       <c r="J32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1714,6 +1813,9 @@
       <c r="J33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1752,6 +1854,9 @@
       <c r="J34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1790,6 +1895,9 @@
       <c r="J35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1828,6 +1936,9 @@
       <c r="J36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1866,6 +1977,9 @@
       <c r="J37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1904,6 +2018,9 @@
       <c r="J38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="K38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1942,6 +2059,9 @@
       <c r="J39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="K39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1980,6 +2100,9 @@
       <c r="J40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2018,6 +2141,9 @@
       <c r="J41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2056,6 +2182,9 @@
       <c r="J42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2094,6 +2223,9 @@
       <c r="J43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2132,6 +2264,9 @@
       <c r="J44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2170,6 +2305,9 @@
       <c r="J45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2208,6 +2346,9 @@
       <c r="J46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="K46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2246,6 +2387,9 @@
       <c r="J47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2284,6 +2428,9 @@
       <c r="J48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2322,6 +2469,9 @@
       <c r="J49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2360,6 +2510,9 @@
       <c r="J50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2398,6 +2551,9 @@
       <c r="J51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="K51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2436,6 +2592,9 @@
       <c r="J52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="K52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2474,6 +2633,9 @@
       <c r="J53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2512,6 +2674,9 @@
       <c r="J54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="K54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2550,6 +2715,9 @@
       <c r="J55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2588,6 +2756,9 @@
       <c r="J56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2626,6 +2797,9 @@
       <c r="J57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2664,6 +2838,9 @@
       <c r="J58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2702,6 +2879,9 @@
       <c r="J59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="K59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2740,6 +2920,9 @@
       <c r="J60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2778,6 +2961,9 @@
       <c r="J61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="K61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2816,6 +3002,9 @@
       <c r="J62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2854,6 +3043,9 @@
       <c r="J63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2892,6 +3084,9 @@
       <c r="J64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2930,6 +3125,9 @@
       <c r="J65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2968,6 +3166,9 @@
       <c r="J66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3006,6 +3207,9 @@
       <c r="J67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3044,6 +3248,9 @@
       <c r="J68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3082,6 +3289,9 @@
       <c r="J69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="K69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3120,6 +3330,9 @@
       <c r="J70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3158,6 +3371,9 @@
       <c r="J71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3196,6 +3412,9 @@
       <c r="J72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="K72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3234,6 +3453,9 @@
       <c r="J73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="K73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3272,6 +3494,9 @@
       <c r="J74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3310,6 +3535,9 @@
       <c r="J75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3348,6 +3576,9 @@
       <c r="J76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3386,6 +3617,9 @@
       <c r="J77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3424,6 +3658,9 @@
       <c r="J78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3462,6 +3699,9 @@
       <c r="J79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3500,6 +3740,9 @@
       <c r="J80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3538,6 +3781,9 @@
       <c r="J81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3576,6 +3822,9 @@
       <c r="J82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3614,6 +3863,9 @@
       <c r="J83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3652,6 +3904,9 @@
       <c r="J84" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="K84" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3690,6 +3945,9 @@
       <c r="J85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3728,6 +3986,9 @@
       <c r="J86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="K86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3766,6 +4027,9 @@
       <c r="J87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3804,6 +4068,9 @@
       <c r="J88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3842,6 +4109,9 @@
       <c r="J89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3880,6 +4150,9 @@
       <c r="J90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3918,6 +4191,9 @@
       <c r="J91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3956,6 +4232,9 @@
       <c r="J92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3994,6 +4273,9 @@
       <c r="J93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="K93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4032,6 +4314,9 @@
       <c r="J94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4070,6 +4355,9 @@
       <c r="J95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4108,6 +4396,9 @@
       <c r="J96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4146,6 +4437,9 @@
       <c r="J97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4184,6 +4478,9 @@
       <c r="J98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4222,6 +4519,9 @@
       <c r="J99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4260,6 +4560,9 @@
       <c r="J100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4298,6 +4601,9 @@
       <c r="J101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4336,6 +4642,9 @@
       <c r="J102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="K102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4374,6 +4683,9 @@
       <c r="J103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4412,6 +4724,9 @@
       <c r="J104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4450,6 +4765,9 @@
       <c r="J105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4488,6 +4806,9 @@
       <c r="J106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4526,6 +4847,9 @@
       <c r="J107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4564,6 +4888,9 @@
       <c r="J108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4602,6 +4929,9 @@
       <c r="J109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4640,6 +4970,9 @@
       <c r="J110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="K110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4678,6 +5011,9 @@
       <c r="J111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4716,6 +5052,9 @@
       <c r="J112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4754,6 +5093,9 @@
       <c r="J113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4792,6 +5134,9 @@
       <c r="J114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4830,6 +5175,9 @@
       <c r="J115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4868,6 +5216,9 @@
       <c r="J116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4906,6 +5257,9 @@
       <c r="J117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="K117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4944,6 +5298,9 @@
       <c r="J118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="K118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4982,6 +5339,9 @@
       <c r="J119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5020,6 +5380,9 @@
       <c r="J120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5058,6 +5421,9 @@
       <c r="J121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="K121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5096,6 +5462,9 @@
       <c r="J122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5134,6 +5503,9 @@
       <c r="J123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="K123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5172,6 +5544,9 @@
       <c r="J124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5210,6 +5585,9 @@
       <c r="J125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5248,6 +5626,9 @@
       <c r="J126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5286,6 +5667,9 @@
       <c r="J127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5324,6 +5708,9 @@
       <c r="J128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5362,6 +5749,9 @@
       <c r="J129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5400,6 +5790,9 @@
       <c r="J130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5438,6 +5831,9 @@
       <c r="J131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5476,6 +5872,9 @@
       <c r="J132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="K132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5514,6 +5913,9 @@
       <c r="J133" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="K133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5552,6 +5954,9 @@
       <c r="J134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="K134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5590,6 +5995,9 @@
       <c r="J135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5628,6 +6036,9 @@
       <c r="J136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5666,6 +6077,9 @@
       <c r="J137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5704,6 +6118,9 @@
       <c r="J138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5742,6 +6159,9 @@
       <c r="J139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5780,6 +6200,9 @@
       <c r="J140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5818,6 +6241,9 @@
       <c r="J141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5856,6 +6282,9 @@
       <c r="J142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5894,6 +6323,9 @@
       <c r="J143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5932,6 +6364,9 @@
       <c r="J144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5970,6 +6405,9 @@
       <c r="J145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="K145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6008,6 +6446,9 @@
       <c r="J146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6046,6 +6487,9 @@
       <c r="J147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6084,6 +6528,9 @@
       <c r="J148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="K148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6122,6 +6569,9 @@
       <c r="J149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="K149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6160,6 +6610,9 @@
       <c r="J150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="K150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6198,6 +6651,9 @@
       <c r="J151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="K151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6236,6 +6692,9 @@
       <c r="J152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6274,6 +6733,9 @@
       <c r="J153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6312,6 +6774,9 @@
       <c r="J154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="K154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6350,6 +6815,9 @@
       <c r="J155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="K155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6388,6 +6856,9 @@
       <c r="J156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6426,6 +6897,9 @@
       <c r="J157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6464,6 +6938,9 @@
       <c r="J158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6502,6 +6979,9 @@
       <c r="J159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="K159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6540,6 +7020,9 @@
       <c r="J160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6578,6 +7061,9 @@
       <c r="J161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6616,6 +7102,9 @@
       <c r="J162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="K162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6654,6 +7143,9 @@
       <c r="J163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="K163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6692,6 +7184,9 @@
       <c r="J164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="K164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6730,9 +7225,12 @@
       <c r="J165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J165"/>
+  <autoFilter ref="A1:K165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,42 +459,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-09 01:12</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-09 04:10</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-09 07:11</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-09 10:08</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-09 13:11</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-09 16:08</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-09 19:12</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-09 22:09</t>
+          <t>2026-09-10 01:13</t>
         </is>
       </c>
     </row>
@@ -524,27 +482,6 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>13.45</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,27 +502,6 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -606,27 +522,6 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>17.95</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,27 +542,6 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,27 +562,6 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -729,27 +582,6 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>19.49</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -768,27 +600,6 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K8" s="2" t="n">
         <v>20.49</v>
       </c>
     </row>
@@ -811,27 +622,6 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -852,27 +642,6 @@
       <c r="D10" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -893,27 +662,6 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>20.19</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,27 +682,6 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,27 +702,6 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>20.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1016,27 +722,6 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1057,27 +742,6 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,27 +762,6 @@
       <c r="D16" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1139,27 +782,6 @@
       <c r="D17" s="2" t="n">
         <v>20.75</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>20.75</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1180,27 +802,6 @@
       <c r="D18" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1221,27 +822,6 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>20.77</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1262,27 +842,6 @@
       <c r="D20" s="2" t="n">
         <v>20.65</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>20.65</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1303,27 +862,6 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>20.48</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1344,27 +882,6 @@
       <c r="D22" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1385,27 +902,6 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1426,27 +922,6 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1467,27 +942,6 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1508,27 +962,6 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>20.8</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1549,27 +982,6 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1590,27 +1002,6 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>20.54</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1631,27 +1022,6 @@
       <c r="D29" s="2" t="n">
         <v>20.75</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>20.75</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1670,27 +1040,6 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K30" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1711,27 +1060,6 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K31" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1752,27 +1080,6 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K32" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -1795,27 +1102,6 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1836,27 +1122,6 @@
       <c r="D34" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1877,27 +1142,6 @@
       <c r="D35" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1918,27 +1162,6 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1959,27 +1182,6 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1998,27 +1200,6 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="K38" s="2" t="n">
         <v>20.88</v>
       </c>
     </row>
@@ -2041,27 +1222,6 @@
       <c r="D39" s="2" t="n">
         <v>20.98</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>20.98</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2082,27 +1242,6 @@
       <c r="D40" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2123,27 +1262,6 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2164,27 +1282,6 @@
       <c r="D42" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2205,27 +1302,6 @@
       <c r="D43" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2246,27 +1322,6 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2287,27 +1342,6 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2328,27 +1362,6 @@
       <c r="D46" s="2" t="n">
         <v>21.05</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>21.05</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2369,27 +1382,6 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2410,27 +1402,6 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2449,27 +1420,6 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K49" s="2" t="n">
         <v>21.19</v>
       </c>
     </row>
@@ -2492,27 +1442,6 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2533,27 +1462,6 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>20.85</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2572,27 +1480,6 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="K52" s="2" t="n">
         <v>22.35</v>
       </c>
     </row>
@@ -2615,27 +1502,6 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2656,27 +1522,6 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>21.79</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2697,27 +1542,6 @@
       <c r="D55" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2738,27 +1562,6 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2777,27 +1580,6 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K57" s="2" t="n">
         <v>20.89</v>
       </c>
     </row>
@@ -2820,27 +1602,6 @@
       <c r="D58" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2861,27 +1622,6 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>22.2</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2902,27 +1642,6 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2941,27 +1660,6 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="K61" s="2" t="n">
         <v>21.55</v>
       </c>
     </row>
@@ -2984,27 +1682,6 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3025,27 +1702,6 @@
       <c r="D63" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3066,27 +1722,6 @@
       <c r="D64" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3107,27 +1742,6 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K65" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3148,27 +1762,6 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3187,27 +1780,6 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K67" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -3230,27 +1802,6 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3269,27 +1820,6 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="K69" s="2" t="n">
         <v>21.65</v>
       </c>
     </row>
@@ -3312,27 +1842,6 @@
       <c r="D70" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3353,27 +1862,6 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K71" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3392,27 +1880,6 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="K72" s="2" t="n">
         <v>21.29</v>
       </c>
     </row>
@@ -3433,27 +1900,6 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="K73" s="2" t="n">
         <v>21.65</v>
       </c>
     </row>
@@ -3474,27 +1920,6 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K74" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -3517,27 +1942,6 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3558,27 +1962,6 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3599,27 +1982,6 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3640,27 +2002,6 @@
       <c r="D78" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3681,27 +2022,6 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3720,27 +2040,6 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K80" s="2" t="n">
         <v>21.39</v>
       </c>
     </row>
@@ -3763,27 +2062,6 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3804,27 +2082,6 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3845,27 +2102,6 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3884,27 +2120,6 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="K84" s="2" t="n">
         <v>21.85</v>
       </c>
     </row>
@@ -3927,27 +2142,6 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3966,27 +2160,6 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="K86" s="2" t="n">
         <v>21.65</v>
       </c>
     </row>
@@ -4009,27 +2182,6 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4050,27 +2202,6 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4091,27 +2222,6 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4132,27 +2242,6 @@
       <c r="D90" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4173,27 +2262,6 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4214,27 +2282,6 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4255,27 +2302,6 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
-      <c r="E93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>21.89</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4296,27 +2322,6 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4337,27 +2342,6 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4378,27 +2362,6 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4419,27 +2382,6 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4458,27 +2400,6 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K98" s="2" t="n">
         <v>20.95</v>
       </c>
     </row>
@@ -4501,27 +2422,6 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4542,27 +2442,6 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4583,27 +2462,6 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4622,27 +2480,6 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="K102" s="2" t="n">
         <v>22.79</v>
       </c>
     </row>
@@ -4665,27 +2502,6 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4706,27 +2522,6 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4747,27 +2542,6 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4788,27 +2562,6 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4827,27 +2580,6 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K107" s="2" t="n">
         <v>21.09</v>
       </c>
     </row>
@@ -4870,27 +2602,6 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4909,27 +2620,6 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K109" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -4952,27 +2642,6 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4993,27 +2662,6 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5034,27 +2682,6 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5075,27 +2702,6 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5116,27 +2722,6 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5157,27 +2742,6 @@
       <c r="D115" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5198,27 +2762,6 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5239,27 +2782,6 @@
       <c r="D117" s="2" t="n">
         <v>21.85</v>
       </c>
-      <c r="E117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>21.85</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5278,27 +2800,6 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="K118" s="2" t="n">
         <v>21.75</v>
       </c>
     </row>
@@ -5321,27 +2822,6 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5362,27 +2842,6 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5401,27 +2860,6 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="K121" s="2" t="n">
         <v>21.75</v>
       </c>
     </row>
@@ -5444,27 +2882,6 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5483,27 +2900,6 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="K123" s="2" t="n">
         <v>21.69</v>
       </c>
     </row>
@@ -5526,27 +2922,6 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5567,27 +2942,6 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5608,27 +2962,6 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5649,27 +2982,6 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5690,27 +3002,6 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5731,27 +3022,6 @@
       <c r="D129" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5772,27 +3042,6 @@
       <c r="D130" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5813,27 +3062,6 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5854,27 +3082,6 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="E132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>21.6</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5893,27 +3100,6 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K133" s="2" t="n">
         <v>22.3</v>
       </c>
     </row>
@@ -5936,27 +3122,6 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="E134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>21.7</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5977,27 +3142,6 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6018,27 +3162,6 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6059,27 +3182,6 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6100,27 +3202,6 @@
       <c r="D138" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K138" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6141,27 +3222,6 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K139" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6182,27 +3242,6 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6223,27 +3262,6 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6264,27 +3282,6 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6305,27 +3302,6 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6346,27 +3322,6 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6387,27 +3342,6 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
-      <c r="E145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>22.29</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6428,27 +3362,6 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6469,27 +3382,6 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K147" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6510,27 +3402,6 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
-      <c r="E148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="K148" s="2" t="n">
-        <v>22.35</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6551,27 +3422,6 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
-      <c r="E149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="K149" s="2" t="n">
-        <v>22.49</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6592,27 +3442,6 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K150" s="2" t="n">
-        <v>22.5</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6633,27 +3462,6 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
-      <c r="E151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="K151" s="2" t="n">
-        <v>22.59</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6674,27 +3482,6 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6715,27 +3502,6 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6756,27 +3522,6 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>22.7</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6797,27 +3542,6 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>22.79</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6838,27 +3562,6 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6879,27 +3582,6 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K157" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6920,27 +3602,6 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K158" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6961,27 +3622,6 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
-      <c r="E159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="K159" s="2" t="n">
-        <v>23.99</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7002,27 +3642,6 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K160" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7043,27 +3662,6 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K161" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7084,27 +3682,6 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
-      <c r="E162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="K162" s="2" t="n">
-        <v>23.49</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7125,27 +3702,6 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K163" s="2" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7166,27 +3722,6 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="K164" s="2" t="n">
-        <v>24.25</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7207,30 +3742,9 @@
       <c r="D165" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K165" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K165"/>
+  <autoFilter ref="A1:D165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,13 +432,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,6 +463,11 @@
           <t>2026-09-10 01:13</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,6 +488,9 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,6 +511,9 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -522,6 +534,9 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +557,9 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,6 +580,9 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -582,6 +603,9 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,6 +626,9 @@
       <c r="D8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="E8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +649,9 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,6 +672,9 @@
       <c r="D10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -662,6 +695,9 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,6 +718,9 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -702,6 +741,9 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,6 +764,9 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,6 +787,9 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -762,6 +810,9 @@
       <c r="D16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,6 +833,9 @@
       <c r="D17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="E17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -802,6 +856,9 @@
       <c r="D18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -822,6 +879,9 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,6 +902,9 @@
       <c r="D20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,6 +925,9 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -882,6 +948,9 @@
       <c r="D22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -902,6 +971,9 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -922,6 +994,9 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -942,6 +1017,9 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -962,6 +1040,9 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="E26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -982,6 +1063,9 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1002,6 +1086,9 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1022,6 +1109,9 @@
       <c r="D29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="E29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1042,6 +1132,9 @@
       <c r="D30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1062,6 +1155,9 @@
       <c r="D31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1082,6 +1178,9 @@
       <c r="D32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1102,6 +1201,9 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1122,6 +1224,9 @@
       <c r="D34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1142,6 +1247,9 @@
       <c r="D35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1162,6 +1270,9 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1182,6 +1293,9 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1202,6 +1316,9 @@
       <c r="D38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="E38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1222,6 +1339,9 @@
       <c r="D39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="E39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1242,6 +1362,9 @@
       <c r="D40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1262,6 +1385,9 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1282,6 +1408,9 @@
       <c r="D42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1302,6 +1431,9 @@
       <c r="D43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1322,6 +1454,9 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1342,6 +1477,9 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1362,6 +1500,9 @@
       <c r="D46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="E46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1382,6 +1523,9 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1402,6 +1546,9 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1422,6 +1569,9 @@
       <c r="D49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1442,6 +1592,9 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1462,6 +1615,9 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="E51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1482,6 +1638,9 @@
       <c r="D52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1502,6 +1661,9 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1522,6 +1684,9 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1542,6 +1707,9 @@
       <c r="D55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1562,6 +1730,9 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1582,6 +1753,9 @@
       <c r="D57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1602,6 +1776,9 @@
       <c r="D58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1622,6 +1799,9 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="E59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1642,6 +1822,9 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1662,6 +1845,9 @@
       <c r="D61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="E61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1682,6 +1868,9 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1702,6 +1891,9 @@
       <c r="D63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1722,6 +1914,9 @@
       <c r="D64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1742,6 +1937,9 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1762,6 +1960,9 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1782,6 +1983,9 @@
       <c r="D67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1802,6 +2006,9 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1822,6 +2029,9 @@
       <c r="D69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1842,6 +2052,9 @@
       <c r="D70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1862,6 +2075,9 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1882,6 +2098,9 @@
       <c r="D72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="E72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1902,6 +2121,9 @@
       <c r="D73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1922,6 +2144,9 @@
       <c r="D74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1942,6 +2167,9 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1962,6 +2190,9 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1982,6 +2213,9 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2002,6 +2236,9 @@
       <c r="D78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2022,6 +2259,9 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2042,6 +2282,9 @@
       <c r="D80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2062,6 +2305,9 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2082,6 +2328,9 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2102,6 +2351,9 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2122,6 +2374,9 @@
       <c r="D84" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="E84" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2142,6 +2397,9 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2162,6 +2420,9 @@
       <c r="D86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2182,6 +2443,9 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2202,6 +2466,9 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2222,6 +2489,9 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2242,6 +2512,9 @@
       <c r="D90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2262,6 +2535,9 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2282,6 +2558,9 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2302,6 +2581,9 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="E93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2322,6 +2604,9 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2342,6 +2627,9 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2362,6 +2650,9 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2382,6 +2673,9 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2402,6 +2696,9 @@
       <c r="D98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2422,6 +2719,9 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2442,6 +2742,9 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2462,6 +2765,9 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2482,6 +2788,9 @@
       <c r="D102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2502,6 +2811,9 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2522,6 +2834,9 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2542,6 +2857,9 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2562,6 +2880,9 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2582,6 +2903,9 @@
       <c r="D107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2602,6 +2926,9 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2622,6 +2949,9 @@
       <c r="D109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2642,6 +2972,9 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2662,6 +2995,9 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2682,6 +3018,9 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2702,6 +3041,9 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2722,6 +3064,9 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2742,6 +3087,9 @@
       <c r="D115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2762,6 +3110,9 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2782,6 +3133,9 @@
       <c r="D117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="E117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2802,6 +3156,9 @@
       <c r="D118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2822,6 +3179,9 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2842,6 +3202,9 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2862,6 +3225,9 @@
       <c r="D121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2882,6 +3248,9 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2902,6 +3271,9 @@
       <c r="D123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="E123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2922,6 +3294,9 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2942,6 +3317,9 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2962,6 +3340,9 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2982,6 +3363,9 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3002,6 +3386,9 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3022,6 +3409,9 @@
       <c r="D129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3042,6 +3432,9 @@
       <c r="D130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3062,6 +3455,9 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3082,6 +3478,9 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="E132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3102,6 +3501,9 @@
       <c r="D133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3122,6 +3524,9 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="E134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3142,6 +3547,9 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3162,6 +3570,9 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3182,6 +3593,9 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3202,6 +3616,9 @@
       <c r="D138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3222,6 +3639,9 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3242,6 +3662,9 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3262,6 +3685,9 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3282,6 +3708,9 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3302,6 +3731,9 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3322,6 +3754,9 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3342,6 +3777,9 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="E145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3362,6 +3800,9 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3382,6 +3823,9 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3402,6 +3846,9 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3422,6 +3869,9 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="E149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3442,6 +3892,9 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="E150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3462,6 +3915,9 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="E151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3482,6 +3938,9 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3502,6 +3961,9 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3522,6 +3984,9 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="E154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3542,6 +4007,9 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3562,6 +4030,9 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3582,6 +4053,9 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3602,6 +4076,9 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3622,6 +4099,9 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="E159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3642,6 +4122,9 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3662,6 +4145,9 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3682,6 +4168,9 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="E162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3702,6 +4191,9 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="E163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3722,6 +4214,9 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="E164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3742,9 +4237,12 @@
       <c r="D165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D165"/>
+  <autoFilter ref="A1:E165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,11 @@
           <t>2026-09-10 04:09</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10 07:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +497,9 @@
       <c r="E2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,6 +523,9 @@
       <c r="E3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="F3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +549,9 @@
       <c r="E4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,6 +575,9 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +601,9 @@
       <c r="E6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -606,6 +627,9 @@
       <c r="E7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="F7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -629,6 +653,9 @@
       <c r="E8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -652,6 +679,9 @@
       <c r="E9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="F9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -675,6 +705,9 @@
       <c r="E10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +731,9 @@
       <c r="E11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="F11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -721,6 +757,9 @@
       <c r="E12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,6 +783,9 @@
       <c r="E13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="F13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -767,6 +809,9 @@
       <c r="E14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -790,6 +835,9 @@
       <c r="E15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -813,6 +861,9 @@
       <c r="E16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -836,6 +887,9 @@
       <c r="E17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="F17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -859,6 +913,9 @@
       <c r="E18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -882,6 +939,9 @@
       <c r="E19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="F19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -905,6 +965,9 @@
       <c r="E20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="F20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -928,6 +991,9 @@
       <c r="E21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="F21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -951,6 +1017,9 @@
       <c r="E22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -974,6 +1043,9 @@
       <c r="E23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -997,6 +1069,9 @@
       <c r="E24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1020,6 +1095,9 @@
       <c r="E25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1043,6 +1121,9 @@
       <c r="E26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="F26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1066,6 +1147,9 @@
       <c r="E27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1089,6 +1173,9 @@
       <c r="E28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="F28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1112,6 +1199,9 @@
       <c r="E29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="F29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1135,6 +1225,9 @@
       <c r="E30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1158,6 +1251,9 @@
       <c r="E31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1181,6 +1277,9 @@
       <c r="E32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1204,6 +1303,9 @@
       <c r="E33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1227,6 +1329,9 @@
       <c r="E34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1250,6 +1355,9 @@
       <c r="E35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1273,6 +1381,9 @@
       <c r="E36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1296,6 +1407,9 @@
       <c r="E37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1319,6 +1433,9 @@
       <c r="E38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="F38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1342,6 +1459,9 @@
       <c r="E39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="F39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1365,6 +1485,9 @@
       <c r="E40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F40" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1388,6 +1511,9 @@
       <c r="E41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1411,6 +1537,9 @@
       <c r="E42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1434,6 +1563,9 @@
       <c r="E43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1457,6 +1589,9 @@
       <c r="E44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1480,6 +1615,9 @@
       <c r="E45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1503,6 +1641,9 @@
       <c r="E46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="F46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1526,6 +1667,9 @@
       <c r="E47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1549,6 +1693,9 @@
       <c r="E48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1572,6 +1719,9 @@
       <c r="E49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1595,6 +1745,9 @@
       <c r="E50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1618,6 +1771,9 @@
       <c r="E51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="F51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1641,6 +1797,9 @@
       <c r="E52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1664,6 +1823,9 @@
       <c r="E53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1687,6 +1849,9 @@
       <c r="E54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1710,6 +1875,9 @@
       <c r="E55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1733,6 +1901,9 @@
       <c r="E56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1756,6 +1927,9 @@
       <c r="E57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1779,6 +1953,9 @@
       <c r="E58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F58" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1802,6 +1979,9 @@
       <c r="E59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="F59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1825,6 +2005,9 @@
       <c r="E60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1848,6 +2031,9 @@
       <c r="E61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="F61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1871,6 +2057,9 @@
       <c r="E62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1894,6 +2083,9 @@
       <c r="E63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F63" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1917,6 +2109,9 @@
       <c r="E64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F64" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1940,6 +2135,9 @@
       <c r="E65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1963,6 +2161,9 @@
       <c r="E66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1986,6 +2187,9 @@
       <c r="E67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2009,6 +2213,9 @@
       <c r="E68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2032,6 +2239,9 @@
       <c r="E69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2055,6 +2265,9 @@
       <c r="E70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2078,6 +2291,9 @@
       <c r="E71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2101,6 +2317,9 @@
       <c r="E72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="F72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2124,6 +2343,9 @@
       <c r="E73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2147,6 +2369,9 @@
       <c r="E74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2170,6 +2395,9 @@
       <c r="E75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2193,6 +2421,9 @@
       <c r="E76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2216,6 +2447,9 @@
       <c r="E77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2239,6 +2473,9 @@
       <c r="E78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2262,6 +2499,9 @@
       <c r="E79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2285,6 +2525,9 @@
       <c r="E80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2308,6 +2551,9 @@
       <c r="E81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2331,6 +2577,9 @@
       <c r="E82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2354,6 +2603,9 @@
       <c r="E83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2377,6 +2629,9 @@
       <c r="E84" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="F84" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2400,6 +2655,9 @@
       <c r="E85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2423,6 +2681,9 @@
       <c r="E86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2446,6 +2707,9 @@
       <c r="E87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2469,6 +2733,9 @@
       <c r="E88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2492,6 +2759,9 @@
       <c r="E89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2515,6 +2785,9 @@
       <c r="E90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2538,6 +2811,9 @@
       <c r="E91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2561,6 +2837,9 @@
       <c r="E92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2584,6 +2863,9 @@
       <c r="E93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="F93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2607,6 +2889,9 @@
       <c r="E94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2630,6 +2915,9 @@
       <c r="E95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2653,6 +2941,9 @@
       <c r="E96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2676,6 +2967,9 @@
       <c r="E97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2699,6 +2993,9 @@
       <c r="E98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2722,6 +3019,9 @@
       <c r="E99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2745,6 +3045,9 @@
       <c r="E100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2768,6 +3071,9 @@
       <c r="E101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2791,6 +3097,9 @@
       <c r="E102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2814,6 +3123,9 @@
       <c r="E103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2837,6 +3149,9 @@
       <c r="E104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2860,6 +3175,9 @@
       <c r="E105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2883,6 +3201,9 @@
       <c r="E106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2906,6 +3227,9 @@
       <c r="E107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2929,6 +3253,9 @@
       <c r="E108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2952,6 +3279,9 @@
       <c r="E109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2975,6 +3305,9 @@
       <c r="E110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2998,6 +3331,9 @@
       <c r="E111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3021,6 +3357,9 @@
       <c r="E112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3044,6 +3383,9 @@
       <c r="E113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3067,6 +3409,9 @@
       <c r="E114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3090,6 +3435,9 @@
       <c r="E115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3113,6 +3461,9 @@
       <c r="E116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3136,6 +3487,9 @@
       <c r="E117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="F117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3159,6 +3513,9 @@
       <c r="E118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3182,6 +3539,9 @@
       <c r="E119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3205,6 +3565,9 @@
       <c r="E120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3228,6 +3591,9 @@
       <c r="E121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3251,6 +3617,9 @@
       <c r="E122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3274,6 +3643,9 @@
       <c r="E123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="F123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3297,6 +3669,9 @@
       <c r="E124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3320,6 +3695,9 @@
       <c r="E125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3343,6 +3721,9 @@
       <c r="E126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3366,6 +3747,9 @@
       <c r="E127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3389,6 +3773,9 @@
       <c r="E128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3412,6 +3799,9 @@
       <c r="E129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3435,6 +3825,9 @@
       <c r="E130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F130" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3458,6 +3851,9 @@
       <c r="E131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3481,6 +3877,9 @@
       <c r="E132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="F132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3504,6 +3903,9 @@
       <c r="E133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3527,6 +3929,9 @@
       <c r="E134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="F134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3550,6 +3955,9 @@
       <c r="E135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3573,6 +3981,9 @@
       <c r="E136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3596,6 +4007,9 @@
       <c r="E137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3619,6 +4033,9 @@
       <c r="E138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3642,6 +4059,9 @@
       <c r="E139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3665,6 +4085,9 @@
       <c r="E140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3688,6 +4111,9 @@
       <c r="E141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3711,6 +4137,9 @@
       <c r="E142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3734,6 +4163,9 @@
       <c r="E143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3757,6 +4189,9 @@
       <c r="E144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3780,6 +4215,9 @@
       <c r="E145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="F145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3803,6 +4241,9 @@
       <c r="E146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3826,6 +4267,9 @@
       <c r="E147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3849,6 +4293,9 @@
       <c r="E148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3872,6 +4319,9 @@
       <c r="E149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="F149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3895,6 +4345,9 @@
       <c r="E150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="F150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3918,6 +4371,9 @@
       <c r="E151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="F151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3941,6 +4397,9 @@
       <c r="E152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3964,6 +4423,9 @@
       <c r="E153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3987,6 +4449,9 @@
       <c r="E154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="F154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4010,6 +4475,9 @@
       <c r="E155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4033,6 +4501,9 @@
       <c r="E156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4056,6 +4527,9 @@
       <c r="E157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4079,6 +4553,9 @@
       <c r="E158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4102,6 +4579,9 @@
       <c r="E159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="F159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4125,6 +4605,9 @@
       <c r="E160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4148,6 +4631,9 @@
       <c r="E161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4171,6 +4657,9 @@
       <c r="E162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="F162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4194,6 +4683,9 @@
       <c r="E163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="F163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4217,6 +4709,9 @@
       <c r="E164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="F164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4240,9 +4735,12 @@
       <c r="E165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E165"/>
+  <autoFilter ref="A1:F165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>2026-09-10 07:12</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,9 @@
       <c r="F2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +535,9 @@
       <c r="F3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,6 +564,9 @@
       <c r="F4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,6 +593,9 @@
       <c r="F5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,6 +622,9 @@
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +651,9 @@
       <c r="F7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,6 +680,9 @@
       <c r="F8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +709,9 @@
       <c r="F9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -708,6 +738,9 @@
       <c r="F10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -734,6 +767,9 @@
       <c r="F11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -760,6 +796,9 @@
       <c r="F12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,6 +825,9 @@
       <c r="F13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -812,6 +854,9 @@
       <c r="F14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -838,6 +883,9 @@
       <c r="F15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -864,6 +912,9 @@
       <c r="F16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,6 +941,9 @@
       <c r="F17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -916,6 +970,9 @@
       <c r="F18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -942,6 +999,9 @@
       <c r="F19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -968,6 +1028,9 @@
       <c r="F20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -994,6 +1057,9 @@
       <c r="F21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1020,6 +1086,9 @@
       <c r="F22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1046,6 +1115,9 @@
       <c r="F23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1072,6 +1144,9 @@
       <c r="F24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1098,6 +1173,9 @@
       <c r="F25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1124,6 +1202,9 @@
       <c r="F26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1150,6 +1231,9 @@
       <c r="F27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1176,6 +1260,9 @@
       <c r="F28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1202,6 +1289,9 @@
       <c r="F29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1228,6 +1318,9 @@
       <c r="F30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1254,6 +1347,9 @@
       <c r="F31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1280,6 +1376,9 @@
       <c r="F32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1405,9 @@
       <c r="F33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1332,6 +1434,9 @@
       <c r="F34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1358,6 +1463,9 @@
       <c r="F35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1384,6 +1492,9 @@
       <c r="F36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1410,6 +1521,9 @@
       <c r="F37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1436,6 +1550,9 @@
       <c r="F38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="G38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1462,6 +1579,9 @@
       <c r="F39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="G39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1488,6 +1608,9 @@
       <c r="F40" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1514,6 +1637,9 @@
       <c r="F41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1540,6 +1666,9 @@
       <c r="F42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1566,6 +1695,9 @@
       <c r="F43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1592,6 +1724,9 @@
       <c r="F44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1618,6 +1753,9 @@
       <c r="F45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1644,6 +1782,9 @@
       <c r="F46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="G46" s="2" t="n">
+        <v>21.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1670,6 +1811,9 @@
       <c r="F47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1696,6 +1840,9 @@
       <c r="F48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1722,6 +1869,9 @@
       <c r="F49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1748,6 +1898,9 @@
       <c r="F50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1774,6 +1927,9 @@
       <c r="F51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1800,6 +1956,9 @@
       <c r="F52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1826,6 +1985,9 @@
       <c r="F53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1852,6 +2014,9 @@
       <c r="F54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1878,6 +2043,9 @@
       <c r="F55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1904,6 +2072,9 @@
       <c r="F56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1930,6 +2101,9 @@
       <c r="F57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1956,6 +2130,9 @@
       <c r="F58" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1982,6 +2159,9 @@
       <c r="F59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="G59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2008,6 +2188,9 @@
       <c r="F60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2034,6 +2217,9 @@
       <c r="F61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="G61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2060,6 +2246,9 @@
       <c r="F62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2086,6 +2275,9 @@
       <c r="F63" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2112,6 +2304,9 @@
       <c r="F64" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2138,6 +2333,9 @@
       <c r="F65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2164,6 +2362,9 @@
       <c r="F66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2190,6 +2391,9 @@
       <c r="F67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2216,6 +2420,9 @@
       <c r="F68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2242,6 +2449,9 @@
       <c r="F69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2268,6 +2478,9 @@
       <c r="F70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2294,6 +2507,9 @@
       <c r="F71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2320,6 +2536,9 @@
       <c r="F72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="G72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2346,6 +2565,9 @@
       <c r="F73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2372,6 +2594,9 @@
       <c r="F74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2398,6 +2623,9 @@
       <c r="F75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2424,6 +2652,9 @@
       <c r="F76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2450,6 +2681,9 @@
       <c r="F77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2476,6 +2710,9 @@
       <c r="F78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G78" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2502,6 +2739,9 @@
       <c r="F79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2528,6 +2768,9 @@
       <c r="F80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2554,6 +2797,9 @@
       <c r="F81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2580,6 +2826,9 @@
       <c r="F82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2606,6 +2855,9 @@
       <c r="F83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2632,6 +2884,9 @@
       <c r="F84" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="G84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2658,6 +2913,9 @@
       <c r="F85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2684,6 +2942,9 @@
       <c r="F86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2710,6 +2971,9 @@
       <c r="F87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2736,6 +3000,9 @@
       <c r="F88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2762,6 +3029,9 @@
       <c r="F89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2788,6 +3058,9 @@
       <c r="F90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G90" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2814,6 +3087,9 @@
       <c r="F91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2840,6 +3116,9 @@
       <c r="F92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2866,6 +3145,9 @@
       <c r="F93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2892,6 +3174,9 @@
       <c r="F94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2918,6 +3203,9 @@
       <c r="F95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2944,6 +3232,9 @@
       <c r="F96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2970,6 +3261,9 @@
       <c r="F97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2996,6 +3290,9 @@
       <c r="F98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3022,6 +3319,9 @@
       <c r="F99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3048,6 +3348,9 @@
       <c r="F100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3074,6 +3377,9 @@
       <c r="F101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3100,6 +3406,9 @@
       <c r="F102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3126,6 +3435,9 @@
       <c r="F103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3152,6 +3464,9 @@
       <c r="F104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3178,6 +3493,9 @@
       <c r="F105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3204,6 +3522,9 @@
       <c r="F106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3230,6 +3551,9 @@
       <c r="F107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3256,6 +3580,9 @@
       <c r="F108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3282,6 +3609,9 @@
       <c r="F109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3308,6 +3638,9 @@
       <c r="F110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3334,6 +3667,9 @@
       <c r="F111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3360,6 +3696,9 @@
       <c r="F112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3386,6 +3725,9 @@
       <c r="F113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3412,6 +3754,9 @@
       <c r="F114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3438,6 +3783,9 @@
       <c r="F115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G115" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3464,6 +3812,9 @@
       <c r="F116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3490,6 +3841,9 @@
       <c r="F117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="G117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3516,6 +3870,9 @@
       <c r="F118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3542,6 +3899,9 @@
       <c r="F119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3568,6 +3928,9 @@
       <c r="F120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3594,6 +3957,9 @@
       <c r="F121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3620,6 +3986,9 @@
       <c r="F122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3646,6 +4015,9 @@
       <c r="F123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="G123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3672,6 +4044,9 @@
       <c r="F124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3698,6 +4073,9 @@
       <c r="F125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3724,6 +4102,9 @@
       <c r="F126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3750,6 +4131,9 @@
       <c r="F127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3776,6 +4160,9 @@
       <c r="F128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3802,6 +4189,9 @@
       <c r="F129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3828,6 +4218,9 @@
       <c r="F130" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3854,6 +4247,9 @@
       <c r="F131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3880,6 +4276,9 @@
       <c r="F132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="G132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3906,6 +4305,9 @@
       <c r="F133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3932,6 +4334,9 @@
       <c r="F134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3958,6 +4363,9 @@
       <c r="F135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3984,6 +4392,9 @@
       <c r="F136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4010,6 +4421,9 @@
       <c r="F137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4036,6 +4450,9 @@
       <c r="F138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4062,6 +4479,9 @@
       <c r="F139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4088,6 +4508,9 @@
       <c r="F140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4114,6 +4537,9 @@
       <c r="F141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4140,6 +4566,9 @@
       <c r="F142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4166,6 +4595,9 @@
       <c r="F143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4192,6 +4624,9 @@
       <c r="F144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4218,6 +4653,9 @@
       <c r="F145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="G145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4244,6 +4682,9 @@
       <c r="F146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4270,6 +4711,9 @@
       <c r="F147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4296,6 +4740,9 @@
       <c r="F148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4322,6 +4769,9 @@
       <c r="F149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="G149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4348,6 +4798,9 @@
       <c r="F150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4374,6 +4827,9 @@
       <c r="F151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="G151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4400,6 +4856,9 @@
       <c r="F152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4426,6 +4885,9 @@
       <c r="F153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4452,6 +4914,9 @@
       <c r="F154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="G154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4478,6 +4943,9 @@
       <c r="F155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4504,6 +4972,9 @@
       <c r="F156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4530,6 +5001,9 @@
       <c r="F157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4556,6 +5030,9 @@
       <c r="F158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4582,6 +5059,9 @@
       <c r="F159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="G159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4608,6 +5088,9 @@
       <c r="F160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4634,6 +5117,9 @@
       <c r="F161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4660,6 +5146,9 @@
       <c r="F162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="G162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4686,6 +5175,9 @@
       <c r="F163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="G163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4712,6 +5204,9 @@
       <c r="F164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="G164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4738,9 +5233,12 @@
       <c r="F165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F165"/>
+  <autoFilter ref="A1:G165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>2026-09-10 10:09</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +515,9 @@
       <c r="G2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="H2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +547,9 @@
       <c r="G3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +579,9 @@
       <c r="G4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="H4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +611,9 @@
       <c r="G5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,6 +643,9 @@
       <c r="G6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,6 +675,9 @@
       <c r="G7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="H7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +707,9 @@
       <c r="G8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +739,9 @@
       <c r="G9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -741,6 +771,9 @@
       <c r="G10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,6 +803,9 @@
       <c r="G11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +835,9 @@
       <c r="G12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -828,6 +867,9 @@
       <c r="G13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="H13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +899,9 @@
       <c r="G14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -886,6 +931,9 @@
       <c r="G15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -915,6 +963,9 @@
       <c r="G16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -944,6 +995,9 @@
       <c r="G17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="H17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -973,6 +1027,9 @@
       <c r="G18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1002,6 +1059,9 @@
       <c r="G19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="H19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1031,6 +1091,9 @@
       <c r="G20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="H20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1060,6 +1123,9 @@
       <c r="G21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1089,6 +1155,9 @@
       <c r="G22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1118,6 +1187,9 @@
       <c r="G23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1147,6 +1219,9 @@
       <c r="G24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1176,6 +1251,9 @@
       <c r="G25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1205,6 +1283,9 @@
       <c r="G26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="H26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1234,6 +1315,9 @@
       <c r="G27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1263,6 +1347,9 @@
       <c r="G28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="H28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1292,6 +1379,9 @@
       <c r="G29" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="H29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,6 +1411,9 @@
       <c r="G30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1350,6 +1443,9 @@
       <c r="G31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1379,6 +1475,9 @@
       <c r="G32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1507,9 @@
       <c r="G33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1437,6 +1539,9 @@
       <c r="G34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1466,6 +1571,9 @@
       <c r="G35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1495,6 +1603,9 @@
       <c r="G36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1524,6 +1635,9 @@
       <c r="G37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1553,6 +1667,9 @@
       <c r="G38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="H38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1582,6 +1699,9 @@
       <c r="G39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="H39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,6 +1731,9 @@
       <c r="G40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1640,6 +1763,9 @@
       <c r="G41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1669,6 +1795,9 @@
       <c r="G42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1698,6 +1827,9 @@
       <c r="G43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1727,6 +1859,9 @@
       <c r="G44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1756,6 +1891,9 @@
       <c r="G45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1785,6 +1923,9 @@
       <c r="G46" s="2" t="n">
         <v>21.05</v>
       </c>
+      <c r="H46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1814,6 +1955,9 @@
       <c r="G47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1843,6 +1987,9 @@
       <c r="G48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1872,6 +2019,9 @@
       <c r="G49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1901,6 +2051,9 @@
       <c r="G50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1930,6 +2083,9 @@
       <c r="G51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="H51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1959,6 +2115,9 @@
       <c r="G52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1988,6 +2147,9 @@
       <c r="G53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2017,6 +2179,9 @@
       <c r="G54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2046,6 +2211,9 @@
       <c r="G55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2075,6 +2243,9 @@
       <c r="G56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2104,6 +2275,9 @@
       <c r="G57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2133,6 +2307,9 @@
       <c r="G58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2162,6 +2339,9 @@
       <c r="G59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="H59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2191,6 +2371,9 @@
       <c r="G60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2220,6 +2403,9 @@
       <c r="G61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="H61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2249,6 +2435,9 @@
       <c r="G62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2278,6 +2467,9 @@
       <c r="G63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="H63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2307,6 +2499,9 @@
       <c r="G64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2336,6 +2531,9 @@
       <c r="G65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2365,6 +2563,9 @@
       <c r="G66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2394,6 +2595,9 @@
       <c r="G67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2423,6 +2627,9 @@
       <c r="G68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2452,6 +2659,9 @@
       <c r="G69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2481,6 +2691,9 @@
       <c r="G70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2510,6 +2723,9 @@
       <c r="G71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2539,6 +2755,9 @@
       <c r="G72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="H72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2568,6 +2787,9 @@
       <c r="G73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2597,6 +2819,9 @@
       <c r="G74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2626,6 +2851,9 @@
       <c r="G75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2655,6 +2883,9 @@
       <c r="G76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2684,6 +2915,9 @@
       <c r="G77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2713,6 +2947,9 @@
       <c r="G78" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2742,6 +2979,9 @@
       <c r="G79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2771,6 +3011,9 @@
       <c r="G80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2800,6 +3043,9 @@
       <c r="G81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2829,6 +3075,9 @@
       <c r="G82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2858,6 +3107,9 @@
       <c r="G83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2887,6 +3139,9 @@
       <c r="G84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2916,6 +3171,9 @@
       <c r="G85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2945,6 +3203,9 @@
       <c r="G86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2974,6 +3235,9 @@
       <c r="G87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3003,6 +3267,9 @@
       <c r="G88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3032,6 +3299,9 @@
       <c r="G89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3061,6 +3331,9 @@
       <c r="G90" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3090,6 +3363,9 @@
       <c r="G91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3119,6 +3395,9 @@
       <c r="G92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3148,6 +3427,9 @@
       <c r="G93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3177,6 +3459,9 @@
       <c r="G94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3206,6 +3491,9 @@
       <c r="G95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3235,6 +3523,9 @@
       <c r="G96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3264,6 +3555,9 @@
       <c r="G97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3293,6 +3587,9 @@
       <c r="G98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3322,6 +3619,9 @@
       <c r="G99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3351,6 +3651,9 @@
       <c r="G100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3380,6 +3683,9 @@
       <c r="G101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3409,6 +3715,9 @@
       <c r="G102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3438,6 +3747,9 @@
       <c r="G103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3467,6 +3779,9 @@
       <c r="G104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3496,6 +3811,9 @@
       <c r="G105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3525,6 +3843,9 @@
       <c r="G106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3554,6 +3875,9 @@
       <c r="G107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3583,6 +3907,9 @@
       <c r="G108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3612,6 +3939,9 @@
       <c r="G109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3641,6 +3971,9 @@
       <c r="G110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3670,6 +4003,9 @@
       <c r="G111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3699,6 +4035,9 @@
       <c r="G112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3728,6 +4067,9 @@
       <c r="G113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3757,6 +4099,9 @@
       <c r="G114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3786,6 +4131,9 @@
       <c r="G115" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3815,6 +4163,9 @@
       <c r="G116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3844,6 +4195,9 @@
       <c r="G117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3873,6 +4227,9 @@
       <c r="G118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3902,6 +4259,9 @@
       <c r="G119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3931,6 +4291,9 @@
       <c r="G120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3960,6 +4323,9 @@
       <c r="G121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3989,6 +4355,9 @@
       <c r="G122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4018,6 +4387,9 @@
       <c r="G123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="H123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4047,6 +4419,9 @@
       <c r="G124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4076,6 +4451,9 @@
       <c r="G125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4105,6 +4483,9 @@
       <c r="G126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4134,6 +4515,9 @@
       <c r="G127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4163,6 +4547,9 @@
       <c r="G128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4192,6 +4579,9 @@
       <c r="G129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4221,6 +4611,9 @@
       <c r="G130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4250,6 +4643,9 @@
       <c r="G131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4279,6 +4675,9 @@
       <c r="G132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="H132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4308,6 +4707,9 @@
       <c r="G133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4337,6 +4739,9 @@
       <c r="G134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4366,6 +4771,9 @@
       <c r="G135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4395,6 +4803,9 @@
       <c r="G136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4424,6 +4835,9 @@
       <c r="G137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4453,6 +4867,9 @@
       <c r="G138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4482,6 +4899,9 @@
       <c r="G139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4511,6 +4931,9 @@
       <c r="G140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4540,6 +4963,9 @@
       <c r="G141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4569,6 +4995,9 @@
       <c r="G142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4598,6 +5027,9 @@
       <c r="G143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4627,6 +5059,9 @@
       <c r="G144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4656,6 +5091,9 @@
       <c r="G145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="H145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4685,6 +5123,9 @@
       <c r="G146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4714,6 +5155,9 @@
       <c r="G147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4743,6 +5187,9 @@
       <c r="G148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4772,6 +5219,9 @@
       <c r="G149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="H149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4801,6 +5251,9 @@
       <c r="G150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4830,6 +5283,9 @@
       <c r="G151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="H151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4859,6 +5315,9 @@
       <c r="G152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4888,6 +5347,9 @@
       <c r="G153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4917,6 +5379,9 @@
       <c r="G154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="H154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4946,6 +5411,9 @@
       <c r="G155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4975,6 +5443,9 @@
       <c r="G156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5004,6 +5475,9 @@
       <c r="G157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5033,6 +5507,9 @@
       <c r="G158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5062,6 +5539,9 @@
       <c r="G159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="H159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5091,6 +5571,9 @@
       <c r="G160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5120,6 +5603,9 @@
       <c r="G161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5149,6 +5635,9 @@
       <c r="G162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="H162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5178,6 +5667,9 @@
       <c r="G163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="H163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5207,6 +5699,9 @@
       <c r="G164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="H164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5236,9 +5731,12 @@
       <c r="G165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G165"/>
+  <autoFilter ref="A1:H165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +487,11 @@
           <t>2026-09-10 13:10</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10 16:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +524,9 @@
       <c r="H2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,6 +559,9 @@
       <c r="H3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,6 +594,9 @@
       <c r="H4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,6 +629,9 @@
       <c r="H5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,6 +664,9 @@
       <c r="H6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +699,9 @@
       <c r="H7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -710,6 +734,9 @@
       <c r="H8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,6 +769,9 @@
       <c r="H9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -774,6 +804,9 @@
       <c r="H10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,6 +839,9 @@
       <c r="H11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -838,6 +874,9 @@
       <c r="H12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -870,6 +909,9 @@
       <c r="H13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -902,6 +944,9 @@
       <c r="H14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,6 +979,9 @@
       <c r="H15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -966,6 +1014,9 @@
       <c r="H16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -998,6 +1049,9 @@
       <c r="H17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1030,6 +1084,9 @@
       <c r="H18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1062,6 +1119,9 @@
       <c r="H19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1094,6 +1154,9 @@
       <c r="H20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1126,6 +1189,9 @@
       <c r="H21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1158,6 +1224,9 @@
       <c r="H22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1190,6 +1259,9 @@
       <c r="H23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1222,6 +1294,9 @@
       <c r="H24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,6 +1329,9 @@
       <c r="H25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1286,6 +1364,9 @@
       <c r="H26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1318,6 +1399,9 @@
       <c r="H27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1350,6 +1434,9 @@
       <c r="H28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="I28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1382,6 +1469,9 @@
       <c r="H29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1414,6 +1504,9 @@
       <c r="H30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1446,6 +1539,9 @@
       <c r="H31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1478,6 +1574,9 @@
       <c r="H32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,6 +1609,9 @@
       <c r="H33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1542,6 +1644,9 @@
       <c r="H34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1574,6 +1679,9 @@
       <c r="H35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1606,6 +1714,9 @@
       <c r="H36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1638,6 +1749,9 @@
       <c r="H37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1670,6 +1784,9 @@
       <c r="H38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="I38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1702,6 +1819,9 @@
       <c r="H39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="I39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1734,6 +1854,9 @@
       <c r="H40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1766,6 +1889,9 @@
       <c r="H41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1798,6 +1924,9 @@
       <c r="H42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I42" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1830,6 +1959,9 @@
       <c r="H43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1862,6 +1994,9 @@
       <c r="H44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1894,6 +2029,9 @@
       <c r="H45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1926,6 +2064,9 @@
       <c r="H46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="I46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1958,6 +2099,9 @@
       <c r="H47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1990,6 +2134,9 @@
       <c r="H48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2022,6 +2169,9 @@
       <c r="H49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2054,6 +2204,9 @@
       <c r="H50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2086,6 +2239,9 @@
       <c r="H51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="I51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2118,6 +2274,9 @@
       <c r="H52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2150,6 +2309,9 @@
       <c r="H53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2182,6 +2344,9 @@
       <c r="H54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2214,6 +2379,9 @@
       <c r="H55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2246,6 +2414,9 @@
       <c r="H56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2278,6 +2449,9 @@
       <c r="H57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,6 +2484,9 @@
       <c r="H58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2342,6 +2519,9 @@
       <c r="H59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="I59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2374,6 +2554,9 @@
       <c r="H60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2406,6 +2589,9 @@
       <c r="H61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="I61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2438,6 +2624,9 @@
       <c r="H62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,6 +2659,9 @@
       <c r="H63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="I63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2502,6 +2694,9 @@
       <c r="H64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,6 +2729,9 @@
       <c r="H65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2566,6 +2764,9 @@
       <c r="H66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2598,6 +2799,9 @@
       <c r="H67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2630,6 +2834,9 @@
       <c r="H68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2662,6 +2869,9 @@
       <c r="H69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2694,6 +2904,9 @@
       <c r="H70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I70" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2726,6 +2939,9 @@
       <c r="H71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2758,6 +2974,9 @@
       <c r="H72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="I72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2790,6 +3009,9 @@
       <c r="H73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2822,6 +3044,9 @@
       <c r="H74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2854,6 +3079,9 @@
       <c r="H75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2886,6 +3114,9 @@
       <c r="H76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2918,6 +3149,9 @@
       <c r="H77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2950,6 +3184,9 @@
       <c r="H78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2982,6 +3219,9 @@
       <c r="H79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3014,6 +3254,9 @@
       <c r="H80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3046,6 +3289,9 @@
       <c r="H81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3078,6 +3324,9 @@
       <c r="H82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3110,6 +3359,9 @@
       <c r="H83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3142,6 +3394,9 @@
       <c r="H84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3174,6 +3429,9 @@
       <c r="H85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3206,6 +3464,9 @@
       <c r="H86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3238,6 +3499,9 @@
       <c r="H87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3270,6 +3534,9 @@
       <c r="H88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3302,6 +3569,9 @@
       <c r="H89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3334,6 +3604,9 @@
       <c r="H90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3366,6 +3639,9 @@
       <c r="H91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3398,6 +3674,9 @@
       <c r="H92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3430,6 +3709,9 @@
       <c r="H93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3462,6 +3744,9 @@
       <c r="H94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3494,6 +3779,9 @@
       <c r="H95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3526,6 +3814,9 @@
       <c r="H96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3558,6 +3849,9 @@
       <c r="H97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3590,6 +3884,9 @@
       <c r="H98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3622,6 +3919,9 @@
       <c r="H99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3654,6 +3954,9 @@
       <c r="H100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3686,6 +3989,9 @@
       <c r="H101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3718,6 +4024,9 @@
       <c r="H102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3750,6 +4059,9 @@
       <c r="H103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3782,6 +4094,9 @@
       <c r="H104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3814,6 +4129,9 @@
       <c r="H105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3846,6 +4164,9 @@
       <c r="H106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3878,6 +4199,9 @@
       <c r="H107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3910,6 +4234,9 @@
       <c r="H108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3942,6 +4269,9 @@
       <c r="H109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3974,6 +4304,9 @@
       <c r="H110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="I110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4006,6 +4339,9 @@
       <c r="H111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4038,6 +4374,9 @@
       <c r="H112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4070,6 +4409,9 @@
       <c r="H113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4102,6 +4444,9 @@
       <c r="H114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4134,6 +4479,9 @@
       <c r="H115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4166,6 +4514,9 @@
       <c r="H116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4198,6 +4549,9 @@
       <c r="H117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="I117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4230,6 +4584,9 @@
       <c r="H118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4262,6 +4619,9 @@
       <c r="H119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4294,6 +4654,9 @@
       <c r="H120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4326,6 +4689,9 @@
       <c r="H121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4358,6 +4724,9 @@
       <c r="H122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4390,6 +4759,9 @@
       <c r="H123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="I123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4422,6 +4794,9 @@
       <c r="H124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4454,6 +4829,9 @@
       <c r="H125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4486,6 +4864,9 @@
       <c r="H126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4518,6 +4899,9 @@
       <c r="H127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4550,6 +4934,9 @@
       <c r="H128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4582,6 +4969,9 @@
       <c r="H129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4614,6 +5004,9 @@
       <c r="H130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4646,6 +5039,9 @@
       <c r="H131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4678,6 +5074,9 @@
       <c r="H132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="I132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4710,6 +5109,9 @@
       <c r="H133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4742,6 +5144,9 @@
       <c r="H134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4774,6 +5179,9 @@
       <c r="H135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4806,6 +5214,9 @@
       <c r="H136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4838,6 +5249,9 @@
       <c r="H137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4870,6 +5284,9 @@
       <c r="H138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4902,6 +5319,9 @@
       <c r="H139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4934,6 +5354,9 @@
       <c r="H140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4966,6 +5389,9 @@
       <c r="H141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4998,6 +5424,9 @@
       <c r="H142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5030,6 +5459,9 @@
       <c r="H143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5062,6 +5494,9 @@
       <c r="H144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5094,6 +5529,9 @@
       <c r="H145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="I145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5126,6 +5564,9 @@
       <c r="H146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5158,6 +5599,9 @@
       <c r="H147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5190,6 +5634,9 @@
       <c r="H148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5222,6 +5669,9 @@
       <c r="H149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="I149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5254,6 +5704,9 @@
       <c r="H150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5286,6 +5739,9 @@
       <c r="H151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="I151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5318,6 +5774,9 @@
       <c r="H152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5350,6 +5809,9 @@
       <c r="H153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5382,6 +5844,9 @@
       <c r="H154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="I154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5414,6 +5879,9 @@
       <c r="H155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5446,6 +5914,9 @@
       <c r="H156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5478,6 +5949,9 @@
       <c r="H157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5510,6 +5984,9 @@
       <c r="H158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5542,6 +6019,9 @@
       <c r="H159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="I159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5574,6 +6054,9 @@
       <c r="H160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5606,6 +6089,9 @@
       <c r="H161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5638,6 +6124,9 @@
       <c r="H162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="I162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5670,6 +6159,9 @@
       <c r="H163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="I163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5702,6 +6194,9 @@
       <c r="H164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="I164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5734,9 +6229,12 @@
       <c r="H165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H165"/>
+  <autoFilter ref="A1:I165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,6 +493,11 @@
           <t>2026-09-10 16:08</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +533,9 @@
       <c r="I2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="J2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +571,9 @@
       <c r="I3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="J3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +609,9 @@
       <c r="I4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,6 +647,9 @@
       <c r="I5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +685,9 @@
       <c r="I6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +723,9 @@
       <c r="I7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="J7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +761,9 @@
       <c r="I8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="J8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +799,9 @@
       <c r="I9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="J9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -807,6 +837,9 @@
       <c r="I10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,6 +875,9 @@
       <c r="I11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="J11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -877,6 +913,9 @@
       <c r="I12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -912,6 +951,9 @@
       <c r="I13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="J13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -947,6 +989,9 @@
       <c r="I14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -982,6 +1027,9 @@
       <c r="I15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1017,6 +1065,9 @@
       <c r="I16" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J16" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,6 +1103,9 @@
       <c r="I17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="J17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1087,6 +1141,9 @@
       <c r="I18" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J18" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1122,6 +1179,9 @@
       <c r="I19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="J19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1157,6 +1217,9 @@
       <c r="I20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="J20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1192,6 +1255,9 @@
       <c r="I21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="J21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1227,6 +1293,9 @@
       <c r="I22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1262,6 +1331,9 @@
       <c r="I23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1297,6 +1369,9 @@
       <c r="I24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1332,6 +1407,9 @@
       <c r="I25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1367,6 +1445,9 @@
       <c r="I26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="J26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1402,6 +1483,9 @@
       <c r="I27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1437,6 +1521,9 @@
       <c r="I28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="J28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1472,6 +1559,9 @@
       <c r="I29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1597,9 @@
       <c r="I30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1542,6 +1635,9 @@
       <c r="I31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1577,6 +1673,9 @@
       <c r="I32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1612,6 +1711,9 @@
       <c r="I33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1647,6 +1749,9 @@
       <c r="I34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1682,6 +1787,9 @@
       <c r="I35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1717,6 +1825,9 @@
       <c r="I36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1752,6 +1863,9 @@
       <c r="I37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1787,6 +1901,9 @@
       <c r="I38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="J38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1822,6 +1939,9 @@
       <c r="I39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="J39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1857,6 +1977,9 @@
       <c r="I40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1892,6 +2015,9 @@
       <c r="I41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,6 +2053,9 @@
       <c r="I42" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1962,6 +2091,9 @@
       <c r="I43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1997,6 +2129,9 @@
       <c r="I44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2032,6 +2167,9 @@
       <c r="I45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2067,6 +2205,9 @@
       <c r="I46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="J46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2102,6 +2243,9 @@
       <c r="I47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2137,6 +2281,9 @@
       <c r="I48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2172,6 +2319,9 @@
       <c r="I49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2207,6 +2357,9 @@
       <c r="I50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2242,6 +2395,9 @@
       <c r="I51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="J51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2277,6 +2433,9 @@
       <c r="I52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2312,6 +2471,9 @@
       <c r="I53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2347,6 +2509,9 @@
       <c r="I54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2382,6 +2547,9 @@
       <c r="I55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2417,6 +2585,9 @@
       <c r="I56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2452,6 +2623,9 @@
       <c r="I57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2487,6 +2661,9 @@
       <c r="I58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2522,6 +2699,9 @@
       <c r="I59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="J59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2557,6 +2737,9 @@
       <c r="I60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2592,6 +2775,9 @@
       <c r="I61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="J61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2627,6 +2813,9 @@
       <c r="I62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +2851,9 @@
       <c r="I63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="J63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2697,6 +2889,9 @@
       <c r="I64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2732,6 +2927,9 @@
       <c r="I65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2767,6 +2965,9 @@
       <c r="I66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2802,6 +3003,9 @@
       <c r="I67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2837,6 +3041,9 @@
       <c r="I68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2872,6 +3079,9 @@
       <c r="I69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2907,6 +3117,9 @@
       <c r="I70" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2942,6 +3155,9 @@
       <c r="I71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2977,6 +3193,9 @@
       <c r="I72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="J72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3012,6 +3231,9 @@
       <c r="I73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3047,6 +3269,9 @@
       <c r="I74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3082,6 +3307,9 @@
       <c r="I75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3117,6 +3345,9 @@
       <c r="I76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3152,6 +3383,9 @@
       <c r="I77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3187,6 +3421,9 @@
       <c r="I78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3222,6 +3459,9 @@
       <c r="I79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3257,6 +3497,9 @@
       <c r="I80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3292,6 +3535,9 @@
       <c r="I81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3327,6 +3573,9 @@
       <c r="I82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3362,6 +3611,9 @@
       <c r="I83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3397,6 +3649,9 @@
       <c r="I84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3432,6 +3687,9 @@
       <c r="I85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3467,6 +3725,9 @@
       <c r="I86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3502,6 +3763,9 @@
       <c r="I87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3537,6 +3801,9 @@
       <c r="I88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3572,6 +3839,9 @@
       <c r="I89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3607,6 +3877,9 @@
       <c r="I90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3642,6 +3915,9 @@
       <c r="I91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3677,6 +3953,9 @@
       <c r="I92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3712,6 +3991,9 @@
       <c r="I93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3747,6 +4029,9 @@
       <c r="I94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3782,6 +4067,9 @@
       <c r="I95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3817,6 +4105,9 @@
       <c r="I96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3852,6 +4143,9 @@
       <c r="I97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3887,6 +4181,9 @@
       <c r="I98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3922,6 +4219,9 @@
       <c r="I99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3957,6 +4257,9 @@
       <c r="I100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3992,6 +4295,9 @@
       <c r="I101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4027,6 +4333,9 @@
       <c r="I102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4062,6 +4371,9 @@
       <c r="I103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4097,6 +4409,9 @@
       <c r="I104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4132,6 +4447,9 @@
       <c r="I105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4167,6 +4485,9 @@
       <c r="I106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4202,6 +4523,9 @@
       <c r="I107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4237,6 +4561,9 @@
       <c r="I108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4272,6 +4599,9 @@
       <c r="I109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4307,6 +4637,9 @@
       <c r="I110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="J110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4342,6 +4675,9 @@
       <c r="I111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4377,6 +4713,9 @@
       <c r="I112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4412,6 +4751,9 @@
       <c r="I113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4447,6 +4789,9 @@
       <c r="I114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4482,6 +4827,9 @@
       <c r="I115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4517,6 +4865,9 @@
       <c r="I116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4552,6 +4903,9 @@
       <c r="I117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="J117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4587,6 +4941,9 @@
       <c r="I118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4622,6 +4979,9 @@
       <c r="I119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4657,6 +5017,9 @@
       <c r="I120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4692,6 +5055,9 @@
       <c r="I121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4727,6 +5093,9 @@
       <c r="I122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4762,6 +5131,9 @@
       <c r="I123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="J123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4797,6 +5169,9 @@
       <c r="I124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4832,6 +5207,9 @@
       <c r="I125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4867,6 +5245,9 @@
       <c r="I126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4902,6 +5283,9 @@
       <c r="I127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4937,6 +5321,9 @@
       <c r="I128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4972,6 +5359,9 @@
       <c r="I129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5007,6 +5397,9 @@
       <c r="I130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5042,6 +5435,9 @@
       <c r="I131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5077,6 +5473,9 @@
       <c r="I132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="J132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5112,6 +5511,9 @@
       <c r="I133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5147,6 +5549,9 @@
       <c r="I134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5182,6 +5587,9 @@
       <c r="I135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5217,6 +5625,9 @@
       <c r="I136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5252,6 +5663,9 @@
       <c r="I137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5287,6 +5701,9 @@
       <c r="I138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5322,6 +5739,9 @@
       <c r="I139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5357,6 +5777,9 @@
       <c r="I140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5392,6 +5815,9 @@
       <c r="I141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5427,6 +5853,9 @@
       <c r="I142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5462,6 +5891,9 @@
       <c r="I143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5497,6 +5929,9 @@
       <c r="I144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5532,6 +5967,9 @@
       <c r="I145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="J145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5567,6 +6005,9 @@
       <c r="I146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5602,6 +6043,9 @@
       <c r="I147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5637,6 +6081,9 @@
       <c r="I148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5672,6 +6119,9 @@
       <c r="I149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="J149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5707,6 +6157,9 @@
       <c r="I150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5742,6 +6195,9 @@
       <c r="I151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="J151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5777,6 +6233,9 @@
       <c r="I152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5812,6 +6271,9 @@
       <c r="I153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5847,6 +6309,9 @@
       <c r="I154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="J154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5882,6 +6347,9 @@
       <c r="I155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5917,6 +6385,9 @@
       <c r="I156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5952,6 +6423,9 @@
       <c r="I157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5987,6 +6461,9 @@
       <c r="I158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6022,6 +6499,9 @@
       <c r="I159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6057,6 +6537,9 @@
       <c r="I160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6092,6 +6575,9 @@
       <c r="I161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6127,6 +6613,9 @@
       <c r="I162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="J162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6162,6 +6651,9 @@
       <c r="I163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="J163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6197,6 +6689,9 @@
       <c r="I164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="J164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6232,9 +6727,12 @@
       <c r="I165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I165"/>
+  <autoFilter ref="A1:J165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,19 +432,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,37 +459,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-10 01:13</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-10 04:09</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-10 07:12</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-10 10:09</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-10 13:10</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-10 16:08</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-10 22:09</t>
+          <t>2026-09-11 01:11</t>
         </is>
       </c>
     </row>
@@ -518,24 +482,6 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>13.45</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,24 +502,6 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,24 +522,6 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>17.95</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,24 +542,6 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -670,24 +562,6 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -708,24 +582,6 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>19.49</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -746,24 +602,6 @@
       <c r="D8" s="2" t="n">
         <v>20.49</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>20.49</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -784,24 +622,6 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -822,24 +642,6 @@
       <c r="D10" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -860,24 +662,6 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>20.19</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -898,24 +682,6 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -936,24 +702,6 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>20.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -974,24 +722,6 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1012,24 +742,6 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1048,25 +760,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>20.39</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="17">
@@ -1088,24 +782,6 @@
       <c r="D17" s="2" t="n">
         <v>20.75</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>20.75</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1124,25 +800,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>20.39</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="19">
@@ -1164,24 +822,6 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>20.77</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1202,24 +842,6 @@
       <c r="D20" s="2" t="n">
         <v>20.65</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>20.65</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1240,24 +862,6 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>20.48</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1278,24 +882,6 @@
       <c r="D22" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1316,24 +902,6 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1354,24 +922,6 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1392,24 +942,6 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1430,24 +962,6 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>20.8</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1468,24 +982,6 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1506,24 +1002,6 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>20.54</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1542,24 +1020,6 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J29" s="2" t="n">
         <v>20.89</v>
       </c>
     </row>
@@ -1582,24 +1042,6 @@
       <c r="D30" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1620,24 +1062,6 @@
       <c r="D31" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1658,24 +1082,6 @@
       <c r="D32" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1696,24 +1102,6 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1734,24 +1122,6 @@
       <c r="D34" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1772,24 +1142,6 @@
       <c r="D35" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1810,24 +1162,6 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1848,24 +1182,6 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1886,24 +1202,6 @@
       <c r="D38" s="2" t="n">
         <v>20.88</v>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>20.88</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1924,24 +1222,6 @@
       <c r="D39" s="2" t="n">
         <v>20.98</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>20.98</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1960,24 +1240,6 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J40" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -2000,24 +1262,6 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2036,24 +1280,6 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J42" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -2076,24 +1302,6 @@
       <c r="D43" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2114,24 +1322,6 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2152,24 +1342,6 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2188,24 +1360,6 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="J46" s="2" t="n">
         <v>21.15</v>
       </c>
     </row>
@@ -2228,24 +1382,6 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2266,24 +1402,6 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2304,24 +1422,6 @@
       <c r="D49" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2342,24 +1442,6 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2380,24 +1462,6 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>20.85</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2418,24 +1482,6 @@
       <c r="D52" s="2" t="n">
         <v>22.35</v>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>22.35</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2456,24 +1502,6 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2494,24 +1522,6 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>21.79</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2532,24 +1542,6 @@
       <c r="D55" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2570,24 +1562,6 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2608,24 +1582,6 @@
       <c r="D57" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2644,24 +1600,6 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J58" s="2" t="n">
         <v>21.75</v>
       </c>
     </row>
@@ -2684,24 +1622,6 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>22.2</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2722,24 +1642,6 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2760,24 +1662,6 @@
       <c r="D61" s="2" t="n">
         <v>21.55</v>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>21.55</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2798,24 +1682,6 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2834,24 +1700,6 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="J63" s="2" t="n">
         <v>21.25</v>
       </c>
     </row>
@@ -2872,24 +1720,6 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="J64" s="2" t="n">
         <v>21.79</v>
       </c>
     </row>
@@ -2912,24 +1742,6 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2950,24 +1762,6 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2988,24 +1782,6 @@
       <c r="D67" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3026,24 +1802,6 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3064,24 +1822,6 @@
       <c r="D69" s="2" t="n">
         <v>21.65</v>
       </c>
-      <c r="E69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>21.65</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3100,24 +1840,6 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J70" s="2" t="n">
         <v>21.49</v>
       </c>
     </row>
@@ -3140,24 +1862,6 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3178,24 +1882,6 @@
       <c r="D72" s="2" t="n">
         <v>21.29</v>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>21.29</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3216,24 +1902,6 @@
       <c r="D73" s="2" t="n">
         <v>21.65</v>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>21.65</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3254,24 +1922,6 @@
       <c r="D74" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3292,24 +1942,6 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3330,24 +1962,6 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3368,24 +1982,6 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3404,24 +2000,6 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J78" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -3444,24 +2022,6 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3482,24 +2042,6 @@
       <c r="D80" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3520,24 +2062,6 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3558,24 +2082,6 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3596,24 +2102,6 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3632,24 +2120,6 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J84" s="2" t="n">
         <v>21.65</v>
       </c>
     </row>
@@ -3672,24 +2142,6 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3710,24 +2162,6 @@
       <c r="D86" s="2" t="n">
         <v>21.65</v>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>21.65</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3748,24 +2182,6 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3786,24 +2202,6 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3824,24 +2222,6 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3860,24 +2240,6 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J90" s="2" t="n">
         <v>21.49</v>
       </c>
     </row>
@@ -3900,24 +2262,6 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3938,24 +2282,6 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3976,24 +2302,6 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
-      <c r="E93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>21.89</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4014,24 +2322,6 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4052,24 +2342,6 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4090,24 +2362,6 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4128,24 +2382,6 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4166,24 +2402,6 @@
       <c r="D98" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4204,24 +2422,6 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4242,24 +2442,6 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4280,24 +2462,6 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4318,24 +2482,6 @@
       <c r="D102" s="2" t="n">
         <v>22.79</v>
       </c>
-      <c r="E102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>22.79</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4356,24 +2502,6 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4394,24 +2522,6 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4432,24 +2542,6 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4470,24 +2562,6 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4508,24 +2582,6 @@
       <c r="D107" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4546,24 +2602,6 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4584,24 +2622,6 @@
       <c r="D109" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4622,24 +2642,6 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
-      <c r="E110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>20.39</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4660,24 +2662,6 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4698,24 +2682,6 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4736,24 +2702,6 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4774,24 +2722,6 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4810,24 +2740,6 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J115" s="2" t="n">
         <v>21.65</v>
       </c>
     </row>
@@ -4850,24 +2762,6 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4888,24 +2782,6 @@
       <c r="D117" s="2" t="n">
         <v>21.85</v>
       </c>
-      <c r="E117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>21.85</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4926,24 +2802,6 @@
       <c r="D118" s="2" t="n">
         <v>21.75</v>
       </c>
-      <c r="E118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>21.75</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4964,24 +2822,6 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5002,24 +2842,6 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5040,24 +2862,6 @@
       <c r="D121" s="2" t="n">
         <v>21.75</v>
       </c>
-      <c r="E121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>21.75</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5078,24 +2882,6 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5116,24 +2902,6 @@
       <c r="D123" s="2" t="n">
         <v>21.69</v>
       </c>
-      <c r="E123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>21.69</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5154,24 +2922,6 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5192,24 +2942,6 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5230,24 +2962,6 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5268,24 +2982,6 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5306,24 +3002,6 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5344,24 +3022,6 @@
       <c r="D129" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5380,24 +3040,6 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J130" s="2" t="n">
         <v>22.5</v>
       </c>
     </row>
@@ -5420,24 +3062,6 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5458,24 +3082,6 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="E132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>21.6</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5496,24 +3102,6 @@
       <c r="D133" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5534,24 +3122,6 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="E134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>21.7</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5572,24 +3142,6 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5610,24 +3162,6 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5648,24 +3182,6 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5686,24 +3202,6 @@
       <c r="D138" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5724,24 +3222,6 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5762,24 +3242,6 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5800,24 +3262,6 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5838,24 +3282,6 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5876,24 +3302,6 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5914,24 +3322,6 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5952,24 +3342,6 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
-      <c r="E145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>22.29</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5990,24 +3362,6 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6028,24 +3382,6 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6066,24 +3402,6 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
-      <c r="E148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>22.35</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6104,24 +3422,6 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
-      <c r="E149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>22.49</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6142,24 +3442,6 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>22.5</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6180,24 +3462,6 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
-      <c r="E151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>22.59</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6218,24 +3482,6 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6256,24 +3502,6 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6294,24 +3522,6 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>22.7</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6332,24 +3542,6 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>22.79</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6370,24 +3562,6 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6408,24 +3582,6 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6446,24 +3602,6 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6484,24 +3622,6 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
-      <c r="E159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>23.99</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6522,24 +3642,6 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6560,24 +3662,6 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6598,24 +3682,6 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
-      <c r="E162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>23.49</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6636,24 +3702,6 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6674,24 +3722,6 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>24.25</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6712,27 +3742,9 @@
       <c r="D165" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J165"/>
+  <autoFilter ref="A1:D165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,13 +432,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,6 +463,11 @@
           <t>2026-09-11 01:11</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,6 +488,9 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,6 +511,9 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -522,6 +534,9 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +557,9 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,6 +580,9 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -582,6 +603,9 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,6 +626,9 @@
       <c r="D8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="E8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +649,9 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,6 +672,9 @@
       <c r="D10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -662,6 +695,9 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,6 +718,9 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -702,6 +741,9 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,6 +764,9 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,6 +787,9 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -762,6 +810,9 @@
       <c r="D16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,6 +833,9 @@
       <c r="D17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="E17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -802,6 +856,9 @@
       <c r="D18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -822,6 +879,9 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,6 +902,9 @@
       <c r="D20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,6 +925,9 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -882,6 +948,9 @@
       <c r="D22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -902,6 +971,9 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -922,6 +994,9 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -942,6 +1017,9 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -962,6 +1040,9 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="E26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -982,6 +1063,9 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1002,6 +1086,9 @@
       <c r="D28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1022,6 +1109,9 @@
       <c r="D29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1042,6 +1132,9 @@
       <c r="D30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1062,6 +1155,9 @@
       <c r="D31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1082,6 +1178,9 @@
       <c r="D32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1102,6 +1201,9 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1122,6 +1224,9 @@
       <c r="D34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1142,6 +1247,9 @@
       <c r="D35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1162,6 +1270,9 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1182,6 +1293,9 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1202,6 +1316,9 @@
       <c r="D38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="E38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1222,6 +1339,9 @@
       <c r="D39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="E39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1242,6 +1362,9 @@
       <c r="D40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1262,6 +1385,9 @@
       <c r="D41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1282,6 +1408,9 @@
       <c r="D42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1302,6 +1431,9 @@
       <c r="D43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1322,6 +1454,9 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1342,6 +1477,9 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1362,6 +1500,9 @@
       <c r="D46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="E46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1382,6 +1523,9 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1402,6 +1546,9 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1422,6 +1569,9 @@
       <c r="D49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1442,6 +1592,9 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1462,6 +1615,9 @@
       <c r="D51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="E51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1482,6 +1638,9 @@
       <c r="D52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1502,6 +1661,9 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1522,6 +1684,9 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1542,6 +1707,9 @@
       <c r="D55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1562,6 +1730,9 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1582,6 +1753,9 @@
       <c r="D57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1602,6 +1776,9 @@
       <c r="D58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1622,6 +1799,9 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="E59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1642,6 +1822,9 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1662,6 +1845,9 @@
       <c r="D61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="E61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1682,6 +1868,9 @@
       <c r="D62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E62" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1702,6 +1891,9 @@
       <c r="D63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="E63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1722,6 +1914,9 @@
       <c r="D64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1742,6 +1937,9 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1762,6 +1960,9 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1782,6 +1983,9 @@
       <c r="D67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1802,6 +2006,9 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1822,6 +2029,9 @@
       <c r="D69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1842,6 +2052,9 @@
       <c r="D70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1862,6 +2075,9 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1882,6 +2098,9 @@
       <c r="D72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="E72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1902,6 +2121,9 @@
       <c r="D73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1922,6 +2144,9 @@
       <c r="D74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1942,6 +2167,9 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1962,6 +2190,9 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1982,6 +2213,9 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2002,6 +2236,9 @@
       <c r="D78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2022,6 +2259,9 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2042,6 +2282,9 @@
       <c r="D80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2062,6 +2305,9 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2082,6 +2328,9 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2102,6 +2351,9 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2122,6 +2374,9 @@
       <c r="D84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2142,6 +2397,9 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2162,6 +2420,9 @@
       <c r="D86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2182,6 +2443,9 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2202,6 +2466,9 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2222,6 +2489,9 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2242,6 +2512,9 @@
       <c r="D90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2262,6 +2535,9 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2282,6 +2558,9 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2302,6 +2581,9 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="E93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2322,6 +2604,9 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2342,6 +2627,9 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2362,6 +2650,9 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2382,6 +2673,9 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2402,6 +2696,9 @@
       <c r="D98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2422,6 +2719,9 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2442,6 +2742,9 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2462,6 +2765,9 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2482,6 +2788,9 @@
       <c r="D102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2502,6 +2811,9 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2522,6 +2834,9 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2542,6 +2857,9 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2562,6 +2880,9 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2582,6 +2903,9 @@
       <c r="D107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2602,6 +2926,9 @@
       <c r="D108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2622,6 +2949,9 @@
       <c r="D109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2642,6 +2972,9 @@
       <c r="D110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="E110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2662,6 +2995,9 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2682,6 +3018,9 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2702,6 +3041,9 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2722,6 +3064,9 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2742,6 +3087,9 @@
       <c r="D115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2762,6 +3110,9 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2782,6 +3133,9 @@
       <c r="D117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="E117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2802,6 +3156,9 @@
       <c r="D118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2822,6 +3179,9 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2842,6 +3202,9 @@
       <c r="D120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2862,6 +3225,9 @@
       <c r="D121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2882,6 +3248,9 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2902,6 +3271,9 @@
       <c r="D123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="E123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2922,6 +3294,9 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2942,6 +3317,9 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2962,6 +3340,9 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2982,6 +3363,9 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3002,6 +3386,9 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3022,6 +3409,9 @@
       <c r="D129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3042,6 +3432,9 @@
       <c r="D130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="E130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3062,6 +3455,9 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3082,6 +3478,9 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="E132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3102,6 +3501,9 @@
       <c r="D133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3122,6 +3524,9 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="E134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3142,6 +3547,9 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3162,6 +3570,9 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3182,6 +3593,9 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3202,6 +3616,9 @@
       <c r="D138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3222,6 +3639,9 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3242,6 +3662,9 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3262,6 +3685,9 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3282,6 +3708,9 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3302,6 +3731,9 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3322,6 +3754,9 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3342,6 +3777,9 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="E145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3362,6 +3800,9 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3382,6 +3823,9 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3402,6 +3846,9 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3422,6 +3869,9 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="E149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3442,6 +3892,9 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="E150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3462,6 +3915,9 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="E151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3482,6 +3938,9 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3502,6 +3961,9 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3522,6 +3984,9 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="E154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3542,6 +4007,9 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3562,6 +4030,9 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3582,6 +4053,9 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3602,6 +4076,9 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3622,6 +4099,9 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="E159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3642,6 +4122,9 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3662,6 +4145,9 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3682,6 +4168,9 @@
       <c r="D162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="E162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3702,6 +4191,9 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="E163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3722,6 +4214,9 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="E164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3742,9 +4237,12 @@
       <c r="D165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D165"/>
+  <autoFilter ref="A1:E165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,11 @@
           <t>2026-09-11 04:09</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 07:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +497,9 @@
       <c r="E2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,6 +523,9 @@
       <c r="E3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="F3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +549,9 @@
       <c r="E4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,6 +575,9 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +601,9 @@
       <c r="E6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -606,6 +627,9 @@
       <c r="E7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="F7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -629,6 +653,9 @@
       <c r="E8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -652,6 +679,9 @@
       <c r="E9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="F9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -675,6 +705,9 @@
       <c r="E10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +731,9 @@
       <c r="E11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="F11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -721,6 +757,9 @@
       <c r="E12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,6 +783,9 @@
       <c r="E13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="F13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -767,6 +809,9 @@
       <c r="E14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -790,6 +835,9 @@
       <c r="E15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -813,6 +861,9 @@
       <c r="E16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -836,6 +887,9 @@
       <c r="E17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="F17" s="2" t="n">
+        <v>20.75</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -859,6 +913,9 @@
       <c r="E18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -882,6 +939,9 @@
       <c r="E19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="F19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -905,6 +965,9 @@
       <c r="E20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="F20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -928,6 +991,9 @@
       <c r="E21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="F21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -951,6 +1017,9 @@
       <c r="E22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -974,6 +1043,9 @@
       <c r="E23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -997,6 +1069,9 @@
       <c r="E24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1020,6 +1095,9 @@
       <c r="E25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1043,6 +1121,9 @@
       <c r="E26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="F26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1066,6 +1147,9 @@
       <c r="E27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1089,6 +1173,9 @@
       <c r="E28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="F28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1112,6 +1199,9 @@
       <c r="E29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1135,6 +1225,9 @@
       <c r="E30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1158,6 +1251,9 @@
       <c r="E31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1181,6 +1277,9 @@
       <c r="E32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1204,6 +1303,9 @@
       <c r="E33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1227,6 +1329,9 @@
       <c r="E34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1250,6 +1355,9 @@
       <c r="E35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1273,6 +1381,9 @@
       <c r="E36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1296,6 +1407,9 @@
       <c r="E37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1319,6 +1433,9 @@
       <c r="E38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="F38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1342,6 +1459,9 @@
       <c r="E39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="F39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1365,6 +1485,9 @@
       <c r="E40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1388,6 +1511,9 @@
       <c r="E41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1411,6 +1537,9 @@
       <c r="E42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1434,6 +1563,9 @@
       <c r="E43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1457,6 +1589,9 @@
       <c r="E44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1480,6 +1615,9 @@
       <c r="E45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1503,6 +1641,9 @@
       <c r="E46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="F46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1526,6 +1667,9 @@
       <c r="E47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1549,6 +1693,9 @@
       <c r="E48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1572,6 +1719,9 @@
       <c r="E49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1595,6 +1745,9 @@
       <c r="E50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1618,6 +1771,9 @@
       <c r="E51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="F51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1641,6 +1797,9 @@
       <c r="E52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1664,6 +1823,9 @@
       <c r="E53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1687,6 +1849,9 @@
       <c r="E54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1710,6 +1875,9 @@
       <c r="E55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1733,6 +1901,9 @@
       <c r="E56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1756,6 +1927,9 @@
       <c r="E57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1779,6 +1953,9 @@
       <c r="E58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1802,6 +1979,9 @@
       <c r="E59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="F59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1825,6 +2005,9 @@
       <c r="E60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1848,6 +2031,9 @@
       <c r="E61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="F61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1871,6 +2057,9 @@
       <c r="E62" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1894,6 +2083,9 @@
       <c r="E63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="F63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1917,6 +2109,9 @@
       <c r="E64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1940,6 +2135,9 @@
       <c r="E65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1963,6 +2161,9 @@
       <c r="E66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1986,6 +2187,9 @@
       <c r="E67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2009,6 +2213,9 @@
       <c r="E68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2032,6 +2239,9 @@
       <c r="E69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2055,6 +2265,9 @@
       <c r="E70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2078,6 +2291,9 @@
       <c r="E71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2101,6 +2317,9 @@
       <c r="E72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="F72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2124,6 +2343,9 @@
       <c r="E73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2147,6 +2369,9 @@
       <c r="E74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2170,6 +2395,9 @@
       <c r="E75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2193,6 +2421,9 @@
       <c r="E76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2216,6 +2447,9 @@
       <c r="E77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2239,6 +2473,9 @@
       <c r="E78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2262,6 +2499,9 @@
       <c r="E79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2285,6 +2525,9 @@
       <c r="E80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2308,6 +2551,9 @@
       <c r="E81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2331,6 +2577,9 @@
       <c r="E82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2354,6 +2603,9 @@
       <c r="E83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2377,6 +2629,9 @@
       <c r="E84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2400,6 +2655,9 @@
       <c r="E85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2423,6 +2681,9 @@
       <c r="E86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2446,6 +2707,9 @@
       <c r="E87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2469,6 +2733,9 @@
       <c r="E88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2492,6 +2759,9 @@
       <c r="E89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2515,6 +2785,9 @@
       <c r="E90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2538,6 +2811,9 @@
       <c r="E91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2561,6 +2837,9 @@
       <c r="E92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2584,6 +2863,9 @@
       <c r="E93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="F93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2607,6 +2889,9 @@
       <c r="E94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2630,6 +2915,9 @@
       <c r="E95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2653,6 +2941,9 @@
       <c r="E96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2676,6 +2967,9 @@
       <c r="E97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2699,6 +2993,9 @@
       <c r="E98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2722,6 +3019,9 @@
       <c r="E99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2745,6 +3045,9 @@
       <c r="E100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2768,6 +3071,9 @@
       <c r="E101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2791,6 +3097,9 @@
       <c r="E102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2814,6 +3123,9 @@
       <c r="E103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2837,6 +3149,9 @@
       <c r="E104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2860,6 +3175,9 @@
       <c r="E105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2883,6 +3201,9 @@
       <c r="E106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2906,6 +3227,9 @@
       <c r="E107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2929,6 +3253,9 @@
       <c r="E108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2952,6 +3279,9 @@
       <c r="E109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F109" s="2" t="n">
+        <v>21.51</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2975,6 +3305,9 @@
       <c r="E110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="F110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2998,6 +3331,9 @@
       <c r="E111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3021,6 +3357,9 @@
       <c r="E112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3044,6 +3383,9 @@
       <c r="E113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3067,6 +3409,9 @@
       <c r="E114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3090,6 +3435,9 @@
       <c r="E115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3113,6 +3461,9 @@
       <c r="E116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3136,6 +3487,9 @@
       <c r="E117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="F117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3159,6 +3513,9 @@
       <c r="E118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3182,6 +3539,9 @@
       <c r="E119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3205,6 +3565,9 @@
       <c r="E120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3228,6 +3591,9 @@
       <c r="E121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3251,6 +3617,9 @@
       <c r="E122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3274,6 +3643,9 @@
       <c r="E123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="F123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3297,6 +3669,9 @@
       <c r="E124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3320,6 +3695,9 @@
       <c r="E125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3343,6 +3721,9 @@
       <c r="E126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3366,6 +3747,9 @@
       <c r="E127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3389,6 +3773,9 @@
       <c r="E128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3412,6 +3799,9 @@
       <c r="E129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3435,6 +3825,9 @@
       <c r="E130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="F130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3458,6 +3851,9 @@
       <c r="E131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3481,6 +3877,9 @@
       <c r="E132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="F132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3504,6 +3903,9 @@
       <c r="E133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3527,6 +3929,9 @@
       <c r="E134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="F134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3550,6 +3955,9 @@
       <c r="E135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3573,6 +3981,9 @@
       <c r="E136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3596,6 +4007,9 @@
       <c r="E137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3619,6 +4033,9 @@
       <c r="E138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3642,6 +4059,9 @@
       <c r="E139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3665,6 +4085,9 @@
       <c r="E140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3688,6 +4111,9 @@
       <c r="E141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3711,6 +4137,9 @@
       <c r="E142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3734,6 +4163,9 @@
       <c r="E143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3757,6 +4189,9 @@
       <c r="E144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3780,6 +4215,9 @@
       <c r="E145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="F145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3803,6 +4241,9 @@
       <c r="E146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3826,6 +4267,9 @@
       <c r="E147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3849,6 +4293,9 @@
       <c r="E148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3872,6 +4319,9 @@
       <c r="E149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="F149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3895,6 +4345,9 @@
       <c r="E150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="F150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3918,6 +4371,9 @@
       <c r="E151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="F151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3941,6 +4397,9 @@
       <c r="E152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3964,6 +4423,9 @@
       <c r="E153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3987,6 +4449,9 @@
       <c r="E154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="F154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4010,6 +4475,9 @@
       <c r="E155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4033,6 +4501,9 @@
       <c r="E156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4056,6 +4527,9 @@
       <c r="E157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4079,6 +4553,9 @@
       <c r="E158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4102,6 +4579,9 @@
       <c r="E159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="F159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4125,6 +4605,9 @@
       <c r="E160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4148,6 +4631,9 @@
       <c r="E161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4171,6 +4657,9 @@
       <c r="E162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="F162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4194,6 +4683,9 @@
       <c r="E163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="F163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4217,6 +4709,9 @@
       <c r="E164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="F164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4240,9 +4735,12 @@
       <c r="E165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E165"/>
+  <autoFilter ref="A1:F165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>2026-09-11 07:12</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,9 @@
       <c r="F2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +535,9 @@
       <c r="F3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,6 +564,9 @@
       <c r="F4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,6 +593,9 @@
       <c r="F5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,6 +622,9 @@
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +651,9 @@
       <c r="F7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,6 +680,9 @@
       <c r="F8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +709,9 @@
       <c r="F9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -708,6 +738,9 @@
       <c r="F10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -734,6 +767,9 @@
       <c r="F11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -760,6 +796,9 @@
       <c r="F12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,6 +825,9 @@
       <c r="F13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -812,6 +854,9 @@
       <c r="F14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -838,6 +883,9 @@
       <c r="F15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -864,6 +912,9 @@
       <c r="F16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,6 +941,9 @@
       <c r="F17" s="2" t="n">
         <v>20.75</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -916,6 +970,9 @@
       <c r="F18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -942,6 +999,9 @@
       <c r="F19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -968,6 +1028,9 @@
       <c r="F20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -994,6 +1057,9 @@
       <c r="F21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1020,6 +1086,9 @@
       <c r="F22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1046,6 +1115,9 @@
       <c r="F23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1072,6 +1144,9 @@
       <c r="F24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1098,6 +1173,9 @@
       <c r="F25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1124,6 +1202,9 @@
       <c r="F26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1150,6 +1231,9 @@
       <c r="F27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1176,6 +1260,9 @@
       <c r="F28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1202,6 +1289,9 @@
       <c r="F29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1228,6 +1318,9 @@
       <c r="F30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1254,6 +1347,9 @@
       <c r="F31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1280,6 +1376,9 @@
       <c r="F32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1405,9 @@
       <c r="F33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1332,6 +1434,9 @@
       <c r="F34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1358,6 +1463,9 @@
       <c r="F35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G35" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1384,6 +1492,9 @@
       <c r="F36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1410,6 +1521,9 @@
       <c r="F37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1436,6 +1550,9 @@
       <c r="F38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="G38" s="2" t="n">
+        <v>20.88</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1462,6 +1579,9 @@
       <c r="F39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="G39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1488,6 +1608,9 @@
       <c r="F40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1514,6 +1637,9 @@
       <c r="F41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1540,6 +1666,9 @@
       <c r="F42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1566,6 +1695,9 @@
       <c r="F43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1592,6 +1724,9 @@
       <c r="F44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1618,6 +1753,9 @@
       <c r="F45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1644,6 +1782,9 @@
       <c r="F46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="G46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1670,6 +1811,9 @@
       <c r="F47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1696,6 +1840,9 @@
       <c r="F48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1722,6 +1869,9 @@
       <c r="F49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1748,6 +1898,9 @@
       <c r="F50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1774,6 +1927,9 @@
       <c r="F51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="G51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1800,6 +1956,9 @@
       <c r="F52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1826,6 +1985,9 @@
       <c r="F53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1852,6 +2014,9 @@
       <c r="F54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1878,6 +2043,9 @@
       <c r="F55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1904,6 +2072,9 @@
       <c r="F56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1930,6 +2101,9 @@
       <c r="F57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1956,6 +2130,9 @@
       <c r="F58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1982,6 +2159,9 @@
       <c r="F59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="G59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2008,6 +2188,9 @@
       <c r="F60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2034,6 +2217,9 @@
       <c r="F61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="G61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2060,6 +2246,9 @@
       <c r="F62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2086,6 +2275,9 @@
       <c r="F63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="G63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2112,6 +2304,9 @@
       <c r="F64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2138,6 +2333,9 @@
       <c r="F65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2164,6 +2362,9 @@
       <c r="F66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2190,6 +2391,9 @@
       <c r="F67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2216,6 +2420,9 @@
       <c r="F68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2242,6 +2449,9 @@
       <c r="F69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G69" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2268,6 +2478,9 @@
       <c r="F70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2294,6 +2507,9 @@
       <c r="F71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2320,6 +2536,9 @@
       <c r="F72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="G72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2346,6 +2565,9 @@
       <c r="F73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G73" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2372,6 +2594,9 @@
       <c r="F74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2398,6 +2623,9 @@
       <c r="F75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2424,6 +2652,9 @@
       <c r="F76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2450,6 +2681,9 @@
       <c r="F77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2476,6 +2710,9 @@
       <c r="F78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2502,6 +2739,9 @@
       <c r="F79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2528,6 +2768,9 @@
       <c r="F80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2554,6 +2797,9 @@
       <c r="F81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2580,6 +2826,9 @@
       <c r="F82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2606,6 +2855,9 @@
       <c r="F83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2632,6 +2884,9 @@
       <c r="F84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2658,6 +2913,9 @@
       <c r="F85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2684,6 +2942,9 @@
       <c r="F86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G86" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2710,6 +2971,9 @@
       <c r="F87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2736,6 +3000,9 @@
       <c r="F88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2762,6 +3029,9 @@
       <c r="F89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2788,6 +3058,9 @@
       <c r="F90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2814,6 +3087,9 @@
       <c r="F91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2840,6 +3116,9 @@
       <c r="F92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2866,6 +3145,9 @@
       <c r="F93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2892,6 +3174,9 @@
       <c r="F94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2918,6 +3203,9 @@
       <c r="F95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2944,6 +3232,9 @@
       <c r="F96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2970,6 +3261,9 @@
       <c r="F97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2996,6 +3290,9 @@
       <c r="F98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3022,6 +3319,9 @@
       <c r="F99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3048,6 +3348,9 @@
       <c r="F100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3074,6 +3377,9 @@
       <c r="F101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3100,6 +3406,9 @@
       <c r="F102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3126,6 +3435,9 @@
       <c r="F103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3152,6 +3464,9 @@
       <c r="F104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3178,6 +3493,9 @@
       <c r="F105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3204,6 +3522,9 @@
       <c r="F106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3230,6 +3551,9 @@
       <c r="F107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3256,6 +3580,9 @@
       <c r="F108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3282,6 +3609,9 @@
       <c r="F109" s="2" t="n">
         <v>21.51</v>
       </c>
+      <c r="G109" s="2" t="n">
+        <v>21.51</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3308,6 +3638,9 @@
       <c r="F110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="G110" s="2" t="n">
+        <v>20.39</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3334,6 +3667,9 @@
       <c r="F111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3360,6 +3696,9 @@
       <c r="F112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3386,6 +3725,9 @@
       <c r="F113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3412,6 +3754,9 @@
       <c r="F114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3438,6 +3783,9 @@
       <c r="F115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3464,6 +3812,9 @@
       <c r="F116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3490,6 +3841,9 @@
       <c r="F117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="G117" s="2" t="n">
+        <v>21.85</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3516,6 +3870,9 @@
       <c r="F118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3542,6 +3899,9 @@
       <c r="F119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3568,6 +3928,9 @@
       <c r="F120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3594,6 +3957,9 @@
       <c r="F121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3620,6 +3986,9 @@
       <c r="F122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3646,6 +4015,9 @@
       <c r="F123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="G123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3672,6 +4044,9 @@
       <c r="F124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3698,6 +4073,9 @@
       <c r="F125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3724,6 +4102,9 @@
       <c r="F126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3750,6 +4131,9 @@
       <c r="F127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3776,6 +4160,9 @@
       <c r="F128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3802,6 +4189,9 @@
       <c r="F129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3828,6 +4218,9 @@
       <c r="F130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3854,6 +4247,9 @@
       <c r="F131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3880,6 +4276,9 @@
       <c r="F132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="G132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3906,6 +4305,9 @@
       <c r="F133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3932,6 +4334,9 @@
       <c r="F134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3958,6 +4363,9 @@
       <c r="F135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3984,6 +4392,9 @@
       <c r="F136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4010,6 +4421,9 @@
       <c r="F137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4036,6 +4450,9 @@
       <c r="F138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4062,6 +4479,9 @@
       <c r="F139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4088,6 +4508,9 @@
       <c r="F140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4114,6 +4537,9 @@
       <c r="F141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4140,6 +4566,9 @@
       <c r="F142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4166,6 +4595,9 @@
       <c r="F143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4192,6 +4624,9 @@
       <c r="F144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4218,6 +4653,9 @@
       <c r="F145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="G145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4244,6 +4682,9 @@
       <c r="F146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4270,6 +4711,9 @@
       <c r="F147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4296,6 +4740,9 @@
       <c r="F148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4322,6 +4769,9 @@
       <c r="F149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="G149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4348,6 +4798,9 @@
       <c r="F150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4374,6 +4827,9 @@
       <c r="F151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="G151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4400,6 +4856,9 @@
       <c r="F152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4426,6 +4885,9 @@
       <c r="F153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4452,6 +4914,9 @@
       <c r="F154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="G154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4478,6 +4943,9 @@
       <c r="F155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4504,6 +4972,9 @@
       <c r="F156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4530,6 +5001,9 @@
       <c r="F157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4556,6 +5030,9 @@
       <c r="F158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4582,6 +5059,9 @@
       <c r="F159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="G159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4608,6 +5088,9 @@
       <c r="F160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4634,6 +5117,9 @@
       <c r="F161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4660,6 +5146,9 @@
       <c r="F162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="G162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4686,6 +5175,9 @@
       <c r="F163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="G163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4712,6 +5204,9 @@
       <c r="F164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="G164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4738,9 +5233,12 @@
       <c r="F165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F165"/>
+  <autoFilter ref="A1:G165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>2026-09-11 10:09</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +515,9 @@
       <c r="G2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="H2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +547,9 @@
       <c r="G3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +579,9 @@
       <c r="G4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="H4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +611,9 @@
       <c r="G5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,6 +643,9 @@
       <c r="G6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,6 +675,9 @@
       <c r="G7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="H7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +707,9 @@
       <c r="G8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +739,9 @@
       <c r="G9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -741,6 +771,9 @@
       <c r="G10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,6 +803,9 @@
       <c r="G11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +835,9 @@
       <c r="G12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -828,6 +867,9 @@
       <c r="G13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="H13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +899,9 @@
       <c r="G14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -886,6 +931,9 @@
       <c r="G15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -915,6 +963,9 @@
       <c r="G16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -944,6 +995,9 @@
       <c r="G17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -973,6 +1027,9 @@
       <c r="G18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1002,6 +1059,9 @@
       <c r="G19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="H19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1031,6 +1091,9 @@
       <c r="G20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="H20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1060,6 +1123,9 @@
       <c r="G21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1089,6 +1155,9 @@
       <c r="G22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1118,6 +1187,9 @@
       <c r="G23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1147,6 +1219,9 @@
       <c r="G24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1176,6 +1251,9 @@
       <c r="G25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1205,6 +1283,9 @@
       <c r="G26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="H26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1234,6 +1315,9 @@
       <c r="G27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1263,6 +1347,9 @@
       <c r="G28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="H28" s="2" t="n">
+        <v>20.54</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1292,6 +1379,9 @@
       <c r="G29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,6 +1411,9 @@
       <c r="G30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1350,6 +1443,9 @@
       <c r="G31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1379,6 +1475,9 @@
       <c r="G32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1507,9 @@
       <c r="G33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1437,6 +1539,9 @@
       <c r="G34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1466,6 +1571,9 @@
       <c r="G35" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1495,6 +1603,9 @@
       <c r="G36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1524,6 +1635,9 @@
       <c r="G37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1553,6 +1667,9 @@
       <c r="G38" s="2" t="n">
         <v>20.88</v>
       </c>
+      <c r="H38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1582,6 +1699,9 @@
       <c r="G39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="H39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,6 +1731,9 @@
       <c r="G40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1640,6 +1763,9 @@
       <c r="G41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1669,6 +1795,9 @@
       <c r="G42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1698,6 +1827,9 @@
       <c r="G43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1727,6 +1859,9 @@
       <c r="G44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1756,6 +1891,9 @@
       <c r="G45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1785,6 +1923,9 @@
       <c r="G46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="H46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1814,6 +1955,9 @@
       <c r="G47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1843,6 +1987,9 @@
       <c r="G48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1872,6 +2019,9 @@
       <c r="G49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1901,6 +2051,9 @@
       <c r="G50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1930,6 +2083,9 @@
       <c r="G51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="H51" s="2" t="n">
+        <v>20.85</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1959,6 +2115,9 @@
       <c r="G52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1988,6 +2147,9 @@
       <c r="G53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2017,6 +2179,9 @@
       <c r="G54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2046,6 +2211,9 @@
       <c r="G55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2075,6 +2243,9 @@
       <c r="G56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2104,6 +2275,9 @@
       <c r="G57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2133,6 +2307,9 @@
       <c r="G58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2162,6 +2339,9 @@
       <c r="G59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="H59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2191,6 +2371,9 @@
       <c r="G60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2220,6 +2403,9 @@
       <c r="G61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="H61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2249,6 +2435,9 @@
       <c r="G62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="H62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2278,6 +2467,9 @@
       <c r="G63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="H63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2307,6 +2499,9 @@
       <c r="G64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2336,6 +2531,9 @@
       <c r="G65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2365,6 +2563,9 @@
       <c r="G66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2394,6 +2595,9 @@
       <c r="G67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2423,6 +2627,9 @@
       <c r="G68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2452,6 +2659,9 @@
       <c r="G69" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2481,6 +2691,9 @@
       <c r="G70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2510,6 +2723,9 @@
       <c r="G71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2539,6 +2755,9 @@
       <c r="G72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="H72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2568,6 +2787,9 @@
       <c r="G73" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2597,6 +2819,9 @@
       <c r="G74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2626,6 +2851,9 @@
       <c r="G75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2655,6 +2883,9 @@
       <c r="G76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2684,6 +2915,9 @@
       <c r="G77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2713,6 +2947,9 @@
       <c r="G78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2742,6 +2979,9 @@
       <c r="G79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2771,6 +3011,9 @@
       <c r="G80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2800,6 +3043,9 @@
       <c r="G81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2829,6 +3075,9 @@
       <c r="G82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2858,6 +3107,9 @@
       <c r="G83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2887,6 +3139,9 @@
       <c r="G84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2916,6 +3171,9 @@
       <c r="G85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2945,6 +3203,9 @@
       <c r="G86" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2974,6 +3235,9 @@
       <c r="G87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3003,6 +3267,9 @@
       <c r="G88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3032,6 +3299,9 @@
       <c r="G89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3061,6 +3331,9 @@
       <c r="G90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3090,6 +3363,9 @@
       <c r="G91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3119,6 +3395,9 @@
       <c r="G92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3148,6 +3427,9 @@
       <c r="G93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3177,6 +3459,9 @@
       <c r="G94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3206,6 +3491,9 @@
       <c r="G95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3235,6 +3523,9 @@
       <c r="G96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3264,6 +3555,9 @@
       <c r="G97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3293,6 +3587,9 @@
       <c r="G98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3322,6 +3619,9 @@
       <c r="G99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3351,6 +3651,9 @@
       <c r="G100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3380,6 +3683,9 @@
       <c r="G101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3409,6 +3715,9 @@
       <c r="G102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3438,6 +3747,9 @@
       <c r="G103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3467,6 +3779,9 @@
       <c r="G104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3496,6 +3811,9 @@
       <c r="G105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3525,6 +3843,9 @@
       <c r="G106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3554,6 +3875,9 @@
       <c r="G107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3583,6 +3907,9 @@
       <c r="G108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3612,6 +3939,9 @@
       <c r="G109" s="2" t="n">
         <v>21.51</v>
       </c>
+      <c r="H109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3641,6 +3971,9 @@
       <c r="G110" s="2" t="n">
         <v>20.39</v>
       </c>
+      <c r="H110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3670,6 +4003,9 @@
       <c r="G111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3699,6 +4035,9 @@
       <c r="G112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3728,6 +4067,9 @@
       <c r="G113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3757,6 +4099,9 @@
       <c r="G114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3786,6 +4131,9 @@
       <c r="G115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3815,6 +4163,9 @@
       <c r="G116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3844,6 +4195,9 @@
       <c r="G117" s="2" t="n">
         <v>21.85</v>
       </c>
+      <c r="H117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3873,6 +4227,9 @@
       <c r="G118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3902,6 +4259,9 @@
       <c r="G119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3931,6 +4291,9 @@
       <c r="G120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3960,6 +4323,9 @@
       <c r="G121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3989,6 +4355,9 @@
       <c r="G122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4018,6 +4387,9 @@
       <c r="G123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="H123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4047,6 +4419,9 @@
       <c r="G124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4076,6 +4451,9 @@
       <c r="G125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4105,6 +4483,9 @@
       <c r="G126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4134,6 +4515,9 @@
       <c r="G127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4163,6 +4547,9 @@
       <c r="G128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4192,6 +4579,9 @@
       <c r="G129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4221,6 +4611,9 @@
       <c r="G130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4250,6 +4643,9 @@
       <c r="G131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4279,6 +4675,9 @@
       <c r="G132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="H132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4308,6 +4707,9 @@
       <c r="G133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4337,6 +4739,9 @@
       <c r="G134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4366,6 +4771,9 @@
       <c r="G135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4395,6 +4803,9 @@
       <c r="G136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4424,6 +4835,9 @@
       <c r="G137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4453,6 +4867,9 @@
       <c r="G138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H138" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4482,6 +4899,9 @@
       <c r="G139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4511,6 +4931,9 @@
       <c r="G140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4540,6 +4963,9 @@
       <c r="G141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4569,6 +4995,9 @@
       <c r="G142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4598,6 +5027,9 @@
       <c r="G143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4627,6 +5059,9 @@
       <c r="G144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4656,6 +5091,9 @@
       <c r="G145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="H145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4685,6 +5123,9 @@
       <c r="G146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4714,6 +5155,9 @@
       <c r="G147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4743,6 +5187,9 @@
       <c r="G148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4772,6 +5219,9 @@
       <c r="G149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="H149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4801,6 +5251,9 @@
       <c r="G150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4830,6 +5283,9 @@
       <c r="G151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="H151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4859,6 +5315,9 @@
       <c r="G152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4888,6 +5347,9 @@
       <c r="G153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4917,6 +5379,9 @@
       <c r="G154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="H154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4946,6 +5411,9 @@
       <c r="G155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4975,6 +5443,9 @@
       <c r="G156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5004,6 +5475,9 @@
       <c r="G157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5033,6 +5507,9 @@
       <c r="G158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5062,6 +5539,9 @@
       <c r="G159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="H159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5091,6 +5571,9 @@
       <c r="G160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5120,6 +5603,9 @@
       <c r="G161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5149,6 +5635,9 @@
       <c r="G162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="H162" s="2" t="n">
+        <v>23.49</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5178,6 +5667,9 @@
       <c r="G163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="H163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5207,6 +5699,9 @@
       <c r="G164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="H164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5236,9 +5731,12 @@
       <c r="G165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G165"/>
+  <autoFilter ref="A1:H165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +487,11 @@
           <t>2026-09-11 13:10</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 16:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +524,9 @@
       <c r="H2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,6 +559,9 @@
       <c r="H3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,6 +594,9 @@
       <c r="H4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,6 +629,9 @@
       <c r="H5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,6 +664,9 @@
       <c r="H6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +699,9 @@
       <c r="H7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -710,6 +734,9 @@
       <c r="H8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,6 +769,9 @@
       <c r="H9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -774,6 +804,9 @@
       <c r="H10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,6 +839,9 @@
       <c r="H11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -838,6 +874,9 @@
       <c r="H12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -870,6 +909,9 @@
       <c r="H13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -902,6 +944,9 @@
       <c r="H14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,6 +979,9 @@
       <c r="H15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -966,6 +1014,9 @@
       <c r="H16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -998,6 +1049,9 @@
       <c r="H17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1030,6 +1084,9 @@
       <c r="H18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1062,6 +1119,9 @@
       <c r="H19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1094,6 +1154,9 @@
       <c r="H20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1126,6 +1189,9 @@
       <c r="H21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1158,6 +1224,9 @@
       <c r="H22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1190,6 +1259,9 @@
       <c r="H23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1222,6 +1294,9 @@
       <c r="H24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,6 +1329,9 @@
       <c r="H25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1286,6 +1364,9 @@
       <c r="H26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1318,6 +1399,9 @@
       <c r="H27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1350,6 +1434,9 @@
       <c r="H28" s="2" t="n">
         <v>20.54</v>
       </c>
+      <c r="I28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1382,6 +1469,9 @@
       <c r="H29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1414,6 +1504,9 @@
       <c r="H30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1446,6 +1539,9 @@
       <c r="H31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1478,6 +1574,9 @@
       <c r="H32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,6 +1609,9 @@
       <c r="H33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1542,6 +1644,9 @@
       <c r="H34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1574,6 +1679,9 @@
       <c r="H35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1606,6 +1714,9 @@
       <c r="H36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1638,6 +1749,9 @@
       <c r="H37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1670,6 +1784,9 @@
       <c r="H38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1702,6 +1819,9 @@
       <c r="H39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="I39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1734,6 +1854,9 @@
       <c r="H40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1766,6 +1889,9 @@
       <c r="H41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I41" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1798,6 +1924,9 @@
       <c r="H42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1830,6 +1959,9 @@
       <c r="H43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1862,6 +1994,9 @@
       <c r="H44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1894,6 +2029,9 @@
       <c r="H45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1926,6 +2064,9 @@
       <c r="H46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="I46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1958,6 +2099,9 @@
       <c r="H47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1990,6 +2134,9 @@
       <c r="H48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2022,6 +2169,9 @@
       <c r="H49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2054,6 +2204,9 @@
       <c r="H50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2086,6 +2239,9 @@
       <c r="H51" s="2" t="n">
         <v>20.85</v>
       </c>
+      <c r="I51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2118,6 +2274,9 @@
       <c r="H52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2150,6 +2309,9 @@
       <c r="H53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2182,6 +2344,9 @@
       <c r="H54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2214,6 +2379,9 @@
       <c r="H55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2246,6 +2414,9 @@
       <c r="H56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2278,6 +2449,9 @@
       <c r="H57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,6 +2484,9 @@
       <c r="H58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2342,6 +2519,9 @@
       <c r="H59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="I59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2374,6 +2554,9 @@
       <c r="H60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2406,6 +2589,9 @@
       <c r="H61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="I61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2438,6 +2624,9 @@
       <c r="H62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="I62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,6 +2659,9 @@
       <c r="H63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="I63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2502,6 +2694,9 @@
       <c r="H64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,6 +2729,9 @@
       <c r="H65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2566,6 +2764,9 @@
       <c r="H66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2598,6 +2799,9 @@
       <c r="H67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2630,6 +2834,9 @@
       <c r="H68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2662,6 +2869,9 @@
       <c r="H69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2694,6 +2904,9 @@
       <c r="H70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2726,6 +2939,9 @@
       <c r="H71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2758,6 +2974,9 @@
       <c r="H72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="I72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2790,6 +3009,9 @@
       <c r="H73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2822,6 +3044,9 @@
       <c r="H74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2854,6 +3079,9 @@
       <c r="H75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2886,6 +3114,9 @@
       <c r="H76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2918,6 +3149,9 @@
       <c r="H77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2950,6 +3184,9 @@
       <c r="H78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2982,6 +3219,9 @@
       <c r="H79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3014,6 +3254,9 @@
       <c r="H80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3046,6 +3289,9 @@
       <c r="H81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3078,6 +3324,9 @@
       <c r="H82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3110,6 +3359,9 @@
       <c r="H83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3142,6 +3394,9 @@
       <c r="H84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3174,6 +3429,9 @@
       <c r="H85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3206,6 +3464,9 @@
       <c r="H86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3238,6 +3499,9 @@
       <c r="H87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3270,6 +3534,9 @@
       <c r="H88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3302,6 +3569,9 @@
       <c r="H89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3334,6 +3604,9 @@
       <c r="H90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3366,6 +3639,9 @@
       <c r="H91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3398,6 +3674,9 @@
       <c r="H92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3430,6 +3709,9 @@
       <c r="H93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3462,6 +3744,9 @@
       <c r="H94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3494,6 +3779,9 @@
       <c r="H95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3526,6 +3814,9 @@
       <c r="H96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3558,6 +3849,9 @@
       <c r="H97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3590,6 +3884,9 @@
       <c r="H98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3622,6 +3919,9 @@
       <c r="H99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3654,6 +3954,9 @@
       <c r="H100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3686,6 +3989,9 @@
       <c r="H101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3718,6 +4024,9 @@
       <c r="H102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3750,6 +4059,9 @@
       <c r="H103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3782,6 +4094,9 @@
       <c r="H104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3814,6 +4129,9 @@
       <c r="H105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3846,6 +4164,9 @@
       <c r="H106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3878,6 +4199,9 @@
       <c r="H107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3910,6 +4234,9 @@
       <c r="H108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3942,6 +4269,9 @@
       <c r="H109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3974,6 +4304,9 @@
       <c r="H110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4006,6 +4339,9 @@
       <c r="H111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4038,6 +4374,9 @@
       <c r="H112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4070,6 +4409,9 @@
       <c r="H113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4102,6 +4444,9 @@
       <c r="H114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4134,6 +4479,9 @@
       <c r="H115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4166,6 +4514,9 @@
       <c r="H116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4198,6 +4549,9 @@
       <c r="H117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4230,6 +4584,9 @@
       <c r="H118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4262,6 +4619,9 @@
       <c r="H119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4294,6 +4654,9 @@
       <c r="H120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I120" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4326,6 +4689,9 @@
       <c r="H121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4358,6 +4724,9 @@
       <c r="H122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4390,6 +4759,9 @@
       <c r="H123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="I123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4422,6 +4794,9 @@
       <c r="H124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4454,6 +4829,9 @@
       <c r="H125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4486,6 +4864,9 @@
       <c r="H126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4518,6 +4899,9 @@
       <c r="H127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4550,6 +4934,9 @@
       <c r="H128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4582,6 +4969,9 @@
       <c r="H129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4614,6 +5004,9 @@
       <c r="H130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4646,6 +5039,9 @@
       <c r="H131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4678,6 +5074,9 @@
       <c r="H132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="I132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4710,6 +5109,9 @@
       <c r="H133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4742,6 +5144,9 @@
       <c r="H134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4774,6 +5179,9 @@
       <c r="H135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4806,6 +5214,9 @@
       <c r="H136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4838,6 +5249,9 @@
       <c r="H137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4870,6 +5284,9 @@
       <c r="H138" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I138" s="2" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4902,6 +5319,9 @@
       <c r="H139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4934,6 +5354,9 @@
       <c r="H140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4966,6 +5389,9 @@
       <c r="H141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4998,6 +5424,9 @@
       <c r="H142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5030,6 +5459,9 @@
       <c r="H143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5062,6 +5494,9 @@
       <c r="H144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5094,6 +5529,9 @@
       <c r="H145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="I145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5126,6 +5564,9 @@
       <c r="H146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5158,6 +5599,9 @@
       <c r="H147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5190,6 +5634,9 @@
       <c r="H148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5222,6 +5669,9 @@
       <c r="H149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="I149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5254,6 +5704,9 @@
       <c r="H150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5286,6 +5739,9 @@
       <c r="H151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="I151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5318,6 +5774,9 @@
       <c r="H152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5350,6 +5809,9 @@
       <c r="H153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5382,6 +5844,9 @@
       <c r="H154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="I154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5414,6 +5879,9 @@
       <c r="H155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5446,6 +5914,9 @@
       <c r="H156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5478,6 +5949,9 @@
       <c r="H157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5510,6 +5984,9 @@
       <c r="H158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5542,6 +6019,9 @@
       <c r="H159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="I159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5574,6 +6054,9 @@
       <c r="H160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5606,6 +6089,9 @@
       <c r="H161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5638,6 +6124,9 @@
       <c r="H162" s="2" t="n">
         <v>23.49</v>
       </c>
+      <c r="I162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5670,6 +6159,9 @@
       <c r="H163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="I163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5702,6 +6194,9 @@
       <c r="H164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="I164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5734,9 +6229,12 @@
       <c r="H165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I165" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H165"/>
+  <autoFilter ref="A1:I165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,6 +493,11 @@
           <t>2026-09-11 16:08</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 19:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +533,9 @@
       <c r="I2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="J2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +571,9 @@
       <c r="I3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="J3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +609,9 @@
       <c r="I4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,6 +647,9 @@
       <c r="I5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +685,9 @@
       <c r="I6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +723,9 @@
       <c r="I7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="J7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +761,9 @@
       <c r="I8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="J8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +799,9 @@
       <c r="I9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="J9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -807,6 +837,9 @@
       <c r="I10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,6 +875,9 @@
       <c r="I11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="J11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -877,6 +913,9 @@
       <c r="I12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -912,6 +951,9 @@
       <c r="I13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="J13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -947,6 +989,9 @@
       <c r="I14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -982,6 +1027,9 @@
       <c r="I15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1017,6 +1065,9 @@
       <c r="I16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,6 +1103,9 @@
       <c r="I17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1087,6 +1141,9 @@
       <c r="I18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1122,6 +1179,9 @@
       <c r="I19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="J19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1157,6 +1217,9 @@
       <c r="I20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="J20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1192,6 +1255,9 @@
       <c r="I21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="J21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1227,6 +1293,9 @@
       <c r="I22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1262,6 +1331,9 @@
       <c r="I23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1297,6 +1369,9 @@
       <c r="I24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1332,6 +1407,9 @@
       <c r="I25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1367,6 +1445,9 @@
       <c r="I26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="J26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1402,6 +1483,9 @@
       <c r="I27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1437,6 +1521,9 @@
       <c r="I28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1472,6 +1559,9 @@
       <c r="I29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1597,9 @@
       <c r="I30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1542,6 +1635,9 @@
       <c r="I31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1577,6 +1673,9 @@
       <c r="I32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1612,6 +1711,9 @@
       <c r="I33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1647,6 +1749,9 @@
       <c r="I34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1682,6 +1787,9 @@
       <c r="I35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1717,6 +1825,9 @@
       <c r="I36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1752,6 +1863,9 @@
       <c r="I37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1787,6 +1901,9 @@
       <c r="I38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1822,6 +1939,9 @@
       <c r="I39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="J39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1857,6 +1977,9 @@
       <c r="I40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1892,6 +2015,9 @@
       <c r="I41" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,6 +2053,9 @@
       <c r="I42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1962,6 +2091,9 @@
       <c r="I43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1997,6 +2129,9 @@
       <c r="I44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2032,6 +2167,9 @@
       <c r="I45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2067,6 +2205,9 @@
       <c r="I46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="J46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2102,6 +2243,9 @@
       <c r="I47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2137,6 +2281,9 @@
       <c r="I48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2172,6 +2319,9 @@
       <c r="I49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2207,6 +2357,9 @@
       <c r="I50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2242,6 +2395,9 @@
       <c r="I51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="J51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2277,6 +2433,9 @@
       <c r="I52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2312,6 +2471,9 @@
       <c r="I53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2347,6 +2509,9 @@
       <c r="I54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2382,6 +2547,9 @@
       <c r="I55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2417,6 +2585,9 @@
       <c r="I56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2452,6 +2623,9 @@
       <c r="I57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2487,6 +2661,9 @@
       <c r="I58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2522,6 +2699,9 @@
       <c r="I59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="J59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2557,6 +2737,9 @@
       <c r="I60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2592,6 +2775,9 @@
       <c r="I61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="J61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2627,6 +2813,9 @@
       <c r="I62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="J62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +2851,9 @@
       <c r="I63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="J63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2697,6 +2889,9 @@
       <c r="I64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2732,6 +2927,9 @@
       <c r="I65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2767,6 +2965,9 @@
       <c r="I66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2802,6 +3003,9 @@
       <c r="I67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2837,6 +3041,9 @@
       <c r="I68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2872,6 +3079,9 @@
       <c r="I69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2907,6 +3117,9 @@
       <c r="I70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2942,6 +3155,9 @@
       <c r="I71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2977,6 +3193,9 @@
       <c r="I72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="J72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3012,6 +3231,9 @@
       <c r="I73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3047,6 +3269,9 @@
       <c r="I74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3082,6 +3307,9 @@
       <c r="I75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3117,6 +3345,9 @@
       <c r="I76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3152,6 +3383,9 @@
       <c r="I77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3187,6 +3421,9 @@
       <c r="I78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3222,6 +3459,9 @@
       <c r="I79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3257,6 +3497,9 @@
       <c r="I80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3292,6 +3535,9 @@
       <c r="I81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3327,6 +3573,9 @@
       <c r="I82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3362,6 +3611,9 @@
       <c r="I83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3397,6 +3649,9 @@
       <c r="I84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3432,6 +3687,9 @@
       <c r="I85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3467,6 +3725,9 @@
       <c r="I86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3502,6 +3763,9 @@
       <c r="I87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3537,6 +3801,9 @@
       <c r="I88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3572,6 +3839,9 @@
       <c r="I89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3607,6 +3877,9 @@
       <c r="I90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3642,6 +3915,9 @@
       <c r="I91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3677,6 +3953,9 @@
       <c r="I92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3712,6 +3991,9 @@
       <c r="I93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3747,6 +4029,9 @@
       <c r="I94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3782,6 +4067,9 @@
       <c r="I95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3817,6 +4105,9 @@
       <c r="I96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3852,6 +4143,9 @@
       <c r="I97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3887,6 +4181,9 @@
       <c r="I98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3922,6 +4219,9 @@
       <c r="I99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3957,6 +4257,9 @@
       <c r="I100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3992,6 +4295,9 @@
       <c r="I101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4027,6 +4333,9 @@
       <c r="I102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4062,6 +4371,9 @@
       <c r="I103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4097,6 +4409,9 @@
       <c r="I104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4132,6 +4447,9 @@
       <c r="I105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4167,6 +4485,9 @@
       <c r="I106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4202,6 +4523,9 @@
       <c r="I107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4237,6 +4561,9 @@
       <c r="I108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J108" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4272,6 +4599,9 @@
       <c r="I109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4307,6 +4637,9 @@
       <c r="I110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4342,6 +4675,9 @@
       <c r="I111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4377,6 +4713,9 @@
       <c r="I112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4412,6 +4751,9 @@
       <c r="I113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4447,6 +4789,9 @@
       <c r="I114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4482,6 +4827,9 @@
       <c r="I115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4517,6 +4865,9 @@
       <c r="I116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4552,6 +4903,9 @@
       <c r="I117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4587,6 +4941,9 @@
       <c r="I118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4622,6 +4979,9 @@
       <c r="I119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4657,6 +5017,9 @@
       <c r="I120" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4692,6 +5055,9 @@
       <c r="I121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4727,6 +5093,9 @@
       <c r="I122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4762,6 +5131,9 @@
       <c r="I123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="J123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4797,6 +5169,9 @@
       <c r="I124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4832,6 +5207,9 @@
       <c r="I125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4867,6 +5245,9 @@
       <c r="I126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4902,6 +5283,9 @@
       <c r="I127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4937,6 +5321,9 @@
       <c r="I128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4972,6 +5359,9 @@
       <c r="I129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5007,6 +5397,9 @@
       <c r="I130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5042,6 +5435,9 @@
       <c r="I131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5077,6 +5473,9 @@
       <c r="I132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="J132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5112,6 +5511,9 @@
       <c r="I133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5147,6 +5549,9 @@
       <c r="I134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5182,6 +5587,9 @@
       <c r="I135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5217,6 +5625,9 @@
       <c r="I136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5252,6 +5663,9 @@
       <c r="I137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5287,6 +5701,9 @@
       <c r="I138" s="2" t="n">
         <v>22.19</v>
       </c>
+      <c r="J138" s="2" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5322,6 +5739,9 @@
       <c r="I139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5357,6 +5777,9 @@
       <c r="I140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5392,6 +5815,9 @@
       <c r="I141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5427,6 +5853,9 @@
       <c r="I142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5462,6 +5891,9 @@
       <c r="I143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5497,6 +5929,9 @@
       <c r="I144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5532,6 +5967,9 @@
       <c r="I145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="J145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5567,6 +6005,9 @@
       <c r="I146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5602,6 +6043,9 @@
       <c r="I147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5637,6 +6081,9 @@
       <c r="I148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5672,6 +6119,9 @@
       <c r="I149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="J149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5707,6 +6157,9 @@
       <c r="I150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5742,6 +6195,9 @@
       <c r="I151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="J151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5777,6 +6233,9 @@
       <c r="I152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5812,6 +6271,9 @@
       <c r="I153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5847,6 +6309,9 @@
       <c r="I154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="J154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5882,6 +6347,9 @@
       <c r="I155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5917,6 +6385,9 @@
       <c r="I156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5952,6 +6423,9 @@
       <c r="I157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5987,6 +6461,9 @@
       <c r="I158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6022,6 +6499,9 @@
       <c r="I159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6057,6 +6537,9 @@
       <c r="I160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6092,6 +6575,9 @@
       <c r="I161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6127,6 +6613,9 @@
       <c r="I162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6162,6 +6651,9 @@
       <c r="I163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="J163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6197,6 +6689,9 @@
       <c r="I164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="J164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6232,9 +6727,12 @@
       <c r="I165" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I165"/>
+  <autoFilter ref="A1:J165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -445,6 +445,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +499,11 @@
           <t>2026-09-11 19:12</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,6 +542,9 @@
       <c r="J2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="K2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,6 +583,9 @@
       <c r="J3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="K3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,6 +624,9 @@
       <c r="J4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="K4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +665,9 @@
       <c r="J5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,6 +706,9 @@
       <c r="J6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="K6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,6 +747,9 @@
       <c r="J7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="K7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,6 +788,9 @@
       <c r="J8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="K8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -802,6 +829,9 @@
       <c r="J9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="K9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -840,6 +870,9 @@
       <c r="J10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,6 +911,9 @@
       <c r="J11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="K11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -916,6 +952,9 @@
       <c r="J12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -954,6 +993,9 @@
       <c r="J13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="K13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -992,6 +1034,9 @@
       <c r="J14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1030,6 +1075,9 @@
       <c r="J15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="K15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1068,6 +1116,9 @@
       <c r="J16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1106,6 +1157,9 @@
       <c r="J17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1144,6 +1198,9 @@
       <c r="J18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1182,6 +1239,9 @@
       <c r="J19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="K19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1220,6 +1280,9 @@
       <c r="J20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="K20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1258,6 +1321,9 @@
       <c r="J21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="K21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1296,6 +1362,9 @@
       <c r="J22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1334,6 +1403,9 @@
       <c r="J23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1372,6 +1444,9 @@
       <c r="J24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1410,6 +1485,9 @@
       <c r="J25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1448,6 +1526,9 @@
       <c r="J26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="K26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1486,6 +1567,9 @@
       <c r="J27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1524,6 +1608,9 @@
       <c r="J28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1562,6 +1649,9 @@
       <c r="J29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1600,6 +1690,9 @@
       <c r="J30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1638,6 +1731,9 @@
       <c r="J31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1676,6 +1772,9 @@
       <c r="J32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1714,6 +1813,9 @@
       <c r="J33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1752,6 +1854,9 @@
       <c r="J34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1790,6 +1895,9 @@
       <c r="J35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1828,6 +1936,9 @@
       <c r="J36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1866,6 +1977,9 @@
       <c r="J37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="K37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1904,6 +2018,9 @@
       <c r="J38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1942,6 +2059,9 @@
       <c r="J39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="K39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1980,6 +2100,9 @@
       <c r="J40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2018,6 +2141,9 @@
       <c r="J41" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2056,6 +2182,9 @@
       <c r="J42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2094,6 +2223,9 @@
       <c r="J43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2132,6 +2264,9 @@
       <c r="J44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2170,6 +2305,9 @@
       <c r="J45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="K45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2208,6 +2346,9 @@
       <c r="J46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="K46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2246,6 +2387,9 @@
       <c r="J47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2284,6 +2428,9 @@
       <c r="J48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2322,6 +2469,9 @@
       <c r="J49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2360,6 +2510,9 @@
       <c r="J50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2398,6 +2551,9 @@
       <c r="J51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="K51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2436,6 +2592,9 @@
       <c r="J52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="K52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2474,6 +2633,9 @@
       <c r="J53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2512,6 +2674,9 @@
       <c r="J54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="K54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2550,6 +2715,9 @@
       <c r="J55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2588,6 +2756,9 @@
       <c r="J56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2626,6 +2797,9 @@
       <c r="J57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="K57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2664,6 +2838,9 @@
       <c r="J58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="K58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2702,6 +2879,9 @@
       <c r="J59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="K59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2740,6 +2920,9 @@
       <c r="J60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="K60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2778,6 +2961,9 @@
       <c r="J61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="K61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2816,6 +3002,9 @@
       <c r="J62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="K62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2854,6 +3043,9 @@
       <c r="J63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="K63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2892,6 +3084,9 @@
       <c r="J64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="K64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2930,6 +3125,9 @@
       <c r="J65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2968,6 +3166,9 @@
       <c r="J66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3006,6 +3207,9 @@
       <c r="J67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3044,6 +3248,9 @@
       <c r="J68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3082,6 +3289,9 @@
       <c r="J69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3120,6 +3330,9 @@
       <c r="J70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3158,6 +3371,9 @@
       <c r="J71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3196,6 +3412,9 @@
       <c r="J72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="K72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3234,6 +3453,9 @@
       <c r="J73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3272,6 +3494,9 @@
       <c r="J74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3310,6 +3535,9 @@
       <c r="J75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3348,6 +3576,9 @@
       <c r="J76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3386,6 +3617,9 @@
       <c r="J77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3424,6 +3658,9 @@
       <c r="J78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3462,6 +3699,9 @@
       <c r="J79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3500,6 +3740,9 @@
       <c r="J80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3538,6 +3781,9 @@
       <c r="J81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3576,6 +3822,9 @@
       <c r="J82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3614,6 +3863,9 @@
       <c r="J83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3652,6 +3904,9 @@
       <c r="J84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="K84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3690,6 +3945,9 @@
       <c r="J85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3728,6 +3986,9 @@
       <c r="J86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3766,6 +4027,9 @@
       <c r="J87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3804,6 +4068,9 @@
       <c r="J88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3842,6 +4109,9 @@
       <c r="J89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3880,6 +4150,9 @@
       <c r="J90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3918,6 +4191,9 @@
       <c r="J91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3956,6 +4232,9 @@
       <c r="J92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3994,6 +4273,9 @@
       <c r="J93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="K93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4032,6 +4314,9 @@
       <c r="J94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4070,6 +4355,9 @@
       <c r="J95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4108,6 +4396,9 @@
       <c r="J96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="K96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4146,6 +4437,9 @@
       <c r="J97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4184,6 +4478,9 @@
       <c r="J98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="K98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4222,6 +4519,9 @@
       <c r="J99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4260,6 +4560,9 @@
       <c r="J100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4298,6 +4601,9 @@
       <c r="J101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4336,6 +4642,9 @@
       <c r="J102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="K102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4374,6 +4683,9 @@
       <c r="J103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="K103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4412,6 +4724,9 @@
       <c r="J104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4450,6 +4765,9 @@
       <c r="J105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4488,6 +4806,9 @@
       <c r="J106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="K106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4526,6 +4847,9 @@
       <c r="J107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="K107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4564,6 +4888,9 @@
       <c r="J108" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="K108" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4602,6 +4929,9 @@
       <c r="J109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4640,6 +4970,9 @@
       <c r="J110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="K110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4678,6 +5011,9 @@
       <c r="J111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="K111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4716,6 +5052,9 @@
       <c r="J112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4754,6 +5093,9 @@
       <c r="J113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4792,6 +5134,9 @@
       <c r="J114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4830,6 +5175,9 @@
       <c r="J115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="K115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4868,6 +5216,9 @@
       <c r="J116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4906,6 +5257,9 @@
       <c r="J117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="K117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4944,6 +5298,9 @@
       <c r="J118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="K118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4982,6 +5339,9 @@
       <c r="J119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="K119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5020,6 +5380,9 @@
       <c r="J120" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="K120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5058,6 +5421,9 @@
       <c r="J121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="K121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5096,6 +5462,9 @@
       <c r="J122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="K122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5134,6 +5503,9 @@
       <c r="J123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="K123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5172,6 +5544,9 @@
       <c r="J124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5210,6 +5585,9 @@
       <c r="J125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5248,6 +5626,9 @@
       <c r="J126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5286,6 +5667,9 @@
       <c r="J127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="K127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5324,6 +5708,9 @@
       <c r="J128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5362,6 +5749,9 @@
       <c r="J129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5400,6 +5790,9 @@
       <c r="J130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="K130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5438,6 +5831,9 @@
       <c r="J131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="K131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5476,6 +5872,9 @@
       <c r="J132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="K132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5514,6 +5913,9 @@
       <c r="J133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5552,6 +5954,9 @@
       <c r="J134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="K134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5590,6 +5995,9 @@
       <c r="J135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5628,6 +6036,9 @@
       <c r="J136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5666,6 +6077,9 @@
       <c r="J137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="K137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5704,6 +6118,9 @@
       <c r="J138" s="2" t="n">
         <v>22.19</v>
       </c>
+      <c r="K138" s="2" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5742,6 +6159,9 @@
       <c r="J139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5780,6 +6200,9 @@
       <c r="J140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5818,6 +6241,9 @@
       <c r="J141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5856,6 +6282,9 @@
       <c r="J142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5894,6 +6323,9 @@
       <c r="J143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5932,6 +6364,9 @@
       <c r="J144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="K144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5970,6 +6405,9 @@
       <c r="J145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="K145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6008,6 +6446,9 @@
       <c r="J146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6046,6 +6487,9 @@
       <c r="J147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="K147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6084,6 +6528,9 @@
       <c r="J148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="K148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6122,6 +6569,9 @@
       <c r="J149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="K149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6160,6 +6610,9 @@
       <c r="J150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="K150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6198,6 +6651,9 @@
       <c r="J151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="K151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6236,6 +6692,9 @@
       <c r="J152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6274,6 +6733,9 @@
       <c r="J153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="K153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6312,6 +6774,9 @@
       <c r="J154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="K154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6350,6 +6815,9 @@
       <c r="J155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="K155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6388,6 +6856,9 @@
       <c r="J156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6426,6 +6897,9 @@
       <c r="J157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="K157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6464,6 +6938,9 @@
       <c r="J158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6502,6 +6979,9 @@
       <c r="J159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="K159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6540,6 +7020,9 @@
       <c r="J160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6578,6 +7061,9 @@
       <c r="J161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="K161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6616,6 +7102,9 @@
       <c r="J162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="K162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6654,6 +7143,9 @@
       <c r="J163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="K163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6692,6 +7184,9 @@
       <c r="J164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="K164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6730,9 +7225,12 @@
       <c r="J165" s="2" t="n">
         <v>20.59</v>
       </c>
+      <c r="K165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J165"/>
+  <autoFilter ref="A1:K165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$K$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,20 +432,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,42 +459,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-11 01:11</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-11 04:09</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-11 07:12</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-11 10:09</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:10</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-11 16:08</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-11 19:12</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-11 22:09</t>
+          <t>2026-09-12 01:11</t>
         </is>
       </c>
     </row>
@@ -524,27 +482,6 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>13.45</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,27 +502,6 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -606,27 +522,6 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>17.95</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,27 +542,6 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,27 +562,6 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -729,27 +582,6 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>19.49</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>19.49</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -770,27 +602,6 @@
       <c r="D8" s="2" t="n">
         <v>20.49</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>20.49</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -811,27 +622,6 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -852,27 +642,6 @@
       <c r="D10" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -893,27 +662,6 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>20.19</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,27 +682,6 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,27 +702,6 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>20.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1016,27 +722,6 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1057,27 +742,6 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>20.34</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,27 +762,6 @@
       <c r="D16" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1137,27 +780,6 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K17" s="2" t="n">
         <v>20.89</v>
       </c>
     </row>
@@ -1180,27 +802,6 @@
       <c r="D18" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1221,27 +822,6 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>20.77</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1262,27 +842,6 @@
       <c r="D20" s="2" t="n">
         <v>20.65</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>20.65</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1303,27 +862,6 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>20.48</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>20.48</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1344,27 +882,6 @@
       <c r="D22" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1385,27 +902,6 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1426,27 +922,6 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1467,27 +942,6 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1508,27 +962,6 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>20.8</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1549,27 +982,6 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1588,27 +1000,6 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K28" s="2" t="n">
         <v>21.09</v>
       </c>
     </row>
@@ -1631,27 +1022,6 @@
       <c r="D29" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1672,27 +1042,6 @@
       <c r="D30" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1713,27 +1062,6 @@
       <c r="D31" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1754,27 +1082,6 @@
       <c r="D32" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1795,27 +1102,6 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1836,27 +1122,6 @@
       <c r="D34" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1875,27 +1140,6 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K35" s="2" t="n">
         <v>20.79</v>
       </c>
     </row>
@@ -1918,27 +1162,6 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1959,27 +1182,6 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>20.68</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1998,27 +1200,6 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K38" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -2041,27 +1222,6 @@
       <c r="D39" s="2" t="n">
         <v>20.98</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>20.98</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2082,27 +1242,6 @@
       <c r="D40" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2121,27 +1260,6 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K41" s="2" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -2164,27 +1282,6 @@
       <c r="D42" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2205,27 +1302,6 @@
       <c r="D43" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2246,27 +1322,6 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2287,27 +1342,6 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>20.69</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2328,27 +1362,6 @@
       <c r="D46" s="2" t="n">
         <v>21.15</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>21.15</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2369,27 +1382,6 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2410,27 +1402,6 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>20.79</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2451,27 +1422,6 @@
       <c r="D49" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2492,27 +1442,6 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2531,27 +1460,6 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="K51" s="2" t="n">
         <v>21.69</v>
       </c>
     </row>
@@ -2574,27 +1482,6 @@
       <c r="D52" s="2" t="n">
         <v>22.35</v>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>22.35</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2615,27 +1502,6 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2656,27 +1522,6 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>21.79</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2697,27 +1542,6 @@
       <c r="D55" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2738,27 +1562,6 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2779,27 +1582,6 @@
       <c r="D57" s="2" t="n">
         <v>20.89</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>20.89</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2820,27 +1602,6 @@
       <c r="D58" s="2" t="n">
         <v>21.75</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>21.75</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2861,27 +1622,6 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>22.2</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2902,27 +1642,6 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>20.9</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2943,27 +1662,6 @@
       <c r="D61" s="2" t="n">
         <v>21.55</v>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="J61" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>21.55</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2982,27 +1680,6 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="K62" s="2" t="n">
         <v>21.55</v>
       </c>
     </row>
@@ -3025,27 +1702,6 @@
       <c r="D63" s="2" t="n">
         <v>21.25</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="K63" s="2" t="n">
-        <v>21.25</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3066,27 +1722,6 @@
       <c r="D64" s="2" t="n">
         <v>21.79</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="J64" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>21.79</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3107,27 +1742,6 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K65" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3148,27 +1762,6 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3189,27 +1782,6 @@
       <c r="D67" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3230,27 +1802,6 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J68" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3269,27 +1820,6 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J69" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K69" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -3312,27 +1842,6 @@
       <c r="D70" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3353,27 +1862,6 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K71" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3394,27 +1882,6 @@
       <c r="D72" s="2" t="n">
         <v>21.29</v>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>21.29</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3433,27 +1900,6 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K73" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -3476,27 +1922,6 @@
       <c r="D74" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J74" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3517,27 +1942,6 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3558,27 +1962,6 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J76" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3599,27 +1982,6 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3640,27 +2002,6 @@
       <c r="D78" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3681,27 +2022,6 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3722,27 +2042,6 @@
       <c r="D80" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3763,27 +2062,6 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3804,27 +2082,6 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3845,27 +2102,6 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3886,27 +2122,6 @@
       <c r="D84" s="2" t="n">
         <v>21.65</v>
       </c>
-      <c r="E84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>21.65</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3927,27 +2142,6 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3966,27 +2160,6 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K86" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -4009,27 +2182,6 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4050,27 +2202,6 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4091,27 +2222,6 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4132,27 +2242,6 @@
       <c r="D90" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4173,27 +2262,6 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4214,27 +2282,6 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4255,27 +2302,6 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
-      <c r="E93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>21.89</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4296,27 +2322,6 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4337,27 +2342,6 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4378,27 +2362,6 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4419,27 +2382,6 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4460,27 +2402,6 @@
       <c r="D98" s="2" t="n">
         <v>20.95</v>
       </c>
-      <c r="E98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>20.95</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4501,27 +2422,6 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>20.99</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4542,27 +2442,6 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4583,27 +2462,6 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4624,27 +2482,6 @@
       <c r="D102" s="2" t="n">
         <v>22.79</v>
       </c>
-      <c r="E102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>22.79</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4665,27 +2502,6 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
-      <c r="E103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>21.19</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4706,27 +2522,6 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4747,27 +2542,6 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4788,27 +2562,6 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
-      <c r="E106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>21.28</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4829,27 +2582,6 @@
       <c r="D107" s="2" t="n">
         <v>21.09</v>
       </c>
-      <c r="E107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>21.09</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4868,27 +2600,6 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K108" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -4911,27 +2622,6 @@
       <c r="D109" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>21.51</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>21.51</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4950,27 +2640,6 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="K110" s="2" t="n">
         <v>20.79</v>
       </c>
     </row>
@@ -4993,27 +2662,6 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
-      <c r="E111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>21.3</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5034,27 +2682,6 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5075,27 +2702,6 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5116,27 +2722,6 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
-      <c r="E114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>21.59</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5157,27 +2742,6 @@
       <c r="D115" s="2" t="n">
         <v>21.65</v>
       </c>
-      <c r="E115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>21.65</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5198,27 +2762,6 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5237,27 +2780,6 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="K117" s="2" t="n">
         <v>21.59</v>
       </c>
     </row>
@@ -5280,27 +2802,6 @@
       <c r="D118" s="2" t="n">
         <v>21.75</v>
       </c>
-      <c r="E118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>21.75</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5321,27 +2822,6 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
-      <c r="E119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>21.35</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5360,27 +2840,6 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>21.79</v>
-      </c>
-      <c r="K120" s="2" t="n">
         <v>21.79</v>
       </c>
     </row>
@@ -5403,27 +2862,6 @@
       <c r="D121" s="2" t="n">
         <v>21.75</v>
       </c>
-      <c r="E121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>21.75</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5444,27 +2882,6 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
-      <c r="E122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>21.39</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5485,27 +2902,6 @@
       <c r="D123" s="2" t="n">
         <v>21.69</v>
       </c>
-      <c r="E123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>21.69</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5526,27 +2922,6 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5567,27 +2942,6 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5608,27 +2962,6 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5649,27 +2982,6 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
-      <c r="E127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>21.49</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5690,27 +3002,6 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5731,27 +3022,6 @@
       <c r="D129" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5772,27 +3042,6 @@
       <c r="D130" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="E130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>22.5</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5813,27 +3062,6 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>21.5</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5854,27 +3082,6 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="E132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>21.6</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5895,27 +3102,6 @@
       <c r="D133" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5936,27 +3122,6 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="E134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>21.7</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5977,27 +3142,6 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6018,27 +3162,6 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6059,27 +3182,6 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="E137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>21.8</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6098,27 +3200,6 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="K138" s="2" t="n">
         <v>22.19</v>
       </c>
     </row>
@@ -6141,27 +3222,6 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K139" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6182,27 +3242,6 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6223,27 +3262,6 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6264,27 +3282,6 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6305,27 +3302,6 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6346,27 +3322,6 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
-      <c r="E144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>21.99</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6387,27 +3342,6 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
-      <c r="E145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>22.29</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6428,27 +3362,6 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6469,27 +3382,6 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="E147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="K147" s="2" t="n">
-        <v>22.3</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6510,27 +3402,6 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
-      <c r="E148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="K148" s="2" t="n">
-        <v>22.35</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6551,27 +3422,6 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
-      <c r="E149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="K149" s="2" t="n">
-        <v>22.49</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6592,27 +3442,6 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K150" s="2" t="n">
-        <v>22.5</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6633,27 +3462,6 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
-      <c r="E151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="K151" s="2" t="n">
-        <v>22.59</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6674,27 +3482,6 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6715,27 +3502,6 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
-      <c r="E153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K153" s="2" t="n">
-        <v>22.6</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6756,27 +3522,6 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="K154" s="2" t="n">
-        <v>22.7</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6797,27 +3542,6 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>22.79</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6838,27 +3562,6 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6879,27 +3582,6 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="E157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="K157" s="2" t="n">
-        <v>22.8</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6920,27 +3602,6 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K158" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6961,27 +3622,6 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
-      <c r="E159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="K159" s="2" t="n">
-        <v>23.99</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7002,27 +3642,6 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K160" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7043,27 +3662,6 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
-      <c r="E161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="K161" s="2" t="n">
-        <v>22.99</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7082,27 +3680,6 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="K162" s="2" t="n">
         <v>23.99</v>
       </c>
     </row>
@@ -7125,27 +3702,6 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="E163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K163" s="2" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7166,27 +3722,6 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="K164" s="2" t="n">
-        <v>24.25</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7205,32 +3740,11 @@
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="E165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="H165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I165" s="2" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="J165" s="2" t="n">
         <v>20.59</v>
       </c>
-      <c r="K165" s="2" t="n">
-        <v>20.59</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K165"/>
+  <autoFilter ref="A1:D165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$D$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,13 +432,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,6 +463,11 @@
           <t>2026-09-12 01:11</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,6 +488,9 @@
       <c r="D2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,6 +511,9 @@
       <c r="D3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -522,6 +534,9 @@
       <c r="D4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,6 +557,9 @@
       <c r="D5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,6 +580,9 @@
       <c r="D6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -582,6 +603,9 @@
       <c r="D7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,6 +626,9 @@
       <c r="D8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="E8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +649,9 @@
       <c r="D9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,6 +672,9 @@
       <c r="D10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -662,6 +695,9 @@
       <c r="D11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,6 +718,9 @@
       <c r="D12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -702,6 +741,9 @@
       <c r="D13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,6 +764,9 @@
       <c r="D14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,6 +787,9 @@
       <c r="D15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="E15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -762,6 +810,9 @@
       <c r="D16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,6 +833,9 @@
       <c r="D17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -802,6 +856,9 @@
       <c r="D18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -822,6 +879,9 @@
       <c r="D19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,6 +902,9 @@
       <c r="D20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,6 +925,9 @@
       <c r="D21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -882,6 +948,9 @@
       <c r="D22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -902,6 +971,9 @@
       <c r="D23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -922,6 +994,9 @@
       <c r="D24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -942,6 +1017,9 @@
       <c r="D25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -962,6 +1040,9 @@
       <c r="D26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="E26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -982,6 +1063,9 @@
       <c r="D27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1002,6 +1086,9 @@
       <c r="D28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1022,6 +1109,9 @@
       <c r="D29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1042,6 +1132,9 @@
       <c r="D30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1062,6 +1155,9 @@
       <c r="D31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1082,6 +1178,9 @@
       <c r="D32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1102,6 +1201,9 @@
       <c r="D33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1122,6 +1224,9 @@
       <c r="D34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1142,6 +1247,9 @@
       <c r="D35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1162,6 +1270,9 @@
       <c r="D36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1182,6 +1293,9 @@
       <c r="D37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="E37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1202,6 +1316,9 @@
       <c r="D38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1222,6 +1339,9 @@
       <c r="D39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="E39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1242,6 +1362,9 @@
       <c r="D40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1262,6 +1385,9 @@
       <c r="D41" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1282,6 +1408,9 @@
       <c r="D42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1302,6 +1431,9 @@
       <c r="D43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1322,6 +1454,9 @@
       <c r="D44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1342,6 +1477,9 @@
       <c r="D45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="E45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1362,6 +1500,9 @@
       <c r="D46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="E46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1382,6 +1523,9 @@
       <c r="D47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1402,6 +1546,9 @@
       <c r="D48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1422,6 +1569,9 @@
       <c r="D49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1442,6 +1592,9 @@
       <c r="D50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1462,6 +1615,9 @@
       <c r="D51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="E51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1482,6 +1638,9 @@
       <c r="D52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1502,6 +1661,9 @@
       <c r="D53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1522,6 +1684,9 @@
       <c r="D54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1542,6 +1707,9 @@
       <c r="D55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1562,6 +1730,9 @@
       <c r="D56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1582,6 +1753,9 @@
       <c r="D57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="E57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1602,6 +1776,9 @@
       <c r="D58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1622,6 +1799,9 @@
       <c r="D59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="E59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1642,6 +1822,9 @@
       <c r="D60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="E60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1662,6 +1845,9 @@
       <c r="D61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="E61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1682,6 +1868,9 @@
       <c r="D62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="E62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1702,6 +1891,9 @@
       <c r="D63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="E63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1722,6 +1914,9 @@
       <c r="D64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1742,6 +1937,9 @@
       <c r="D65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1762,6 +1960,9 @@
       <c r="D66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1782,6 +1983,9 @@
       <c r="D67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1802,6 +2006,9 @@
       <c r="D68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1822,6 +2029,9 @@
       <c r="D69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1842,6 +2052,9 @@
       <c r="D70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1862,6 +2075,9 @@
       <c r="D71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1882,6 +2098,9 @@
       <c r="D72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="E72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1902,6 +2121,9 @@
       <c r="D73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1922,6 +2144,9 @@
       <c r="D74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1942,6 +2167,9 @@
       <c r="D75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1962,6 +2190,9 @@
       <c r="D76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1982,6 +2213,9 @@
       <c r="D77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2002,6 +2236,9 @@
       <c r="D78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2022,6 +2259,9 @@
       <c r="D79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2042,6 +2282,9 @@
       <c r="D80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2062,6 +2305,9 @@
       <c r="D81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2082,6 +2328,9 @@
       <c r="D82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2102,6 +2351,9 @@
       <c r="D83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2122,6 +2374,9 @@
       <c r="D84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2142,6 +2397,9 @@
       <c r="D85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2162,6 +2420,9 @@
       <c r="D86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2182,6 +2443,9 @@
       <c r="D87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2202,6 +2466,9 @@
       <c r="D88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2222,6 +2489,9 @@
       <c r="D89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2242,6 +2512,9 @@
       <c r="D90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2262,6 +2535,9 @@
       <c r="D91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2282,6 +2558,9 @@
       <c r="D92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2302,6 +2581,9 @@
       <c r="D93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="E93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2322,6 +2604,9 @@
       <c r="D94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2342,6 +2627,9 @@
       <c r="D95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2362,6 +2650,9 @@
       <c r="D96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="E96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2382,6 +2673,9 @@
       <c r="D97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2402,6 +2696,9 @@
       <c r="D98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="E98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2422,6 +2719,9 @@
       <c r="D99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="E99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2442,6 +2742,9 @@
       <c r="D100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2462,6 +2765,9 @@
       <c r="D101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2482,6 +2788,9 @@
       <c r="D102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2502,6 +2811,9 @@
       <c r="D103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="E103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2522,6 +2834,9 @@
       <c r="D104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2542,6 +2857,9 @@
       <c r="D105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2562,6 +2880,9 @@
       <c r="D106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="E106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2582,6 +2903,9 @@
       <c r="D107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="E107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2602,6 +2926,9 @@
       <c r="D108" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E108" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2622,6 +2949,9 @@
       <c r="D109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2642,6 +2972,9 @@
       <c r="D110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="E110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2662,6 +2995,9 @@
       <c r="D111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="E111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2682,6 +3018,9 @@
       <c r="D112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2702,6 +3041,9 @@
       <c r="D113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2722,6 +3064,9 @@
       <c r="D114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2742,6 +3087,9 @@
       <c r="D115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="E115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2762,6 +3110,9 @@
       <c r="D116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2782,6 +3133,9 @@
       <c r="D117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="E117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2802,6 +3156,9 @@
       <c r="D118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2822,6 +3179,9 @@
       <c r="D119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="E119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2842,6 +3202,9 @@
       <c r="D120" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="E120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2862,6 +3225,9 @@
       <c r="D121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="E121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2882,6 +3248,9 @@
       <c r="D122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="E122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2902,6 +3271,9 @@
       <c r="D123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="E123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2922,6 +3294,9 @@
       <c r="D124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2942,6 +3317,9 @@
       <c r="D125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2962,6 +3340,9 @@
       <c r="D126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2982,6 +3363,9 @@
       <c r="D127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="E127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3002,6 +3386,9 @@
       <c r="D128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3022,6 +3409,9 @@
       <c r="D129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3042,6 +3432,9 @@
       <c r="D130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="E130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3062,6 +3455,9 @@
       <c r="D131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="E131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3082,6 +3478,9 @@
       <c r="D132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="E132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3102,6 +3501,9 @@
       <c r="D133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3122,6 +3524,9 @@
       <c r="D134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="E134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3142,6 +3547,9 @@
       <c r="D135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3162,6 +3570,9 @@
       <c r="D136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3182,6 +3593,9 @@
       <c r="D137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="E137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3202,6 +3616,9 @@
       <c r="D138" s="2" t="n">
         <v>22.19</v>
       </c>
+      <c r="E138" s="2" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3222,6 +3639,9 @@
       <c r="D139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3242,6 +3662,9 @@
       <c r="D140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3262,6 +3685,9 @@
       <c r="D141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3282,6 +3708,9 @@
       <c r="D142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3302,6 +3731,9 @@
       <c r="D143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3322,6 +3754,9 @@
       <c r="D144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="E144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3342,6 +3777,9 @@
       <c r="D145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="E145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3362,6 +3800,9 @@
       <c r="D146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3382,6 +3823,9 @@
       <c r="D147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="E147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3402,6 +3846,9 @@
       <c r="D148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="E148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3422,6 +3869,9 @@
       <c r="D149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="E149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3442,6 +3892,9 @@
       <c r="D150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="E150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3462,6 +3915,9 @@
       <c r="D151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="E151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3482,6 +3938,9 @@
       <c r="D152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3502,6 +3961,9 @@
       <c r="D153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="E153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3522,6 +3984,9 @@
       <c r="D154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="E154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3542,6 +4007,9 @@
       <c r="D155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="E155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3562,6 +4030,9 @@
       <c r="D156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3582,6 +4053,9 @@
       <c r="D157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="E157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3602,6 +4076,9 @@
       <c r="D158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3622,6 +4099,9 @@
       <c r="D159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="E159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3642,6 +4122,9 @@
       <c r="D160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3662,6 +4145,9 @@
       <c r="D161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="E161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3682,6 +4168,9 @@
       <c r="D162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="E162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3702,6 +4191,9 @@
       <c r="D163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="E163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3722,6 +4214,9 @@
       <c r="D164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="E164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3742,9 +4237,12 @@
       <c r="D165" s="2" t="n">
         <v>20.59</v>
       </c>
+      <c r="E165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D165"/>
+  <autoFilter ref="A1:E165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$E$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,11 @@
           <t>2026-09-12 04:09</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +497,9 @@
       <c r="E2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,6 +523,9 @@
       <c r="E3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="F3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +549,9 @@
       <c r="E4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -560,6 +575,9 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +601,9 @@
       <c r="E6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -606,6 +627,9 @@
       <c r="E7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="F7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -629,6 +653,9 @@
       <c r="E8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -652,6 +679,9 @@
       <c r="E9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="F9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -675,6 +705,9 @@
       <c r="E10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +731,9 @@
       <c r="E11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="F11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -721,6 +757,9 @@
       <c r="E12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,6 +783,9 @@
       <c r="E13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="F13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -767,6 +809,9 @@
       <c r="E14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -790,6 +835,9 @@
       <c r="E15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="F15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -813,6 +861,9 @@
       <c r="E16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -836,6 +887,9 @@
       <c r="E17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -859,6 +913,9 @@
       <c r="E18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -882,6 +939,9 @@
       <c r="E19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="F19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -905,6 +965,9 @@
       <c r="E20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="F20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -928,6 +991,9 @@
       <c r="E21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="F21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -951,6 +1017,9 @@
       <c r="E22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -974,6 +1043,9 @@
       <c r="E23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F23" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -997,6 +1069,9 @@
       <c r="E24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1020,6 +1095,9 @@
       <c r="E25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1043,6 +1121,9 @@
       <c r="E26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="F26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1066,6 +1147,9 @@
       <c r="E27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1089,6 +1173,9 @@
       <c r="E28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1112,6 +1199,9 @@
       <c r="E29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1135,6 +1225,9 @@
       <c r="E30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1158,6 +1251,9 @@
       <c r="E31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1181,6 +1277,9 @@
       <c r="E32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1204,6 +1303,9 @@
       <c r="E33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1227,6 +1329,9 @@
       <c r="E34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1250,6 +1355,9 @@
       <c r="E35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1273,6 +1381,9 @@
       <c r="E36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1296,6 +1407,9 @@
       <c r="E37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="F37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1319,6 +1433,9 @@
       <c r="E38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1342,6 +1459,9 @@
       <c r="E39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="F39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1365,6 +1485,9 @@
       <c r="E40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1388,6 +1511,9 @@
       <c r="E41" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1411,6 +1537,9 @@
       <c r="E42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1434,6 +1563,9 @@
       <c r="E43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F43" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1457,6 +1589,9 @@
       <c r="E44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1480,6 +1615,9 @@
       <c r="E45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="F45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1503,6 +1641,9 @@
       <c r="E46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="F46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1526,6 +1667,9 @@
       <c r="E47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1549,6 +1693,9 @@
       <c r="E48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1572,6 +1719,9 @@
       <c r="E49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1595,6 +1745,9 @@
       <c r="E50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1618,6 +1771,9 @@
       <c r="E51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="F51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1641,6 +1797,9 @@
       <c r="E52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1664,6 +1823,9 @@
       <c r="E53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1687,6 +1849,9 @@
       <c r="E54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1710,6 +1875,9 @@
       <c r="E55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1733,6 +1901,9 @@
       <c r="E56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1756,6 +1927,9 @@
       <c r="E57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="F57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1779,6 +1953,9 @@
       <c r="E58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1802,6 +1979,9 @@
       <c r="E59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="F59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1825,6 +2005,9 @@
       <c r="E60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="F60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1848,6 +2031,9 @@
       <c r="E61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="F61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1871,6 +2057,9 @@
       <c r="E62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="F62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1894,6 +2083,9 @@
       <c r="E63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="F63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1917,6 +2109,9 @@
       <c r="E64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1940,6 +2135,9 @@
       <c r="E65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1963,6 +2161,9 @@
       <c r="E66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1986,6 +2187,9 @@
       <c r="E67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2009,6 +2213,9 @@
       <c r="E68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2032,6 +2239,9 @@
       <c r="E69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2055,6 +2265,9 @@
       <c r="E70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2078,6 +2291,9 @@
       <c r="E71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2101,6 +2317,9 @@
       <c r="E72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="F72" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2124,6 +2343,9 @@
       <c r="E73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2147,6 +2369,9 @@
       <c r="E74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2170,6 +2395,9 @@
       <c r="E75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2193,6 +2421,9 @@
       <c r="E76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2216,6 +2447,9 @@
       <c r="E77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2239,6 +2473,9 @@
       <c r="E78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2262,6 +2499,9 @@
       <c r="E79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2285,6 +2525,9 @@
       <c r="E80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2308,6 +2551,9 @@
       <c r="E81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2331,6 +2577,9 @@
       <c r="E82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2354,6 +2603,9 @@
       <c r="E83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2377,6 +2629,9 @@
       <c r="E84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F84" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2400,6 +2655,9 @@
       <c r="E85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2423,6 +2681,9 @@
       <c r="E86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2446,6 +2707,9 @@
       <c r="E87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2469,6 +2733,9 @@
       <c r="E88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2492,6 +2759,9 @@
       <c r="E89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2515,6 +2785,9 @@
       <c r="E90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2538,6 +2811,9 @@
       <c r="E91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2561,6 +2837,9 @@
       <c r="E92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F92" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2584,6 +2863,9 @@
       <c r="E93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="F93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2607,6 +2889,9 @@
       <c r="E94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2630,6 +2915,9 @@
       <c r="E95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2653,6 +2941,9 @@
       <c r="E96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="F96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2676,6 +2967,9 @@
       <c r="E97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2699,6 +2993,9 @@
       <c r="E98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="F98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2722,6 +3019,9 @@
       <c r="E99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="F99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2745,6 +3045,9 @@
       <c r="E100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2768,6 +3071,9 @@
       <c r="E101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2791,6 +3097,9 @@
       <c r="E102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2814,6 +3123,9 @@
       <c r="E103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="F103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2837,6 +3149,9 @@
       <c r="E104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2860,6 +3175,9 @@
       <c r="E105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2883,6 +3201,9 @@
       <c r="E106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="F106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2906,6 +3227,9 @@
       <c r="E107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="F107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2929,6 +3253,9 @@
       <c r="E108" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F108" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2952,6 +3279,9 @@
       <c r="E109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2975,6 +3305,9 @@
       <c r="E110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="F110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2998,6 +3331,9 @@
       <c r="E111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="F111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3021,6 +3357,9 @@
       <c r="E112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3044,6 +3383,9 @@
       <c r="E113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3067,6 +3409,9 @@
       <c r="E114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3090,6 +3435,9 @@
       <c r="E115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="F115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3113,6 +3461,9 @@
       <c r="E116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3136,6 +3487,9 @@
       <c r="E117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="F117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3159,6 +3513,9 @@
       <c r="E118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3182,6 +3539,9 @@
       <c r="E119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="F119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3205,6 +3565,9 @@
       <c r="E120" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="F120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3228,6 +3591,9 @@
       <c r="E121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="F121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3251,6 +3617,9 @@
       <c r="E122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="F122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3274,6 +3643,9 @@
       <c r="E123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="F123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3297,6 +3669,9 @@
       <c r="E124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3320,6 +3695,9 @@
       <c r="E125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3343,6 +3721,9 @@
       <c r="E126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3366,6 +3747,9 @@
       <c r="E127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="F127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3389,6 +3773,9 @@
       <c r="E128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3412,6 +3799,9 @@
       <c r="E129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3435,6 +3825,9 @@
       <c r="E130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="F130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3458,6 +3851,9 @@
       <c r="E131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="F131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3481,6 +3877,9 @@
       <c r="E132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="F132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3504,6 +3903,9 @@
       <c r="E133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3527,6 +3929,9 @@
       <c r="E134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="F134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3550,6 +3955,9 @@
       <c r="E135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3573,6 +3981,9 @@
       <c r="E136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3596,6 +4007,9 @@
       <c r="E137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="F137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3619,6 +4033,9 @@
       <c r="E138" s="2" t="n">
         <v>22.19</v>
       </c>
+      <c r="F138" s="2" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3642,6 +4059,9 @@
       <c r="E139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3665,6 +4085,9 @@
       <c r="E140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3688,6 +4111,9 @@
       <c r="E141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3711,6 +4137,9 @@
       <c r="E142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3734,6 +4163,9 @@
       <c r="E143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3757,6 +4189,9 @@
       <c r="E144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="F144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3780,6 +4215,9 @@
       <c r="E145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="F145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3803,6 +4241,9 @@
       <c r="E146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3826,6 +4267,9 @@
       <c r="E147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="F147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3849,6 +4293,9 @@
       <c r="E148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="F148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3872,6 +4319,9 @@
       <c r="E149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="F149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3895,6 +4345,9 @@
       <c r="E150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="F150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3918,6 +4371,9 @@
       <c r="E151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="F151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3941,6 +4397,9 @@
       <c r="E152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3964,6 +4423,9 @@
       <c r="E153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="F153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3987,6 +4449,9 @@
       <c r="E154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="F154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4010,6 +4475,9 @@
       <c r="E155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="F155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4033,6 +4501,9 @@
       <c r="E156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4056,6 +4527,9 @@
       <c r="E157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="F157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4079,6 +4553,9 @@
       <c r="E158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4102,6 +4579,9 @@
       <c r="E159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="F159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4125,6 +4605,9 @@
       <c r="E160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4148,6 +4631,9 @@
       <c r="E161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="F161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4171,6 +4657,9 @@
       <c r="E162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="F162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4194,6 +4683,9 @@
       <c r="E163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="F163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4217,6 +4709,9 @@
       <c r="E164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="F164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4240,9 +4735,12 @@
       <c r="E165" s="2" t="n">
         <v>20.59</v>
       </c>
+      <c r="F165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E165"/>
+  <autoFilter ref="A1:F165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$F$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,6 +475,11 @@
           <t>2026-09-12 07:11</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,9 @@
       <c r="F2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +535,9 @@
       <c r="F3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,6 +564,9 @@
       <c r="F4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,6 +593,9 @@
       <c r="F5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -604,6 +622,9 @@
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -630,6 +651,9 @@
       <c r="F7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,6 +680,9 @@
       <c r="F8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -682,6 +709,9 @@
       <c r="F9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -708,6 +738,9 @@
       <c r="F10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -734,6 +767,9 @@
       <c r="F11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>20.19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -760,6 +796,9 @@
       <c r="F12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,6 +825,9 @@
       <c r="F13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -812,6 +854,9 @@
       <c r="F14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -838,6 +883,9 @@
       <c r="F15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -864,6 +912,9 @@
       <c r="F16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -890,6 +941,9 @@
       <c r="F17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -916,6 +970,9 @@
       <c r="F18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -942,6 +999,9 @@
       <c r="F19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -968,6 +1028,9 @@
       <c r="F20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -994,6 +1057,9 @@
       <c r="F21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1020,6 +1086,9 @@
       <c r="F22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1046,6 +1115,9 @@
       <c r="F23" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1072,6 +1144,9 @@
       <c r="F24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1098,6 +1173,9 @@
       <c r="F25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1124,6 +1202,9 @@
       <c r="F26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1150,6 +1231,9 @@
       <c r="F27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1176,6 +1260,9 @@
       <c r="F28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1202,6 +1289,9 @@
       <c r="F29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1228,6 +1318,9 @@
       <c r="F30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1254,6 +1347,9 @@
       <c r="F31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1280,6 +1376,9 @@
       <c r="F32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1405,9 @@
       <c r="F33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1332,6 +1434,9 @@
       <c r="F34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1358,6 +1463,9 @@
       <c r="F35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1384,6 +1492,9 @@
       <c r="F36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1410,6 +1521,9 @@
       <c r="F37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="G37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1436,6 +1550,9 @@
       <c r="F38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1462,6 +1579,9 @@
       <c r="F39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="G39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1488,6 +1608,9 @@
       <c r="F40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1514,6 +1637,9 @@
       <c r="F41" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1540,6 +1666,9 @@
       <c r="F42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1566,6 +1695,9 @@
       <c r="F43" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G43" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1592,6 +1724,9 @@
       <c r="F44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1618,6 +1753,9 @@
       <c r="F45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="G45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1644,6 +1782,9 @@
       <c r="F46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="G46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1670,6 +1811,9 @@
       <c r="F47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1696,6 +1840,9 @@
       <c r="F48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1722,6 +1869,9 @@
       <c r="F49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1748,6 +1898,9 @@
       <c r="F50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1774,6 +1927,9 @@
       <c r="F51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="G51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1800,6 +1956,9 @@
       <c r="F52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1826,6 +1985,9 @@
       <c r="F53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G53" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1852,6 +2014,9 @@
       <c r="F54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1878,6 +2043,9 @@
       <c r="F55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1904,6 +2072,9 @@
       <c r="F56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1930,6 +2101,9 @@
       <c r="F57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="G57" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1956,6 +2130,9 @@
       <c r="F58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1982,6 +2159,9 @@
       <c r="F59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="G59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2008,6 +2188,9 @@
       <c r="F60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="G60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2034,6 +2217,9 @@
       <c r="F61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="G61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2060,6 +2246,9 @@
       <c r="F62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="G62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2086,6 +2275,9 @@
       <c r="F63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="G63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2112,6 +2304,9 @@
       <c r="F64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2138,6 +2333,9 @@
       <c r="F65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2164,6 +2362,9 @@
       <c r="F66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2190,6 +2391,9 @@
       <c r="F67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2216,6 +2420,9 @@
       <c r="F68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2242,6 +2449,9 @@
       <c r="F69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2268,6 +2478,9 @@
       <c r="F70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2294,6 +2507,9 @@
       <c r="F71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2320,6 +2536,9 @@
       <c r="F72" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="G72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2346,6 +2565,9 @@
       <c r="F73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2372,6 +2594,9 @@
       <c r="F74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2398,6 +2623,9 @@
       <c r="F75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2424,6 +2652,9 @@
       <c r="F76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2450,6 +2681,9 @@
       <c r="F77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2476,6 +2710,9 @@
       <c r="F78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2502,6 +2739,9 @@
       <c r="F79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2528,6 +2768,9 @@
       <c r="F80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2554,6 +2797,9 @@
       <c r="F81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2580,6 +2826,9 @@
       <c r="F82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2606,6 +2855,9 @@
       <c r="F83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2632,6 +2884,9 @@
       <c r="F84" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G84" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2658,6 +2913,9 @@
       <c r="F85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2684,6 +2942,9 @@
       <c r="F86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2710,6 +2971,9 @@
       <c r="F87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2736,6 +3000,9 @@
       <c r="F88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2762,6 +3029,9 @@
       <c r="F89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2788,6 +3058,9 @@
       <c r="F90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2814,6 +3087,9 @@
       <c r="F91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2840,6 +3116,9 @@
       <c r="F92" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G92" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2866,6 +3145,9 @@
       <c r="F93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="G93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2892,6 +3174,9 @@
       <c r="F94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2918,6 +3203,9 @@
       <c r="F95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2944,6 +3232,9 @@
       <c r="F96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="G96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2970,6 +3261,9 @@
       <c r="F97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2996,6 +3290,9 @@
       <c r="F98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="G98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3022,6 +3319,9 @@
       <c r="F99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="G99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3048,6 +3348,9 @@
       <c r="F100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3074,6 +3377,9 @@
       <c r="F101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3100,6 +3406,9 @@
       <c r="F102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3126,6 +3435,9 @@
       <c r="F103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="G103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3152,6 +3464,9 @@
       <c r="F104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3178,6 +3493,9 @@
       <c r="F105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3204,6 +3522,9 @@
       <c r="F106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="G106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3230,6 +3551,9 @@
       <c r="F107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="G107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3256,6 +3580,9 @@
       <c r="F108" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G108" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3282,6 +3609,9 @@
       <c r="F109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3308,6 +3638,9 @@
       <c r="F110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="G110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3334,6 +3667,9 @@
       <c r="F111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="G111" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3360,6 +3696,9 @@
       <c r="F112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3386,6 +3725,9 @@
       <c r="F113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3412,6 +3754,9 @@
       <c r="F114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3438,6 +3783,9 @@
       <c r="F115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="G115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3464,6 +3812,9 @@
       <c r="F116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3490,6 +3841,9 @@
       <c r="F117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="G117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3516,6 +3870,9 @@
       <c r="F118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3542,6 +3899,9 @@
       <c r="F119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="G119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3568,6 +3928,9 @@
       <c r="F120" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="G120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3594,6 +3957,9 @@
       <c r="F121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="G121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3620,6 +3986,9 @@
       <c r="F122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="G122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3646,6 +4015,9 @@
       <c r="F123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="G123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3672,6 +4044,9 @@
       <c r="F124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3698,6 +4073,9 @@
       <c r="F125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3724,6 +4102,9 @@
       <c r="F126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3750,6 +4131,9 @@
       <c r="F127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="G127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3776,6 +4160,9 @@
       <c r="F128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3802,6 +4189,9 @@
       <c r="F129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3828,6 +4218,9 @@
       <c r="F130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3854,6 +4247,9 @@
       <c r="F131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="G131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3880,6 +4276,9 @@
       <c r="F132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="G132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3906,6 +4305,9 @@
       <c r="F133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3932,6 +4334,9 @@
       <c r="F134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="G134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3958,6 +4363,9 @@
       <c r="F135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3984,6 +4392,9 @@
       <c r="F136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4010,6 +4421,9 @@
       <c r="F137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="G137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4036,6 +4450,9 @@
       <c r="F138" s="2" t="n">
         <v>22.19</v>
       </c>
+      <c r="G138" s="2" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4062,6 +4479,9 @@
       <c r="F139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4088,6 +4508,9 @@
       <c r="F140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4114,6 +4537,9 @@
       <c r="F141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4140,6 +4566,9 @@
       <c r="F142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4166,6 +4595,9 @@
       <c r="F143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4192,6 +4624,9 @@
       <c r="F144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="G144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4218,6 +4653,9 @@
       <c r="F145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="G145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4244,6 +4682,9 @@
       <c r="F146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4270,6 +4711,9 @@
       <c r="F147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="G147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4296,6 +4740,9 @@
       <c r="F148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="G148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4322,6 +4769,9 @@
       <c r="F149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="G149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4348,6 +4798,9 @@
       <c r="F150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="G150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4374,6 +4827,9 @@
       <c r="F151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="G151" s="2" t="n">
+        <v>22.59</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4400,6 +4856,9 @@
       <c r="F152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4426,6 +4885,9 @@
       <c r="F153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="G153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4452,6 +4914,9 @@
       <c r="F154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="G154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4478,6 +4943,9 @@
       <c r="F155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="G155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4504,6 +4972,9 @@
       <c r="F156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4530,6 +5001,9 @@
       <c r="F157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="G157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4556,6 +5030,9 @@
       <c r="F158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4582,6 +5059,9 @@
       <c r="F159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="G159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4608,6 +5088,9 @@
       <c r="F160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4634,6 +5117,9 @@
       <c r="F161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="G161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4660,6 +5146,9 @@
       <c r="F162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="G162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4686,6 +5175,9 @@
       <c r="F163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="G163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4712,6 +5204,9 @@
       <c r="F164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="G164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4738,9 +5233,12 @@
       <c r="F165" s="2" t="n">
         <v>20.59</v>
       </c>
+      <c r="G165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F165"/>
+  <autoFilter ref="A1:G165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
           <t>2026-09-12 10:08</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +515,9 @@
       <c r="G2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="H2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +547,9 @@
       <c r="G3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +579,9 @@
       <c r="G4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="H4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +611,9 @@
       <c r="G5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -625,6 +643,9 @@
       <c r="G6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -654,6 +675,9 @@
       <c r="G7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="H7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +707,9 @@
       <c r="G8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,6 +739,9 @@
       <c r="G9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -741,6 +771,9 @@
       <c r="G10" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,6 +803,9 @@
       <c r="G11" s="2" t="n">
         <v>20.19</v>
       </c>
+      <c r="H11" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +835,9 @@
       <c r="G12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -828,6 +867,9 @@
       <c r="G13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="H13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,6 +899,9 @@
       <c r="G14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H14" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -886,6 +931,9 @@
       <c r="G15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="H15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -915,6 +963,9 @@
       <c r="G16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -944,6 +995,9 @@
       <c r="G17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -973,6 +1027,9 @@
       <c r="G18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1002,6 +1059,9 @@
       <c r="G19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="H19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1031,6 +1091,9 @@
       <c r="G20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="H20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1060,6 +1123,9 @@
       <c r="G21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1089,6 +1155,9 @@
       <c r="G22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1118,6 +1187,9 @@
       <c r="G23" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H23" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1147,6 +1219,9 @@
       <c r="G24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1176,6 +1251,9 @@
       <c r="G25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1205,6 +1283,9 @@
       <c r="G26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="H26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1234,6 +1315,9 @@
       <c r="G27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1263,6 +1347,9 @@
       <c r="G28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1292,6 +1379,9 @@
       <c r="G29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,6 +1411,9 @@
       <c r="G30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1350,6 +1443,9 @@
       <c r="G31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1379,6 +1475,9 @@
       <c r="G32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1507,9 @@
       <c r="G33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H33" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1437,6 +1539,9 @@
       <c r="G34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H34" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1466,6 +1571,9 @@
       <c r="G35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1495,6 +1603,9 @@
       <c r="G36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1524,6 +1635,9 @@
       <c r="G37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="H37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1553,6 +1667,9 @@
       <c r="G38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1582,6 +1699,9 @@
       <c r="G39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="H39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1611,6 +1731,9 @@
       <c r="G40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1640,6 +1763,9 @@
       <c r="G41" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1669,6 +1795,9 @@
       <c r="G42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1698,6 +1827,9 @@
       <c r="G43" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H43" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1727,6 +1859,9 @@
       <c r="G44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H44" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1756,6 +1891,9 @@
       <c r="G45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="H45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1785,6 +1923,9 @@
       <c r="G46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="H46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1814,6 +1955,9 @@
       <c r="G47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1843,6 +1987,9 @@
       <c r="G48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1872,6 +2019,9 @@
       <c r="G49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1901,6 +2051,9 @@
       <c r="G50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1930,6 +2083,9 @@
       <c r="G51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="H51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1959,6 +2115,9 @@
       <c r="G52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1988,6 +2147,9 @@
       <c r="G53" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H53" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2017,6 +2179,9 @@
       <c r="G54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2046,6 +2211,9 @@
       <c r="G55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2075,6 +2243,9 @@
       <c r="G56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2104,6 +2275,9 @@
       <c r="G57" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="H57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2133,6 +2307,9 @@
       <c r="G58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H58" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2162,6 +2339,9 @@
       <c r="G59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="H59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2191,6 +2371,9 @@
       <c r="G60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="H60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2220,6 +2403,9 @@
       <c r="G61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="H61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2249,6 +2435,9 @@
       <c r="G62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="H62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2278,6 +2467,9 @@
       <c r="G63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="H63" s="2" t="n">
+        <v>21.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2307,6 +2499,9 @@
       <c r="G64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H64" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2336,6 +2531,9 @@
       <c r="G65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H65" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2365,6 +2563,9 @@
       <c r="G66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2394,6 +2595,9 @@
       <c r="G67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2423,6 +2627,9 @@
       <c r="G68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2452,6 +2659,9 @@
       <c r="G69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2481,6 +2691,9 @@
       <c r="G70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2510,6 +2723,9 @@
       <c r="G71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2539,6 +2755,9 @@
       <c r="G72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2568,6 +2787,9 @@
       <c r="G73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2597,6 +2819,9 @@
       <c r="G74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2626,6 +2851,9 @@
       <c r="G75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2655,6 +2883,9 @@
       <c r="G76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2684,6 +2915,9 @@
       <c r="G77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2713,6 +2947,9 @@
       <c r="G78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2742,6 +2979,9 @@
       <c r="G79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2771,6 +3011,9 @@
       <c r="G80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2800,6 +3043,9 @@
       <c r="G81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2829,6 +3075,9 @@
       <c r="G82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2858,6 +3107,9 @@
       <c r="G83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2887,6 +3139,9 @@
       <c r="G84" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H84" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2916,6 +3171,9 @@
       <c r="G85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2945,6 +3203,9 @@
       <c r="G86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2974,6 +3235,9 @@
       <c r="G87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3003,6 +3267,9 @@
       <c r="G88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3032,6 +3299,9 @@
       <c r="G89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3061,6 +3331,9 @@
       <c r="G90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3090,6 +3363,9 @@
       <c r="G91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3119,6 +3395,9 @@
       <c r="G92" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="H92" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3148,6 +3427,9 @@
       <c r="G93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="H93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3177,6 +3459,9 @@
       <c r="G94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3206,6 +3491,9 @@
       <c r="G95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3235,6 +3523,9 @@
       <c r="G96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="H96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3264,6 +3555,9 @@
       <c r="G97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3293,6 +3587,9 @@
       <c r="G98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="H98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3322,6 +3619,9 @@
       <c r="G99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="H99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3351,6 +3651,9 @@
       <c r="G100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3380,6 +3683,9 @@
       <c r="G101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3409,6 +3715,9 @@
       <c r="G102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3438,6 +3747,9 @@
       <c r="G103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="H103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3467,6 +3779,9 @@
       <c r="G104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3496,6 +3811,9 @@
       <c r="G105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3525,6 +3843,9 @@
       <c r="G106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="H106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3554,6 +3875,9 @@
       <c r="G107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="H107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3583,6 +3907,9 @@
       <c r="G108" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H108" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3612,6 +3939,9 @@
       <c r="G109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3641,6 +3971,9 @@
       <c r="G110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="H110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3670,6 +4003,9 @@
       <c r="G111" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="H111" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3699,6 +4035,9 @@
       <c r="G112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3728,6 +4067,9 @@
       <c r="G113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3757,6 +4099,9 @@
       <c r="G114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3786,6 +4131,9 @@
       <c r="G115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="H115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3815,6 +4163,9 @@
       <c r="G116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3844,6 +4195,9 @@
       <c r="G117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="H117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3873,6 +4227,9 @@
       <c r="G118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3902,6 +4259,9 @@
       <c r="G119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="H119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3931,6 +4291,9 @@
       <c r="G120" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="H120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3960,6 +4323,9 @@
       <c r="G121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="H121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3989,6 +4355,9 @@
       <c r="G122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="H122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4018,6 +4387,9 @@
       <c r="G123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="H123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4047,6 +4419,9 @@
       <c r="G124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4076,6 +4451,9 @@
       <c r="G125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4105,6 +4483,9 @@
       <c r="G126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4134,6 +4515,9 @@
       <c r="G127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="H127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4163,6 +4547,9 @@
       <c r="G128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4192,6 +4579,9 @@
       <c r="G129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4221,6 +4611,9 @@
       <c r="G130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4250,6 +4643,9 @@
       <c r="G131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="H131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4279,6 +4675,9 @@
       <c r="G132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="H132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4308,6 +4707,9 @@
       <c r="G133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4337,6 +4739,9 @@
       <c r="G134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="H134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4366,6 +4771,9 @@
       <c r="G135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4395,6 +4803,9 @@
       <c r="G136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4424,6 +4835,9 @@
       <c r="G137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="H137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4453,6 +4867,9 @@
       <c r="G138" s="2" t="n">
         <v>22.19</v>
       </c>
+      <c r="H138" s="2" t="n">
+        <v>22.19</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4482,6 +4899,9 @@
       <c r="G139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4511,6 +4931,9 @@
       <c r="G140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4540,6 +4963,9 @@
       <c r="G141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4569,6 +4995,9 @@
       <c r="G142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4598,6 +5027,9 @@
       <c r="G143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4627,6 +5059,9 @@
       <c r="G144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="H144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4656,6 +5091,9 @@
       <c r="G145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="H145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4685,6 +5123,9 @@
       <c r="G146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4714,6 +5155,9 @@
       <c r="G147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="H147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4743,6 +5187,9 @@
       <c r="G148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="H148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4772,6 +5219,9 @@
       <c r="G149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="H149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4801,6 +5251,9 @@
       <c r="G150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="H150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4830,6 +5283,9 @@
       <c r="G151" s="2" t="n">
         <v>22.59</v>
       </c>
+      <c r="H151" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4859,6 +5315,9 @@
       <c r="G152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4888,6 +5347,9 @@
       <c r="G153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="H153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4917,6 +5379,9 @@
       <c r="G154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="H154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4946,6 +5411,9 @@
       <c r="G155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="H155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4975,6 +5443,9 @@
       <c r="G156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5004,6 +5475,9 @@
       <c r="G157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="H157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5033,6 +5507,9 @@
       <c r="G158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5062,6 +5539,9 @@
       <c r="G159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="H159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5091,6 +5571,9 @@
       <c r="G160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5120,6 +5603,9 @@
       <c r="G161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="H161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5149,6 +5635,9 @@
       <c r="G162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="H162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5178,6 +5667,9 @@
       <c r="G163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="H163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5207,6 +5699,9 @@
       <c r="G164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="H164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5236,9 +5731,12 @@
       <c r="G165" s="2" t="n">
         <v>20.59</v>
       </c>
+      <c r="H165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G165"/>
+  <autoFilter ref="A1:H165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$H$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +487,11 @@
           <t>2026-09-12 13:10</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 19:13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +524,9 @@
       <c r="H2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,6 +559,9 @@
       <c r="H3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,6 +594,9 @@
       <c r="H4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,6 +629,9 @@
       <c r="H5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,6 +664,9 @@
       <c r="H6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,6 +699,9 @@
       <c r="H7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -710,6 +734,9 @@
       <c r="H8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -742,6 +769,9 @@
       <c r="H9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -774,6 +804,9 @@
       <c r="H10" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -806,6 +839,9 @@
       <c r="H11" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -838,6 +874,9 @@
       <c r="H12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -870,6 +909,9 @@
       <c r="H13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -902,6 +944,9 @@
       <c r="H14" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I14" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,6 +979,9 @@
       <c r="H15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="I15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -966,6 +1014,9 @@
       <c r="H16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -998,6 +1049,9 @@
       <c r="H17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1030,6 +1084,9 @@
       <c r="H18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1062,6 +1119,9 @@
       <c r="H19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1094,6 +1154,9 @@
       <c r="H20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1126,6 +1189,9 @@
       <c r="H21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1158,6 +1224,9 @@
       <c r="H22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1190,6 +1259,9 @@
       <c r="H23" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I23" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1222,6 +1294,9 @@
       <c r="H24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,6 +1329,9 @@
       <c r="H25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1286,6 +1364,9 @@
       <c r="H26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1318,6 +1399,9 @@
       <c r="H27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1350,6 +1434,9 @@
       <c r="H28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1382,6 +1469,9 @@
       <c r="H29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1414,6 +1504,9 @@
       <c r="H30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1446,6 +1539,9 @@
       <c r="H31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1478,6 +1574,9 @@
       <c r="H32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,6 +1609,9 @@
       <c r="H33" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I33" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1542,6 +1644,9 @@
       <c r="H34" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I34" s="2" t="n">
+        <v>21.22</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1574,6 +1679,9 @@
       <c r="H35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1606,6 +1714,9 @@
       <c r="H36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1638,6 +1749,9 @@
       <c r="H37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="I37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1670,6 +1784,9 @@
       <c r="H38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1702,6 +1819,9 @@
       <c r="H39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="I39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1734,6 +1854,9 @@
       <c r="H40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1766,6 +1889,9 @@
       <c r="H41" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1798,6 +1924,9 @@
       <c r="H42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1830,6 +1959,9 @@
       <c r="H43" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I43" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1862,6 +1994,9 @@
       <c r="H44" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I44" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1894,6 +2029,9 @@
       <c r="H45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="I45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1926,6 +2064,9 @@
       <c r="H46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="I46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1958,6 +2099,9 @@
       <c r="H47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1990,6 +2134,9 @@
       <c r="H48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2022,6 +2169,9 @@
       <c r="H49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2054,6 +2204,9 @@
       <c r="H50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2086,6 +2239,9 @@
       <c r="H51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="I51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2118,6 +2274,9 @@
       <c r="H52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2150,6 +2309,9 @@
       <c r="H53" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I53" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2182,6 +2344,9 @@
       <c r="H54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2214,6 +2379,9 @@
       <c r="H55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="I55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2246,6 +2414,9 @@
       <c r="H56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="I56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2278,6 +2449,9 @@
       <c r="H57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,6 +2484,9 @@
       <c r="H58" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I58" s="2" t="n">
+        <v>22.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2342,6 +2519,9 @@
       <c r="H59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="I59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2374,6 +2554,9 @@
       <c r="H60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="I60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2406,6 +2589,9 @@
       <c r="H61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="I61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2438,6 +2624,9 @@
       <c r="H62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="I62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,6 +2659,9 @@
       <c r="H63" s="2" t="n">
         <v>21.25</v>
       </c>
+      <c r="I63" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2502,6 +2694,9 @@
       <c r="H64" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I64" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,6 +2729,9 @@
       <c r="H65" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I65" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2566,6 +2764,9 @@
       <c r="H66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2598,6 +2799,9 @@
       <c r="H67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2630,6 +2834,9 @@
       <c r="H68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2662,6 +2869,9 @@
       <c r="H69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2694,6 +2904,9 @@
       <c r="H70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2726,6 +2939,9 @@
       <c r="H71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2758,6 +2974,9 @@
       <c r="H72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2790,6 +3009,9 @@
       <c r="H73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2822,6 +3044,9 @@
       <c r="H74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2854,6 +3079,9 @@
       <c r="H75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2886,6 +3114,9 @@
       <c r="H76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2918,6 +3149,9 @@
       <c r="H77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2950,6 +3184,9 @@
       <c r="H78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2982,6 +3219,9 @@
       <c r="H79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3014,6 +3254,9 @@
       <c r="H80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3046,6 +3289,9 @@
       <c r="H81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3078,6 +3324,9 @@
       <c r="H82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3110,6 +3359,9 @@
       <c r="H83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3142,6 +3394,9 @@
       <c r="H84" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I84" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3174,6 +3429,9 @@
       <c r="H85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3206,6 +3464,9 @@
       <c r="H86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3238,6 +3499,9 @@
       <c r="H87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3270,6 +3534,9 @@
       <c r="H88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3302,6 +3569,9 @@
       <c r="H89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3334,6 +3604,9 @@
       <c r="H90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3366,6 +3639,9 @@
       <c r="H91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3398,6 +3674,9 @@
       <c r="H92" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="I92" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3430,6 +3709,9 @@
       <c r="H93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="I93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3462,6 +3744,9 @@
       <c r="H94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3494,6 +3779,9 @@
       <c r="H95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3526,6 +3814,9 @@
       <c r="H96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="I96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3558,6 +3849,9 @@
       <c r="H97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3590,6 +3884,9 @@
       <c r="H98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="I98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3622,6 +3919,9 @@
       <c r="H99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="I99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3654,6 +3954,9 @@
       <c r="H100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3686,6 +3989,9 @@
       <c r="H101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3718,6 +4024,9 @@
       <c r="H102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3750,6 +4059,9 @@
       <c r="H103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="I103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3782,6 +4094,9 @@
       <c r="H104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3814,6 +4129,9 @@
       <c r="H105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3846,6 +4164,9 @@
       <c r="H106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="I106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3878,6 +4199,9 @@
       <c r="H107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="I107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3910,6 +4234,9 @@
       <c r="H108" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I108" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3942,6 +4269,9 @@
       <c r="H109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3974,6 +4304,9 @@
       <c r="H110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="I110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4006,6 +4339,9 @@
       <c r="H111" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I111" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4038,6 +4374,9 @@
       <c r="H112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4070,6 +4409,9 @@
       <c r="H113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4102,6 +4444,9 @@
       <c r="H114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4134,6 +4479,9 @@
       <c r="H115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="I115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4166,6 +4514,9 @@
       <c r="H116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4198,6 +4549,9 @@
       <c r="H117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="I117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4230,6 +4584,9 @@
       <c r="H118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4262,6 +4619,9 @@
       <c r="H119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="I119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4294,6 +4654,9 @@
       <c r="H120" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="I120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4326,6 +4689,9 @@
       <c r="H121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="I121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4358,6 +4724,9 @@
       <c r="H122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="I122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4390,6 +4759,9 @@
       <c r="H123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="I123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4422,6 +4794,9 @@
       <c r="H124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4454,6 +4829,9 @@
       <c r="H125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4486,6 +4864,9 @@
       <c r="H126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4518,6 +4899,9 @@
       <c r="H127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="I127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4550,6 +4934,9 @@
       <c r="H128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4582,6 +4969,9 @@
       <c r="H129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4614,6 +5004,9 @@
       <c r="H130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4646,6 +5039,9 @@
       <c r="H131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="I131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4678,6 +5074,9 @@
       <c r="H132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="I132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4710,6 +5109,9 @@
       <c r="H133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4742,6 +5144,9 @@
       <c r="H134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="I134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4774,6 +5179,9 @@
       <c r="H135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4806,6 +5214,9 @@
       <c r="H136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4838,6 +5249,9 @@
       <c r="H137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="I137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4870,6 +5284,9 @@
       <c r="H138" s="2" t="n">
         <v>22.19</v>
       </c>
+      <c r="I138" s="2" t="n">
+        <v>23.29</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4902,6 +5319,9 @@
       <c r="H139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4934,6 +5354,9 @@
       <c r="H140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4966,6 +5389,9 @@
       <c r="H141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4998,6 +5424,9 @@
       <c r="H142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5030,6 +5459,9 @@
       <c r="H143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5062,6 +5494,9 @@
       <c r="H144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="I144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5094,6 +5529,9 @@
       <c r="H145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="I145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5126,6 +5564,9 @@
       <c r="H146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5158,6 +5599,9 @@
       <c r="H147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="I147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5190,6 +5634,9 @@
       <c r="H148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="I148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5222,6 +5669,9 @@
       <c r="H149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="I149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5254,6 +5704,9 @@
       <c r="H150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="I150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5286,6 +5739,9 @@
       <c r="H151" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I151" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5318,6 +5774,9 @@
       <c r="H152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5350,6 +5809,9 @@
       <c r="H153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="I153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5382,6 +5844,9 @@
       <c r="H154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="I154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5414,6 +5879,9 @@
       <c r="H155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="I155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5446,6 +5914,9 @@
       <c r="H156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5478,6 +5949,9 @@
       <c r="H157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="I157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5510,6 +5984,9 @@
       <c r="H158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5542,6 +6019,9 @@
       <c r="H159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="I159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5574,6 +6054,9 @@
       <c r="H160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5606,6 +6089,9 @@
       <c r="H161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="I161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5638,6 +6124,9 @@
       <c r="H162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="I162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5670,6 +6159,9 @@
       <c r="H163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="I163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5702,6 +6194,9 @@
       <c r="H164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="I164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5734,9 +6229,12 @@
       <c r="H165" s="2" t="n">
         <v>20.59</v>
       </c>
+      <c r="I165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H165"/>
+  <autoFilter ref="A1:I165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historial/daily/latest_daily.xlsx
+++ b/historial/daily/latest_daily.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Evolutivo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$I$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evolutivo'!$A$1:$J$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,6 +493,11 @@
           <t>2026-09-12 19:13</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +533,9 @@
       <c r="I2" s="2" t="n">
         <v>13.45</v>
       </c>
+      <c r="J2" s="2" t="n">
+        <v>13.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,6 +571,9 @@
       <c r="I3" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="J3" s="2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +609,9 @@
       <c r="I4" s="2" t="n">
         <v>17.95</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>17.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,6 +647,9 @@
       <c r="I5" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J5" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +685,9 @@
       <c r="I6" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="J6" s="2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -702,6 +723,9 @@
       <c r="I7" s="2" t="n">
         <v>19.49</v>
       </c>
+      <c r="J7" s="2" t="n">
+        <v>19.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +761,9 @@
       <c r="I8" s="2" t="n">
         <v>20.49</v>
       </c>
+      <c r="J8" s="2" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,6 +799,9 @@
       <c r="I9" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="J9" s="2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -807,6 +837,9 @@
       <c r="I10" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J10" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,6 +875,9 @@
       <c r="I11" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J11" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -877,6 +913,9 @@
       <c r="I12" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J12" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -912,6 +951,9 @@
       <c r="I13" s="2" t="n">
         <v>20.2</v>
       </c>
+      <c r="J13" s="2" t="n">
+        <v>20.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -947,6 +989,9 @@
       <c r="I14" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J14" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -982,6 +1027,9 @@
       <c r="I15" s="2" t="n">
         <v>20.34</v>
       </c>
+      <c r="J15" s="2" t="n">
+        <v>20.34</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1017,6 +1065,9 @@
       <c r="I16" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J16" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1052,6 +1103,9 @@
       <c r="I17" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J17" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1087,6 +1141,9 @@
       <c r="I18" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J18" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1122,6 +1179,9 @@
       <c r="I19" s="2" t="n">
         <v>20.77</v>
       </c>
+      <c r="J19" s="2" t="n">
+        <v>20.77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1157,6 +1217,9 @@
       <c r="I20" s="2" t="n">
         <v>20.65</v>
       </c>
+      <c r="J20" s="2" t="n">
+        <v>20.65</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1192,6 +1255,9 @@
       <c r="I21" s="2" t="n">
         <v>20.48</v>
       </c>
+      <c r="J21" s="2" t="n">
+        <v>20.48</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1227,6 +1293,9 @@
       <c r="I22" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J22" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1262,6 +1331,9 @@
       <c r="I23" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J23" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1297,6 +1369,9 @@
       <c r="I24" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J24" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1332,6 +1407,9 @@
       <c r="I25" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J25" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1367,6 +1445,9 @@
       <c r="I26" s="2" t="n">
         <v>20.8</v>
       </c>
+      <c r="J26" s="2" t="n">
+        <v>20.8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1402,6 +1483,9 @@
       <c r="I27" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J27" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1437,6 +1521,9 @@
       <c r="I28" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J28" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1472,6 +1559,9 @@
       <c r="I29" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J29" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1597,9 @@
       <c r="I30" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J30" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1542,6 +1635,9 @@
       <c r="I31" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J31" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1577,6 +1673,9 @@
       <c r="I32" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J32" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1612,6 +1711,9 @@
       <c r="I33" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J33" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1647,6 +1749,9 @@
       <c r="I34" s="2" t="n">
         <v>21.22</v>
       </c>
+      <c r="J34" s="2" t="n">
+        <v>21.22</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1682,6 +1787,9 @@
       <c r="I35" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J35" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1717,6 +1825,9 @@
       <c r="I36" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J36" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1752,6 +1863,9 @@
       <c r="I37" s="2" t="n">
         <v>20.68</v>
       </c>
+      <c r="J37" s="2" t="n">
+        <v>20.68</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1787,6 +1901,9 @@
       <c r="I38" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J38" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1822,6 +1939,9 @@
       <c r="I39" s="2" t="n">
         <v>20.98</v>
       </c>
+      <c r="J39" s="2" t="n">
+        <v>20.98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1857,6 +1977,9 @@
       <c r="I40" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J40" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1892,6 +2015,9 @@
       <c r="I41" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J41" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,6 +2053,9 @@
       <c r="I42" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J42" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1962,6 +2091,9 @@
       <c r="I43" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J43" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1997,6 +2129,9 @@
       <c r="I44" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J44" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2032,6 +2167,9 @@
       <c r="I45" s="2" t="n">
         <v>20.69</v>
       </c>
+      <c r="J45" s="2" t="n">
+        <v>20.69</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2067,6 +2205,9 @@
       <c r="I46" s="2" t="n">
         <v>21.15</v>
       </c>
+      <c r="J46" s="2" t="n">
+        <v>21.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2102,6 +2243,9 @@
       <c r="I47" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J47" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2137,6 +2281,9 @@
       <c r="I48" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J48" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2172,6 +2319,9 @@
       <c r="I49" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J49" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2207,6 +2357,9 @@
       <c r="I50" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J50" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2242,6 +2395,9 @@
       <c r="I51" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="J51" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2277,6 +2433,9 @@
       <c r="I52" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J52" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2312,6 +2471,9 @@
       <c r="I53" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J53" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2347,6 +2509,9 @@
       <c r="I54" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J54" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2382,6 +2547,9 @@
       <c r="I55" s="2" t="n">
         <v>21.3</v>
       </c>
+      <c r="J55" s="2" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2417,6 +2585,9 @@
       <c r="I56" s="2" t="n">
         <v>20.89</v>
       </c>
+      <c r="J56" s="2" t="n">
+        <v>20.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2452,6 +2623,9 @@
       <c r="I57" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J57" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2487,6 +2661,9 @@
       <c r="I58" s="2" t="n">
         <v>22.75</v>
       </c>
+      <c r="J58" s="2" t="n">
+        <v>22.75</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2522,6 +2699,9 @@
       <c r="I59" s="2" t="n">
         <v>22.2</v>
       </c>
+      <c r="J59" s="2" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2557,6 +2737,9 @@
       <c r="I60" s="2" t="n">
         <v>20.9</v>
       </c>
+      <c r="J60" s="2" t="n">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2592,6 +2775,9 @@
       <c r="I61" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="J61" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2627,6 +2813,9 @@
       <c r="I62" s="2" t="n">
         <v>21.55</v>
       </c>
+      <c r="J62" s="2" t="n">
+        <v>21.55</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +2851,9 @@
       <c r="I63" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="J63" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2697,6 +2889,9 @@
       <c r="I64" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J64" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2732,6 +2927,9 @@
       <c r="I65" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J65" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2767,6 +2965,9 @@
       <c r="I66" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J66" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2802,6 +3003,9 @@
       <c r="I67" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J67" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2837,6 +3041,9 @@
       <c r="I68" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J68" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2872,6 +3079,9 @@
       <c r="I69" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J69" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2907,6 +3117,9 @@
       <c r="I70" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J70" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2942,6 +3155,9 @@
       <c r="I71" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J71" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2977,6 +3193,9 @@
       <c r="I72" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J72" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3012,6 +3231,9 @@
       <c r="I73" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J73" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3047,6 +3269,9 @@
       <c r="I74" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J74" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3082,6 +3307,9 @@
       <c r="I75" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J75" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3117,6 +3345,9 @@
       <c r="I76" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J76" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3152,6 +3383,9 @@
       <c r="I77" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J77" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3187,6 +3421,9 @@
       <c r="I78" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J78" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3222,6 +3459,9 @@
       <c r="I79" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J79" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3257,6 +3497,9 @@
       <c r="I80" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J80" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3292,6 +3535,9 @@
       <c r="I81" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J81" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3327,6 +3573,9 @@
       <c r="I82" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J82" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3362,6 +3611,9 @@
       <c r="I83" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J83" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3397,6 +3649,9 @@
       <c r="I84" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J84" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3432,6 +3687,9 @@
       <c r="I85" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J85" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3467,6 +3725,9 @@
       <c r="I86" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J86" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3502,6 +3763,9 @@
       <c r="I87" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J87" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3537,6 +3801,9 @@
       <c r="I88" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J88" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3572,6 +3839,9 @@
       <c r="I89" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J89" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3607,6 +3877,9 @@
       <c r="I90" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J90" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3642,6 +3915,9 @@
       <c r="I91" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J91" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3677,6 +3953,9 @@
       <c r="I92" s="2" t="n">
         <v>21.29</v>
       </c>
+      <c r="J92" s="2" t="n">
+        <v>21.29</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3712,6 +3991,9 @@
       <c r="I93" s="2" t="n">
         <v>21.89</v>
       </c>
+      <c r="J93" s="2" t="n">
+        <v>21.89</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3747,6 +4029,9 @@
       <c r="I94" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J94" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3782,6 +4067,9 @@
       <c r="I95" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J95" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3817,6 +4105,9 @@
       <c r="I96" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="J96" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3852,6 +4143,9 @@
       <c r="I97" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J97" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3887,6 +4181,9 @@
       <c r="I98" s="2" t="n">
         <v>20.95</v>
       </c>
+      <c r="J98" s="2" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3922,6 +4219,9 @@
       <c r="I99" s="2" t="n">
         <v>20.99</v>
       </c>
+      <c r="J99" s="2" t="n">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3957,6 +4257,9 @@
       <c r="I100" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J100" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3992,6 +4295,9 @@
       <c r="I101" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J101" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4027,6 +4333,9 @@
       <c r="I102" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J102" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4062,6 +4371,9 @@
       <c r="I103" s="2" t="n">
         <v>21.19</v>
       </c>
+      <c r="J103" s="2" t="n">
+        <v>21.19</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4097,6 +4409,9 @@
       <c r="I104" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J104" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4132,6 +4447,9 @@
       <c r="I105" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J105" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4167,6 +4485,9 @@
       <c r="I106" s="2" t="n">
         <v>21.28</v>
       </c>
+      <c r="J106" s="2" t="n">
+        <v>21.28</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4202,6 +4523,9 @@
       <c r="I107" s="2" t="n">
         <v>21.09</v>
       </c>
+      <c r="J107" s="2" t="n">
+        <v>21.09</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4237,6 +4561,9 @@
       <c r="I108" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J108" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4272,6 +4599,9 @@
       <c r="I109" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J109" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4307,6 +4637,9 @@
       <c r="I110" s="2" t="n">
         <v>20.79</v>
       </c>
+      <c r="J110" s="2" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4342,6 +4675,9 @@
       <c r="I111" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J111" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4377,6 +4713,9 @@
       <c r="I112" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J112" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4412,6 +4751,9 @@
       <c r="I113" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J113" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4447,6 +4789,9 @@
       <c r="I114" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J114" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4482,6 +4827,9 @@
       <c r="I115" s="2" t="n">
         <v>21.65</v>
       </c>
+      <c r="J115" s="2" t="n">
+        <v>21.65</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4517,6 +4865,9 @@
       <c r="I116" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J116" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4552,6 +4903,9 @@
       <c r="I117" s="2" t="n">
         <v>21.59</v>
       </c>
+      <c r="J117" s="2" t="n">
+        <v>21.59</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4587,6 +4941,9 @@
       <c r="I118" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J118" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4622,6 +4979,9 @@
       <c r="I119" s="2" t="n">
         <v>21.35</v>
       </c>
+      <c r="J119" s="2" t="n">
+        <v>21.35</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4657,6 +5017,9 @@
       <c r="I120" s="2" t="n">
         <v>21.79</v>
       </c>
+      <c r="J120" s="2" t="n">
+        <v>21.79</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4692,6 +5055,9 @@
       <c r="I121" s="2" t="n">
         <v>21.75</v>
       </c>
+      <c r="J121" s="2" t="n">
+        <v>21.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4727,6 +5093,9 @@
       <c r="I122" s="2" t="n">
         <v>21.39</v>
       </c>
+      <c r="J122" s="2" t="n">
+        <v>21.39</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4762,6 +5131,9 @@
       <c r="I123" s="2" t="n">
         <v>21.69</v>
       </c>
+      <c r="J123" s="2" t="n">
+        <v>21.69</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4797,6 +5169,9 @@
       <c r="I124" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J124" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4832,6 +5207,9 @@
       <c r="I125" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J125" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4867,6 +5245,9 @@
       <c r="I126" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J126" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4902,6 +5283,9 @@
       <c r="I127" s="2" t="n">
         <v>21.49</v>
       </c>
+      <c r="J127" s="2" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4937,6 +5321,9 @@
       <c r="I128" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J128" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4972,6 +5359,9 @@
       <c r="I129" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J129" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5007,6 +5397,9 @@
       <c r="I130" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J130" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5042,6 +5435,9 @@
       <c r="I131" s="2" t="n">
         <v>21.5</v>
       </c>
+      <c r="J131" s="2" t="n">
+        <v>21.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5077,6 +5473,9 @@
       <c r="I132" s="2" t="n">
         <v>21.6</v>
       </c>
+      <c r="J132" s="2" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5112,6 +5511,9 @@
       <c r="I133" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J133" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5147,6 +5549,9 @@
       <c r="I134" s="2" t="n">
         <v>21.7</v>
       </c>
+      <c r="J134" s="2" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5182,6 +5587,9 @@
       <c r="I135" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J135" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5217,6 +5625,9 @@
       <c r="I136" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J136" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5252,6 +5663,9 @@
       <c r="I137" s="2" t="n">
         <v>21.8</v>
       </c>
+      <c r="J137" s="2" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5287,6 +5701,9 @@
       <c r="I138" s="2" t="n">
         <v>23.29</v>
       </c>
+      <c r="J138" s="2" t="n">
+        <v>23.29</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5322,6 +5739,9 @@
       <c r="I139" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J139" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5357,6 +5777,9 @@
       <c r="I140" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J140" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5392,6 +5815,9 @@
       <c r="I141" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J141" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5427,6 +5853,9 @@
       <c r="I142" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J142" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5462,6 +5891,9 @@
       <c r="I143" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J143" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5497,6 +5929,9 @@
       <c r="I144" s="2" t="n">
         <v>21.99</v>
       </c>
+      <c r="J144" s="2" t="n">
+        <v>21.99</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5532,6 +5967,9 @@
       <c r="I145" s="2" t="n">
         <v>22.29</v>
       </c>
+      <c r="J145" s="2" t="n">
+        <v>22.29</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5567,6 +6005,9 @@
       <c r="I146" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J146" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5602,6 +6043,9 @@
       <c r="I147" s="2" t="n">
         <v>22.3</v>
       </c>
+      <c r="J147" s="2" t="n">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5637,6 +6081,9 @@
       <c r="I148" s="2" t="n">
         <v>22.35</v>
       </c>
+      <c r="J148" s="2" t="n">
+        <v>22.35</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5672,6 +6119,9 @@
       <c r="I149" s="2" t="n">
         <v>22.49</v>
       </c>
+      <c r="J149" s="2" t="n">
+        <v>22.49</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5707,6 +6157,9 @@
       <c r="I150" s="2" t="n">
         <v>22.5</v>
       </c>
+      <c r="J150" s="2" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5742,6 +6195,9 @@
       <c r="I151" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J151" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5777,6 +6233,9 @@
       <c r="I152" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J152" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5812,6 +6271,9 @@
       <c r="I153" s="2" t="n">
         <v>22.6</v>
       </c>
+      <c r="J153" s="2" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5847,6 +6309,9 @@
       <c r="I154" s="2" t="n">
         <v>22.7</v>
       </c>
+      <c r="J154" s="2" t="n">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5882,6 +6347,9 @@
       <c r="I155" s="2" t="n">
         <v>22.79</v>
       </c>
+      <c r="J155" s="2" t="n">
+        <v>22.79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5917,6 +6385,9 @@
       <c r="I156" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J156" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5952,6 +6423,9 @@
       <c r="I157" s="2" t="n">
         <v>22.8</v>
       </c>
+      <c r="J157" s="2" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5987,6 +6461,9 @@
       <c r="I158" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J158" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6022,6 +6499,9 @@
       <c r="I159" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J159" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6057,6 +6537,9 @@
       <c r="I160" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J160" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6092,6 +6575,9 @@
       <c r="I161" s="2" t="n">
         <v>22.99</v>
       </c>
+      <c r="J161" s="2" t="n">
+        <v>22.99</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6127,6 +6613,9 @@
       <c r="I162" s="2" t="n">
         <v>23.99</v>
       </c>
+      <c r="J162" s="2" t="n">
+        <v>23.99</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6162,6 +6651,9 @@
       <c r="I163" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="J163" s="2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6197,6 +6689,9 @@
       <c r="I164" s="2" t="n">
         <v>24.25</v>
       </c>
+      <c r="J164" s="2" t="n">
+        <v>24.25</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6232,9 +6727,12 @@
       <c r="I165" s="2" t="n">
         <v>20.59</v>
       </c>
+      <c r="J165" s="2" t="n">
+        <v>20.59</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I165"/>
+  <autoFilter ref="A1:J165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>